--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -3315,17 +3315,17 @@
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Move to Pipeline &amp; Mandates</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>Include - aggregate actual pooled mandate</t>
+          <t>Moved - aggregate pooled mandate</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>Retain as aggregate consortium archetype, not as a conventional fund LP row. IFC reports KEPFIC mobilized $113m into two housing projects and facilitated two member-fund investments; MiDA reports Lot 3 Road Project Bonds investment by KEPFIC members.</t>
+          <t>Aggregate pooled mandate / consortium archetype, not a conventional fund vehicle LP row. Kept out of Fund Vehicles and Commitments Database to avoid treating a mandate platform as a fund commitment.</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
@@ -3539,17 +3539,17 @@
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Move to Pipeline &amp; Mandates</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>Include - aggregate actual pooled mandate</t>
+          <t>Moved - aggregate pooled mandate</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
         <is>
-          <t>Retain as aggregate consortium archetype. Engineering News reports AOFSA member funds collectively committed R5.7bn to infrastructure; MiDA/USAID sources also report &gt;$400m commitments.</t>
+          <t>Aggregate pooled mandate / consortium archetype, not a conventional fund vehicle LP row. Kept out of Fund Vehicles and Commitments Database to avoid treating a mandate platform as a fund commitment.</t>
         </is>
       </c>
       <c r="H41" s="23" t="inlineStr">
@@ -31365,7 +31365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="16" min="1" max="1"/>
@@ -32440,6 +32440,170 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KEPFIC (Kenya Pension Funds Investment Consortium)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pension consortium / pooled mandate</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pooled mandate / aggregate evidence</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Various managers via KEPFIC consortium</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KEPFIC pooled mandates (Kenya)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Infrastructure / Alts</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kenya + regional</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2019-ongoing</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>USD 113m mobilized into two housing projects; member AUM ~USD 5bn</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Aggregate consortium / pooled mandate</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>IFC 2023; MiDA Advisors</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Aggregate pooled mandate / consortium archetype, not a conventional fund vehicle LP row. Kept out of Fund Vehicles and Commitments Database to avoid treating a mandate platform as a fund commitment.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://www.ifc.org/en/stories/2023/pooling-pensions-in-kenya ; https://www.midaadvisors.com/advisory-firm-financing-the-development-of-critical-infrastructure-in-kenya-with-local-institutional-capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Asset Owners Forum of South Africa (AOFSA)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pension consortium / pooled mandate</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pooled mandate / aggregate evidence</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Various managers via AOFSA consortium</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AOFSA pooled infrastructure mandates (South Africa)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Infrastructure / Alts</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2021-ongoing</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>R5.7bn / USD 400m+ collectively committed to infrastructure and other alternatives</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ZAR / USD</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Aggregate consortium / pooled mandate</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Engineering News 2022; MiDA/USAID AOFSA case materials</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Aggregate pooled mandate / consortium archetype, not a conventional fund vehicle LP row. Kept out of Fund Vehicles and Commitments Database to avoid treating a mandate platform as a fund commitment.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://www.engineeringnews.co.za/article/aofsa-exceeds-infrastructure-investment-target-as-it-marks-first-anniversary-2022-11-21 ; https://www.midaadvisors.com/advisory-firm-what-we-do/institutional-investors-capacity-development</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32452,7 +32616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -33997,104 +34161,106 @@
     <row r="29" ht="45.75" customHeight="1" s="16">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KEPFIC pooled mandates (Kenya)</t>
+          <t>Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Various (mandates allocated to managers)</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>2019-ongoing</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>USD 113m mobilized into two housing projects; member AUM ~USD 5bn</t>
-        </is>
+          <t>Sahel Capital</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>65.90000000000001</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure / alts</t>
+          <t>PE / Agribusiness</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Kenya + regional</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>24 member schemes</t>
-        </is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24 Kenyan retirement benefit funds (named on KEPFIC site); collective ~1/3 of total Kenyan pension AUM</t>
+          <t>NSIA Nigeria</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
+          <t>AfDB, BII, Dutch Good Growth Fund</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>USAID + World Bank Group technical support; FMA Kenya MOU</t>
-        </is>
-      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Aggregate consortium archetype, not a conventional fund LP row. Retained because IFC reports two facilitated member-fund investments and $113m mobilized; MiDA reports members invested in Lot 3 Road Project Bonds.</t>
+          <t>NSIA's earliest disclosed PE fund LP position; alongside three DFIs.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="90.75" customHeight="1" s="16">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN)</t>
+          <t>Capital Alliance Private Equity I-IV (CAPE)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Sahel Capital</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>65.90000000000001</v>
+          <t>African Capital Alliance (ACA)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1998-ongoing</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>&gt;1,000 cumulative</t>
+        </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>PE / Agribusiness</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>1</v>
+          <t>Nigeria + West Africa</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>historical cohort</t>
+        </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>NSIA Nigeria</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>3</v>
+          <t>Nigerian PFAs (categorical historical disclosure; ACA explicitly 'championed PE inclusion as allowable Nigerian pension asset class')</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>AfDB, BII, Dutch Good Growth Fund</t>
+          <t>BII (CAPE IV); various DFIs across vintages</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -34104,59 +34270,53 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>NSIA's earliest disclosed PE fund LP position; alongside three DFIs.</t>
+          <t>First Nigerian PE firm (founded 1997); CAPE I was Nigeria's first PE fund (1998). Continental pioneer of pension-PE inclusion.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="23.25" customHeight="1" s="16">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Capital Alliance Private Equity I-IV (CAPE)</t>
+          <t>Rwanda SME Growth Fund</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>African Capital Alliance (ACA)</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>1998-ongoing</t>
-        </is>
+          <t>Enko Capital (Rwanda subsidiary)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>2026</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>&gt;1,000 cumulative</t>
+          <t>30 first close (target 100)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PE / SME growth (local-currency)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Nigeria + West Africa</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>historical cohort</t>
-        </is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Nigerian PFAs (categorical historical disclosure; ACA explicitly 'championed PE inclusion as allowable Nigerian pension asset class')</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
+          <t>RSSB (Rwanda Social Security Board) — USD 30m anchor + USD 3m TA seed</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>BII (CAPE IV); various DFIs across vintages</t>
+          <t>FSD Africa Investments (structuring + planned guarantee)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -34166,105 +34326,105 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>First Nigerian PE firm (founded 1997); CAPE I was Nigeria's first PE fund (1998). Continental pioneer of pension-PE inclusion.</t>
+          <t>First permanent capital vehicle anchored by an African pension fund (per RSSB CEO). Three regional firsts: pension-fund-led SME-only mandate, anchor permanent-capital vehicle, pension-fund TA facility.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="23.25" customHeight="1" s="16">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Rwanda SME Growth Fund</t>
+          <t>Mirepa Capital SME Fund I</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Enko Capital (Rwanda subsidiary)</t>
+          <t>Mirepa Investment Advisors</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>30 first close (target 100)</t>
+          <t>~10-12 (GHS 120m initial close)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>PE / SME growth (local-currency)</t>
+          <t>PE / SME growth</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Rwanda</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>1</v>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2 named pension trustees + categorical CAMCOL schemes</t>
+        </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>RSSB (Rwanda Social Security Board) — USD 30m anchor + USD 3m TA seed</t>
+          <t>Petra Trust; Axis Pensions; multiple schemes via CAL Asset Management Company (CAMCOL); Venture Capital Trust Fund (VCTF)</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>FSD Africa Investments (structuring + planned guarantee)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VCTF is a Ghanaian quasi-government VC fund (not strictly a DFI)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>First permanent capital vehicle anchored by an African pension fund (per RSSB CEO). Three regional firsts: pension-fund-led SME-only mandate, anchor permanent-capital vehicle, pension-fund TA facility.</t>
+          <t>Second Ghana fund anchored solely by local investors (after Injaro IGVCF). 100% local-LP-funded. Confirms Ghana's emerging mandated-minimum-alts policy is producing real deal flow.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="23.25" customHeight="1" s="16">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AOFSA pooled infrastructure mandates (South Africa)</t>
+          <t>Injaro Ghana Venture Capital Fund (IGVCF)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Various managers (mandates allocated)</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>2021-ongoing</t>
-        </is>
+          <t>Injaro Investment Advisors</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2023</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>R5.7bn / USD 400m+ collectively committed to infrastructure and other alternatives</t>
+          <t>~17.4 (GHS 216m final close Dec 2023)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure / Alts</t>
+          <t>PE / SME / VC</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Ghana + Côte d'Ivoire</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12-15 member schemes</t>
+          <t>multiple Ghanaian pension funds (anchor cohort)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>GEPF; EPPF; Telkom Retirement Fund; Transnet Retirement Fund; National Fund for Municipal Workers; KZN Joint Municipal Pension Fund (NJMPF); KZN Municipal Pension Fund; Motor Industry Retirement Fund (named); 4-7 additional founding members not individually named</t>
+          <t>Specific names not individually disclosed</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
@@ -34277,131 +34437,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Batseta Council; USAID + MiDA Advisors + World Bank technical support</t>
+          <t>Venture Capital Trust Fund (VCTF) of Ghana</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Aggregate consortium archetype, not a conventional fund LP row. Retained because public sources report actual collective member commitments, while individual member rows are not separately counted as commitments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="23.25" customHeight="1" s="16">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Mirepa Capital SME Fund I</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Mirepa Investment Advisors</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>~10-12 (GHS 120m initial close)</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>PE / SME growth</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>2 named pension trustees + categorical CAMCOL schemes</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Petra Trust; Axis Pensions; multiple schemes via CAL Asset Management Company (CAMCOL); Venture Capital Trust Fund (VCTF)</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>VCTF is a Ghanaian quasi-government VC fund (not strictly a DFI)</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Second Ghana fund anchored solely by local investors (after Injaro IGVCF). 100% local-LP-funded. Confirms Ghana's emerging mandated-minimum-alts policy is producing real deal flow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="23.25" customHeight="1" s="16">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Injaro Ghana Venture Capital Fund (IGVCF)</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Injaro Investment Advisors</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>~17.4 (GHS 216m final close Dec 2023)</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>PE / SME / VC</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Ghana + Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>multiple Ghanaian pension funds (anchor cohort)</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Specific names not individually disclosed</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Venture Capital Trust Fund (VCTF) of Ghana</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
           <t>FIRST Ghana fund of its kind anchored by local pension funds. Historical precedent for Mirepa I, Ci-Gaba, GIP Ghana model. Ghana cedi-denominated.</t>
         </is>
       </c>
     </row>
+    <row r="34" ht="23.25" customHeight="1" s="16"/>
+    <row r="35" ht="23.25" customHeight="1" s="16"/>
     <row r="36" ht="15" customHeight="1" s="16"/>
     <row r="37" ht="34.5" customHeight="1" s="16"/>
     <row r="38" ht="23.25" customHeight="1" s="16"/>
@@ -36911,7 +36957,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="16">
       <c r="A19" s="18" t="inlineStr">
         <is>
@@ -36927,7 +36972,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -2035,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="16" min="1" max="1"/>
@@ -4074,6 +4074,43 @@
       </c>
       <c r="H56" s="23" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Africa Food Security Fund (AFSF)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PIC on behalf of GEPF (South Africa)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Include - confirmed African PF/SWF LP</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DGGF names PIC on behalf of GEPF as a first-round investor in AFSF alongside DFIs and DGGF; this is confirmed African pension fund involvement in a fund vehicle.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://english.dggf.nl/latest/news/2019/01/24/zebu-s-africa-food-security-fund-a-dggf-investee-reaches-total-fund-size-of-usd-84-million</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4086,7 +4123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F179"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -9789,6 +9826,38 @@
       <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Kenya Cabinet-approved National Infrastructure Fund + SWF; KPC IPO planned March 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>GEPF / PIC</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>DFI / fund announcement</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>DGGF - Zebu Africa Food Security Fund reaches total fund size of USD 84 million</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://english.dggf.nl/latest/news/2019/01/24/zebu-s-africa-food-security-fund-a-dggf-investee-reaches-total-fund-size-of-usd-84-million</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>PIC/GEPF LP confirmation in Africa Food Security Fund; co-investors AfDB, CDC/BII, DGGF, IFU, EBID and Kuramo</t>
         </is>
       </c>
     </row>
@@ -24770,7 +24839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -31329,7 +31398,81 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="34.5" customHeight="1" s="16"/>
+    <row r="87" ht="34.5" customHeight="1" s="16">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>GEPF / PIC (South Africa)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Public PF (via asset manager)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Zebu Investment Partners</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Africa Food Security Fund (AFSF)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>PE / agriculture / food security</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>2019</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Not disclosed; fund size USD 84m</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>DFI / fund close announcement</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>DGGF news release, Jan 2019</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>DGGF names PIC on behalf of GEPF among first-round AFSF investors alongside AfDB, CDC Group/BII, DGGF, IFU, and EBID; Kuramo later joined, bringing fund commitments to USD 84m.</t>
+        </is>
+      </c>
+    </row>
     <row r="88" ht="45.75" customHeight="1" s="16"/>
     <row r="89" ht="34.5" customHeight="1" s="16"/>
     <row r="90" ht="34.5" customHeight="1" s="16"/>
@@ -32616,7 +32759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -34446,7 +34589,60 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="23.25" customHeight="1" s="16"/>
+    <row r="34" ht="23.25" customHeight="1" s="16">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Africa Food Security Fund (AFSF)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Zebu Investment Partners</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D34" t="n">
+        <v>84</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PE / agriculture / food security</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PIC on behalf of GEPF (South Africa)</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>AfDB; BII (CDC Group); Dutch Good Growth Fund (DGGF); IFU; EBID</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Kuramo Capital Management</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DGGF news release names PIC/GEPF in first-round investor group alongside DFIs and DGGF; Kuramo subsequently joined to bring commitments to USD 84m.</t>
+        </is>
+      </c>
+    </row>
     <row r="35" ht="23.25" customHeight="1" s="16"/>
     <row r="36" ht="15" customHeight="1" s="16"/>
     <row r="37" ht="34.5" customHeight="1" s="16"/>
@@ -34475,7 +34671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="16" min="1" max="1"/>
@@ -34526,11 +34722,11 @@
         </is>
       </c>
       <c r="B4" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
-          <t>Ascent Rift Valley Fund II (ARVF II); Capital Alliance Private Equity I-IV (CAPE); Catalyst Fund II; Growth Investment Partners (GIP) Ghana; Growth Investment Partners (GIP) Zambia; Helios Investors II/III/IV (historical); Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Vantage Mezzanine IV (Pan-African sub-fund)</t>
+          <t>Ascent Rift Valley Fund II (ARVF II); Capital Alliance Private Equity I-IV (CAPE); Catalyst Fund II; Growth Investment Partners (GIP) Ghana; Growth Investment Partners (GIP) Zambia; Helios Investors II/III/IV (historical); Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Vantage Mezzanine IV (Pan-African sub-fund); Africa Food Security Fund (AFSF)</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -34551,11 +34747,11 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Africa50 (general); Africa50 Infrastructure Acceleration Fund (IAF); Mediterrania Capital II / III / IV; Nigeria Infrastructure Fund (NIF, NSIA sub-fund); Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN)</t>
+          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Africa50 (general); Africa50 Infrastructure Acceleration Fund (IAF); Mediterrania Capital II / III / IV; Nigeria Infrastructure Fund (NIF, NSIA sub-fund); Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Africa Food Security Fund (AFSF)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -35026,11 +35222,11 @@
         </is>
       </c>
       <c r="B24" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN)</t>
+          <t>Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Africa Food Security Fund (AFSF)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -35101,11 +35297,11 @@
         </is>
       </c>
       <c r="B27" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>AfricInvest FIVE (Financial Inclusion Vehicle)</t>
+          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Africa Food Security Fund (AFSF)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -35236,6 +35432,56 @@
     <row r="46" ht="23.85" customHeight="1" s="16"/>
     <row r="47" ht="23.85" customHeight="1" s="16"/>
     <row r="48" ht="129.75" customHeight="1" s="16"/>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EBID</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Africa Food Security Fund (AFSF)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3 (Selective / TA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Kuramo Capital Management</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Africa Food Security Fund (AFSF)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Other named LP / fund-of-funds investor appearing in retained vehicles with African PF/SWF participation.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3 (Selective / TA)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:E27"/>
   <mergeCells count="3">

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -16,10 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country Summary" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology &amp; Caveats" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inclusion Audit" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Library" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absentees Investigation" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regulatory vs Behaviour" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVCA Aggregate vs Disclosed" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omission Candidates" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Library" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absentees Investigation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regulatory vs Behaviour" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVCA Aggregate vs Disclosed" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sovereign Wealth Funds'!$A$1:$K$27</definedName>
@@ -30,9 +31,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Funds &amp; LP Co-Investors'!$A$1:$L$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DFI Co-Investor Patterns'!$A$3:$E$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Inclusion Audit'!$A$1:$H$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Source Library'!$A$1:$F$178</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Absentees Investigation'!$A$3:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Regulatory vs Behaviour'!$A$3:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Source Library'!$A$1:$F$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Absentees Investigation'!$A$3:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Regulatory vs Behaviour'!$A$3:$H$22</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,7 +104,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -130,6 +131,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007A4E00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3A5C"/>
       </patternFill>
     </fill>
   </fills>
@@ -198,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -264,6 +270,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4123,6 +4132,444 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="16" min="1" max="1"/>
+    <col width="34" customWidth="1" style="16" min="2" max="2"/>
+    <col width="24" customWidth="1" style="16" min="3" max="3"/>
+    <col width="34" customWidth="1" style="16" min="4" max="4"/>
+    <col width="38" customWidth="1" style="16" min="5" max="5"/>
+    <col width="20" customWidth="1" style="16" min="6" max="6"/>
+    <col width="20" customWidth="1" style="16" min="7" max="7"/>
+    <col width="14" customWidth="1" style="16" min="8" max="8"/>
+    <col width="34" customWidth="1" style="16" min="9" max="9"/>
+    <col width="12" customWidth="1" style="16" min="10" max="10"/>
+    <col width="42" customWidth="1" style="16" min="11" max="11"/>
+    <col width="52" customWidth="1" style="16" min="12" max="12"/>
+    <col width="58" customWidth="1" style="16" min="13" max="13"/>
+    <col width="58" customWidth="1" style="16" min="14" max="14"/>
+    <col width="24" customWidth="1" style="16" min="15" max="15"/>
+    <col width="14" customWidth="1" style="16" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Candidate status</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Vehicle</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Manager / GP</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>African PF/SWF evidence</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>DFI / Other LP evidence</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>Asset class</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>Geographic focus</t>
+        </is>
+      </c>
+      <c r="H1" s="27" t="inlineStr">
+        <is>
+          <t>Vintage / year</t>
+        </is>
+      </c>
+      <c r="I1" s="27" t="inlineStr">
+        <is>
+          <t>Fund size / commitment evidence</t>
+        </is>
+      </c>
+      <c r="J1" s="27" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="K1" s="27" t="inlineStr">
+        <is>
+          <t>Recommended action</t>
+        </is>
+      </c>
+      <c r="L1" s="27" t="inlineStr">
+        <is>
+          <t>Evidence summary</t>
+        </is>
+      </c>
+      <c r="M1" s="27" t="inlineStr">
+        <is>
+          <t>Primary source URL</t>
+        </is>
+      </c>
+      <c r="N1" s="27" t="inlineStr">
+        <is>
+          <t>Secondary source URL</t>
+        </is>
+      </c>
+      <c r="O1" s="27" t="inlineStr">
+        <is>
+          <t>Search batch</t>
+        </is>
+      </c>
+      <c r="P1" s="27" t="inlineStr">
+        <is>
+          <t>Date added</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Actioned - added to database</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Africa Food Security Fund (AFSF)</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>Zebu Investment Partners</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>PIC on behalf of GEPF (South Africa)</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>AfDB; CDC Group/BII; Dutch Good Growth Fund; IFU; EBID; Kuramo Capital Management</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>PE / agriculture / food security</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>DGGF says AFSF reached USD 84m; BII page says total commitments USD 90m</t>
+        </is>
+      </c>
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K2" s="21" t="inlineStr">
+        <is>
+          <t>Already added to Commitments, Fund Vehicles, Source Library, Inclusion Audit, and DFI/Other LP patterns.</t>
+        </is>
+      </c>
+      <c r="L2" s="21" t="inlineStr">
+        <is>
+          <t>DGGF names PIC on behalf of GEPF in first-round investors alongside DFIs and DGGF; BII confirms CDC invested alongside PIC and DFI group.</t>
+        </is>
+      </c>
+      <c r="M2" s="21" t="inlineStr">
+        <is>
+          <t>https://english.dggf.nl/latest/news/2019/01/24/zebu-s-africa-food-security-fund-a-dggf-investee-reaches-total-fund-size-of-usd-84-million</t>
+        </is>
+      </c>
+      <c r="N2" s="21" t="inlineStr">
+        <is>
+          <t>https://www.bii.co.uk/en/our-impact/fund/africa-food-security-fund-i-investment-01/</t>
+        </is>
+      </c>
+      <c r="O2" s="21" t="inlineStr">
+        <is>
+          <t>PIC/GEPF + DFI sweep</t>
+        </is>
+      </c>
+      <c r="P2" s="21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>Candidate - likely add after row construction</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Pan African Infrastructure Development Fund (PAIDF)</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
+        <is>
+          <t>PAIDF Management Company / Harith-linked platform</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>PIC/GEPF; Eskom Pension and Provident Fund; SSNIT Ghana; Metropolitan/Old Mutual/Stanlib named in source context</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>AfDB; DBSA; Absa Capital; Barclays/ABSA Group</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>AfDB says target up to USD 450m initially; DBSA annual report says first close in Sep 2007 at USD 625m and DBSA committed USD 100m.</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>Add to Commitments and Fund Vehicles if historical scope includes older infrastructure funds; likely multiple African PF/SWF LP rows or a single aggregate historical PAIDF row.</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t>AfDB page names PIC/GEPF and EPPF as potential/reputable investors and PIC as chief sponsor; DBSA annual report says DBSA invested alongside PIC, AfDB, and SSNIT.</t>
+        </is>
+      </c>
+      <c r="M3" s="21" t="inlineStr">
+        <is>
+          <t>https://www.afdb.org/en/news-and-events/pan-african-infrastructure-development-fund-paidf-afdb-group-proposes-us-50-million-investment-in-paidf-3476</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t>https://www.dbsa.org/sites/default/files/media/documents/2021-09/DBSA%20and%20Development%20Fund%20Annual%20Reports%202008.pdf</t>
+        </is>
+      </c>
+      <c r="O3" s="21" t="inlineStr">
+        <is>
+          <t>PIC/GEPF + DFI sweep</t>
+        </is>
+      </c>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Candidate - new 2026 item</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Hlayisani Venture Fund II (HVF II)</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Hlayisani Capital</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Public Investment Corporation (PIC)</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>SA SME Fund; additional private investors and family offices</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>VC / technology-enabled SMEs</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>R500m / about USD 30m commitments to date; final close targeted June 2026.</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>Add to Commitments and Fund Vehicles as confirmed first-close/commitments-to-date, with note that final close is pending.</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t>Hlayisani and multiple trade sources say Fund II is anchored by PIC and SA SME Fund with R500m committed to date.</t>
+        </is>
+      </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>https://hlayisani.com/</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t>https://disruptafrica.com/2026/03/11/sas-hlayisani-capital-launches-2nd-fund-with-initial-29-9m-in-commitments/</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>PIC/GEPF + recent fund-close sweep</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Candidate - research vehicle identity</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Medu Capital Fund II</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Medu Capital</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Eskom Pension and Provident Fund; Public Investment Corporation</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>DBSA; CDC Group; FMO; Alternative Equity Partners; Brait; Metropolitan; Vunani</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>PE / BEE mid-market</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>DBSA annual report says capitalisation R850m; DBSA provided R100m.</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>M-H</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>Review whether the vehicle is in scope as alternatives/fund LP; likely add if historical South Africa domestic PE vehicles are included.</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>DBSA annual report identifies Medu II investors including EPPF, PIC, CDC, FMO and DBSA.</t>
+        </is>
+      </c>
+      <c r="M5" s="21" t="inlineStr">
+        <is>
+          <t>https://www.dbsa.org/sites/default/files/media/documents/2021-09/DBSA%20and%20Development%20Fund%20Annual%20Reports%202008.pdf</t>
+        </is>
+      </c>
+      <c r="N5" s="21" t="inlineStr"/>
+      <c r="O5" s="21" t="inlineStr">
+        <is>
+          <t>DBSA historical PE fund sweep</t>
+        </is>
+      </c>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F179"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
@@ -9868,7 +10315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10290,7 +10737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11166,7 +11613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>Oyass Capital</t>
+          <t>Oyass Capital (SME fund)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>Column H identifies a named African PF/SWF, a named cohort, or the allocator itself is an African SWF/PF vehicle.</t>
+          <t>Retain as a fund/financing vehicle, not a GP. FONSIS describes Oyass Capital as an SME private-equity fund/financing vehicle; SEAF is the manager.</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>Wessal Capital</t>
+          <t>Wessal Capital (SWF joint investment vehicle)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -3190,10 +3190,14 @@
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>Column H identifies a named African PF/SWF, a named cohort, or the allocator itself is an African SWF/PF vehicle.</t>
-        </is>
-      </c>
-      <c r="H31" s="23" t="inlineStr"/>
+          <t>Retain as a direct SWF joint investment vehicle/platform rather than a conventional GP-managed fund. Ithmar names Wessal as an investment vehicle and identifies Wessal Bouregreg and Wessal Casa-Port as launched projects.</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>https://www.ithmar.gov.ma/en/our-portfolio/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
@@ -4570,7 +4574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F179"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -5408,7 +5412,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>FONSIS Oyass Capital launch with SEAF as manager</t>
+          <t>Oyass Capital as FONSIS/KfW/World Bank-backed SME fund/financing vehicle; management mandate awarded to SEAF</t>
         </is>
       </c>
     </row>
@@ -10305,6 +10309,38 @@
       <c r="F179" t="inlineStr">
         <is>
           <t>PIC/GEPF LP confirmation in Africa Food Security Fund; co-investors AfDB, CDC/BII, DGGF, IFU, EBID and Kuramo</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Ithmar Capital</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SWF portfolio page</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ithmar Capital - Our portfolio: Wessal</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.ithmar.gov.ma/en/our-portfolio/</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Wessal as SWF joint investment vehicle; EUR 2.5bn equity commitment; projects Wessal Bouregreg and Wessal Casa-Port</t>
         </is>
       </c>
     </row>
@@ -10340,6 +10376,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -10763,6 +10800,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -11637,6 +11675,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="16">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -11644,6 +11683,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="23.25" customHeight="1" s="16">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -11752,6 +11792,8 @@
         <v>0.19</v>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="16">
       <c r="A11" s="8" t="inlineStr">
         <is>
@@ -12025,6 +12067,8 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="16">
       <c r="A32" s="8" t="inlineStr">
         <is>
@@ -23647,6 +23691,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -27157,22 +27202,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Fund LP</t>
+          <t>Platform / direct strategic investment vehicle</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Wessal Capital</t>
+          <t>Wessal Capital joint venture</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Wessal Capital (joint Morocco + Gulf SWFs platform)</t>
+          <t>Wessal Capital (SWF joint investment vehicle)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Direct / Real estate, infra</t>
+          <t>Direct / real estate / tourism infrastructure</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -27187,7 +27232,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>USD 2.5bn target</t>
+          <t>EUR 2.5bn equity commitment</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -27202,7 +27247,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Wessal Capital announcements</t>
+          <t>Ithmar portfolio: Wessal</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -27212,7 +27257,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Joint platform with Abu Dhabi, Kuwait, Qatar SWFs.</t>
+          <t>Ithmar describes Wessal as an investment vehicle / joint venture equally owned by five SWFs, not a conventional GP-managed fund. Named projects include Wessal Bouregreg and Wessal Casa-Port.</t>
         </is>
       </c>
     </row>
@@ -28450,7 +28495,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Fund LP</t>
+          <t>Fund LP / sponsor</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -28460,7 +28505,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Oyass Capital</t>
+          <t>Oyass Capital (SME fund)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -28503,7 +28548,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>FONSIS partnered with KfW (Germany) to launch Oyass Capital for Senegalese SMEs; awarded mgmt mandate to SEAF after intl tender.</t>
+          <t>FONSIS and KfW/World Bank launched Oyass Capital as an SME-focused private-equity fund/financing vehicle; FONSIS says SEAF received the management mandate after an international tender.</t>
         </is>
       </c>
     </row>
@@ -33230,6 +33275,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="45.75" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -33529,12 +33575,12 @@
     <row r="8" ht="34.5" customHeight="1" s="16">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Oyass Capital</t>
+          <t>Oyass Capital (SME fund)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SEAF (Small Enterprise Assistance Funds)</t>
+          <t>SEAF / SEAF Senegal</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -33544,7 +33590,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>~82 (XOF 50bn)</t>
+          <t>~79m target / EUR 54m mobilized</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -33580,7 +33626,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>FONSIS + KfW launch; SEAF mandate award after international tender.</t>
+          <t>FONSIS source describes Oyass Capital as an SME-focused private-equity fund/financing vehicle set up with KfW/World Bank support; management mandate awarded to SEAF.</t>
         </is>
       </c>
     </row>
@@ -34519,12 +34565,12 @@
     <row r="25" ht="34.5" customHeight="1" s="16">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Wessal Capital</t>
+          <t>Wessal Capital (SWF joint investment vehicle)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Wessal Capital partnership</t>
+          <t>Wessal Capital joint venture</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -34534,12 +34580,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>USD 2.5bn target</t>
+          <t>EUR 2.5bn equity commitment</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Direct (real estate / infra)</t>
+          <t>Direct / real estate / tourism infrastructure</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -34565,12 +34611,12 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Kuwait, Qatar SWFs (Gulf SWF co-investors)</t>
+          <t>Al Ajial Investment Fund Holding; Mubadala; Public Investment Fund; Qatar Holding</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Joint Morocco + Gulf SWF platform.</t>
+          <t>Ithmar describes Wessal as a joint investment vehicle, equally owned by five SWFs. Specific launched projects: Wessal Bouregreg and Wessal Casa-Port.</t>
         </is>
       </c>
     </row>
@@ -35135,6 +35181,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="45.75" customHeight="1" s="16">
       <c r="A3" s="24" t="inlineStr">
         <is>
@@ -35976,6 +36023,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -37650,6 +37698,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="16">
       <c r="A19" s="18" t="inlineStr">
         <is>
@@ -37665,6 +37714,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -29274,7 +29274,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Fund of funds (PE / VC / Private credit)</t>
+          <t>Fund of Funds</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Fund of funds (PE / VC / Private credit)</t>
+          <t>Fund of Funds</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -32298,7 +32298,7 @@
       </c>
       <c r="G4" s="26" t="inlineStr">
         <is>
-          <t>FoF (PE/VC/Private credit)</t>
+          <t>Fund of Funds</t>
         </is>
       </c>
       <c r="H4" s="26" t="inlineStr">
@@ -33475,7 +33475,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>FoF (PE/VC/Private credit)</t>
+          <t>Fund of Funds</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -2044,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="16" min="1" max="1"/>
@@ -4121,6 +4121,216 @@
       <c r="H57" t="inlineStr">
         <is>
           <t>https://english.dggf.nl/latest/news/2019/01/24/zebu-s-africa-food-security-fund-a-dggf-investee-reaches-total-fund-size-of-usd-84-million</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>added May 2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Alitheia IDF Fund</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Column H identifies NSIA, an African SWF, as a named LP/sponsor in the vehicle.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://nsia.com.ng/the-nsia-model-catalyzing-development-through-sustainable-investments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>added May 2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ingressive Capital Fund / funds</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Column H identifies NSIA, an African SWF, as a named LP/sponsor in the vehicle.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://nsia.com.ng/the-nsia-model-catalyzing-development-through-sustainable-investments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>added May 2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Verod Growth Fund II</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Column H identifies NSIA, an African SWF, as a named LP/sponsor in the vehicle.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://nsia.com.ng/the-nsia-model-catalyzing-development-through-sustainable-investments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>added May 2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Verod Growth Fund III</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Column H identifies NSIA, an African SWF, as a named LP/sponsor in the vehicle.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://nsia.com.ng/the-nsia-model-catalyzing-development-through-sustainable-investments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>added May 2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MedServe oncology and diagnostics expansion</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Column H identifies NSIA, an African SWF, as a named LP/sponsor in the vehicle.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.ifc.org/en/pressroom/2026/ifc-and-nsia-to-scale-oncology-and-diagnostic-services-for-underserved-communities</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F180"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -10341,6 +10551,198 @@
       <c r="F180" t="inlineStr">
         <is>
           <t>Wessal as SWF joint investment vehicle; EUR 2.5bn equity commitment; projects Wessal Bouregreg and Wessal Casa-Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>NSIA</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Press release / sustainability article</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>The NSIA Model: Catalyzing Development Through Sustainable Investments</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://nsia.com.ng/the-nsia-model-catalyzing-development-through-sustainable-investments/</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>NSIA investments in Alitheia IDF, Ingressive Capital and Verod Capital; MedServe impact reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>NSIA</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Impact report</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>NSIA Development Impact Report 2021</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://nsia.com.ng/download/56/2021-report/10080/nsia-development-impact-report-2021_.pdf</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Verod Growth Fund II USD 5m commitment and Verod Growth Fund III USD 7.5m commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>IFC / NSIA</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>IFC and NSIA to Scale Oncology and Diagnostic Services for Underserved Communities in Nigeria</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.ifc.org/en/pressroom/2026/ifc-and-nsia-to-scale-oncology-and-diagnostic-services-for-underserved-communities</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>MedServe expansion project size USD 154.1m; IFC USD 24.5m local-currency financing</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Alitheia IDF</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Investor profile</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Soros Economic Development Fund - Alitheia IDF Fund LP</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.soroseconomicdevelopmentfund.org/investments/alitheia-idf-fund-lp</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Alitheia IDF as USD 100m gender-lens fund and SEDF co-investor</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Ingressive Capital</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Manager profile</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ingressive Capital - About Us</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://ingressivecapital.com/about-us/</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Ingressive Capital strategy and geographic focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Verod Capital</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Manager profile</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Verod Capital - Home</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.verod.com/</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Verod Growth fund manager profile and AUM context</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10778,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -10800,7 +11201,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -11675,7 +12075,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="16">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -11683,7 +12082,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="23.25" customHeight="1" s="16">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -11792,8 +12190,6 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="16">
       <c r="A11" s="8" t="inlineStr">
         <is>
@@ -12067,8 +12463,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="16">
       <c r="A32" s="8" t="inlineStr">
         <is>
@@ -23691,7 +24085,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -25331,7 +25724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -31965,11 +32358,387 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="45.75" customHeight="1" s="16"/>
-    <row r="89" ht="34.5" customHeight="1" s="16"/>
-    <row r="90" ht="34.5" customHeight="1" s="16"/>
-    <row r="91" ht="23.25" customHeight="1" s="16"/>
-    <row r="92" ht="23.25" customHeight="1" s="16"/>
+    <row r="88" ht="45.75" customHeight="1" s="16">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Nigeria Sovereign Investment Authority (NSIA)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SWF (FGF)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Alitheia Capital / IDF Capital</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Alitheia IDF Fund</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>PE / gender-lens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2021 or earlier</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Not disclosed publicly</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NSIA sustainability disclosure</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>NSIA sustainability article Apr 2026</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>NSIA names Alitheia IDF among investments supporting women-led and women-impacting businesses. Specific NSIA ticket size not publicly disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="34.5" customHeight="1" s="16">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Nigeria Sovereign Investment Authority (NSIA)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SWF (FGF)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ingressive Capital</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ingressive Capital Fund / funds</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>VC / technology-enabled SMEs</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Africa / Nigeria-led</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2023 or earlier</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Not disclosed publicly</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NSIA sustainability disclosure</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>NSIA sustainability article Apr 2026</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>NSIA names Ingressive Capital among investments supporting women-led and women-impacting businesses. Public NSIA source does not identify a specific vintage, so retained as platform/fund exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="34.5" customHeight="1" s="16">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Nigeria Sovereign Investment Authority (NSIA)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SWF (FGF)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Verod Capital Management</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Verod Growth Fund II</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>PE / growth equity</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>West Africa / Nigeria</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>2017</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>USD 5m</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NSIA impact report</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>NSIA Development Impact Report 2021</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>NSIA impact report states the Authority invested USD 5m in Verod Growth Fund II in 2017.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="23.25" customHeight="1" s="16">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Nigeria Sovereign Investment Authority (NSIA)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SWF (FGF)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Verod Capital Management</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Verod Growth Fund III</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>PE / growth equity</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>West Africa / Nigeria</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2021 or earlier</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>USD 7.5m commitment</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NSIA impact report</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>NSIA Development Impact Report 2021</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>NSIA impact report states the Authority subsequently invested in Verod Growth Fund III, with 8% of the USD 7.5m commitment disbursed at the time of reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="23.25" customHeight="1" s="16">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Nigeria Sovereign Investment Authority (NSIA)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SWF (healthcare subsidiary)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Direct / co-investment</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>NSIA Advanced Medical Services Limited (MedServe)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>MedServe oncology and diagnostics expansion</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Direct / Healthcare</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>USD 154.1m project; IFC USD 24.5m local-currency financing</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>IFC press release</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>IFC-NSIA MedServe financing Feb 2026</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>IFC and NSIA partnered to finance MedServe, NSIA's wholly owned healthcare subsidiary, to scale diagnostic centers, cancer care facilities and cath labs across Nigerian states.</t>
+        </is>
+      </c>
+    </row>
     <row r="93" ht="124.5" customHeight="1" s="16"/>
     <row r="94" ht="124.5" customHeight="1" s="16"/>
     <row r="95" ht="79.5" customHeight="1" s="16"/>
@@ -33251,7 +34020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -33275,7 +34044,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="45.75" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -35136,11 +35904,264 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="23.25" customHeight="1" s="16"/>
-    <row r="36" ht="15" customHeight="1" s="16"/>
-    <row r="37" ht="34.5" customHeight="1" s="16"/>
-    <row r="38" ht="23.25" customHeight="1" s="16"/>
-    <row r="39" ht="34.5" customHeight="1" s="16"/>
+    <row r="35" ht="23.25" customHeight="1" s="16">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Alitheia IDF Fund</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Alitheia Capital / IDF Capital</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2021 or earlier</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PE / gender-lens</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Soros Economic Development Fund</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NSIA names Alitheia IDF as an investment; SEDF describes Alitheia IDF as a USD 100m gender-lens fund. NSIA ticket size not disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="16">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ingressive Capital Fund / funds</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ingressive Capital</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2023 or earlier</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>VC / technology-enabled SMEs</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Africa / Nigeria-led</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NSIA names Ingressive Capital as an investment; specific NSIA vehicle/vintage and ticket size not publicly disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34.5" customHeight="1" s="16">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Verod Growth Fund II</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Verod Capital Management</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PE / growth equity</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>West Africa / Nigeria</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria (USD 5m)</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NSIA impact report identifies a USD 5m FGF commitment to Verod Growth Fund II.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="23.25" customHeight="1" s="16">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Verod Growth Fund III</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Verod Capital Management</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2021 or earlier</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PE / growth equity</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>West Africa / Nigeria</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria (USD 7.5m commitment)</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NSIA impact report identifies a USD 7.5m FGF commitment to Verod Growth Fund III.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34.5" customHeight="1" s="16">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MedServe oncology and diagnostics expansion</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NSIA Advanced Medical Services Limited (MedServe)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>154.1 project size</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Direct / Healthcare</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>IFC</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>International Development Association Private Sector Window Local Currency Facility</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>IFC provided roughly NGN 14.2bn / USD 24.5m local-currency financing for NSIA's wholly owned MedServe expansion program.</t>
+        </is>
+      </c>
+    </row>
     <row r="40" ht="34.5" customHeight="1" s="16"/>
     <row r="41" ht="15" customHeight="1" s="16"/>
     <row r="42" ht="45.75" customHeight="1" s="16"/>
@@ -35181,7 +36202,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="45.75" customHeight="1" s="16">
       <c r="A3" s="24" t="inlineStr">
         <is>
@@ -36023,7 +37043,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -37698,7 +38717,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="16">
       <c r="A19" s="18" t="inlineStr">
         <is>
@@ -37714,7 +38732,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -2044,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="16" min="1" max="1"/>
@@ -4331,6 +4331,90 @@
       <c r="H62" t="inlineStr">
         <is>
           <t>https://www.ifc.org/en/pressroom/2026/ifc-and-nsia-to-scale-oncology-and-diagnostic-services-for-underserved-communities</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>added May 2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>InfraCredit</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Column H identifies NSIA, an African SWF, as sponsor/anchor investor; InfraCredit also has named Nigerian pension shareholders.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://nsia.com.ng/portfolio/infracredit/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>added May 2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Construction Finance Warehouse Facility (CFWF)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Column H identifies NSIA, an African SWF, as sponsor/anchor investor; InfraCredit also has named Nigerian pension shareholders.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://infracredit.ng/nsia-invests-ngn10-billion-into-an-innovative-construction-finance-warehouse-facility-in-collaboration-with-infracredit-to-support-bankable-greenfield-infrastructure-project-finance-in-nigeria/</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -10743,6 +10827,198 @@
       <c r="F186" t="inlineStr">
         <is>
           <t>Verod Growth fund manager profile and AUM context</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>InfraCredit</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Harvard Business School - InfraCredit and the Project Inception Facility</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.hbs.edu/faculty/Pages/item.aspx?num=66419</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>InfraCredit business model and project-inception funding context</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>InfraCredit</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>NSIA portfolio page</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>NSIA Portfolio - InfraCredit</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://nsia.com.ng/portfolio/infracredit/</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>InfraCredit as NSIA/GuarantCo participant vehicle catalysing pension and insurance investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>InfraCredit / NSIA</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>NSIA invests NGN10bn into Construction Finance Warehouse Facility with InfraCredit</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://infracredit.ng/nsia-invests-ngn10-billion-into-an-innovative-construction-finance-warehouse-facility-in-collaboration-with-infracredit-to-support-bankable-greenfield-infrastructure-project-finance-in-nigeria/</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NSIA NGN10bn anchor investment; CFWF target NGN100bn capacity; InfraCredit capitalization USD237m+</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>InfraCredit</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>KfW Development Bank invests EUR31m subordinated capital in InfraCredit</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://infracredit.ng/kfw-development-bank-invests-e31-million-surbordinated-capital-in-infracredit/</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>KfW subordinated capital and InfraCredit establishment by NSIA with GuarantCo/PIDG</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>InfraCredit</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>OECD case study</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>InfraCredit: Making infrastructure projects in Nigeria more bankable through credit enhancement</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.oecd.org/en/publications/blended-finance-case-studies_2fb90b9a-en/infracredit-making-infrastructure-projects-in-nigeria-more-bankable-through-credit-enhancement_bdb679c6-en.html</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>PIDG/NSIA establishment, GuarantCo initial contingent capital, InfraCo Africa and domestic institutional mobilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>NSIA</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Financial statements</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>NSIA 2025 Group Financial Statements - InfraCredit ownership</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://nsia.com.ng/download/267/2025-report/15287/nsia-2025-group-financial-statements-usd.pdf</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>NSIA retained InfraCredit ownership interest; Access ARM Pensions, CardinalStone, AFC and insurers as shareholders</t>
         </is>
       </c>
     </row>
@@ -25724,7 +26000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -32739,8 +33015,158 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="124.5" customHeight="1" s="16"/>
-    <row r="94" ht="124.5" customHeight="1" s="16"/>
+    <row r="93" ht="124.5" customHeight="1" s="16">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Nigeria Sovereign Investment Authority (NSIA)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SWF (NIF sub-fund)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Platform / direct strategic investment vehicle</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Infrastructure Credit Guarantee Company PLC (InfraCredit)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>InfraCredit</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Infrastructure credit enhancement / guarantees</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2016/2017</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>43.88% ownership interest retained by NSIA at FY2025; capitalization over USD 237m reported in 2023</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NSIA portfolio / financial statements</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>NSIA InfraCredit portfolio; NSIA FY2025 financial statements</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>InfraCredit is a specialised infrastructure credit enhancement facility established by NSIA with GuarantCo/PIDG. NSIA FY2025 statements report a 43.88% retained ownership interest after shareholder changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="124.5" customHeight="1" s="16">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Nigeria Sovereign Investment Authority (NSIA)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SWF (NIF sub-fund)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Direct / facility anchor</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>InfraCredit</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Construction Finance Warehouse Facility (CFWF)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Infrastructure construction finance / credit enhancement</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>NGN 10bn NSIA anchor; target NGN 100bn facility capacity</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>NGN</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>InfraCredit press release</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>InfraCredit CFWF announcement Oct 2023</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>NSIA invested NGN 10bn into a multi-funder revolving construction finance facility developed with InfraCredit to support greenfield infrastructure projects backed by InfraCredit guarantees.</t>
+        </is>
+      </c>
+    </row>
     <row r="95" ht="79.5" customHeight="1" s="16"/>
     <row r="96" ht="34.5" customHeight="1" s="16"/>
     <row r="97" ht="45.75" customHeight="1" s="16"/>
@@ -34020,7 +34446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -35946,7 +36372,6 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>Soros Economic Development Fund</t>
@@ -36000,8 +36425,6 @@
       <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>NSIA names Ingressive Capital as an investment; specific NSIA vehicle/vintage and ticket size not publicly disclosed.</t>
@@ -36048,8 +36471,6 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>NSIA impact report identifies a USD 5m FGF commitment to Verod Growth Fund II.</t>
@@ -36098,8 +36519,6 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>NSIA impact report identifies a USD 7.5m FGF commitment to Verod Growth Fund III.</t>
@@ -36162,8 +36581,112 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="34.5" customHeight="1" s="16"/>
-    <row r="41" ht="15" customHeight="1" s="16"/>
+    <row r="40" ht="34.5" customHeight="1" s="16">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>InfraCredit</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Infrastructure Credit Guarantee Company PLC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2016/2017</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>USD 237m+ capitalization reported in 2023</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Infrastructure credit enhancement / guarantees</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria; Access ARM Pensions; CardinalStone Pensions</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>GuarantCo / PIDG; KfW; AfDB; InfraCo Africa</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Africa Finance Corporation; Leadway Assurance; AIICO Insurance; FCDO / Mobilist</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NSIA established InfraCredit with GuarantCo/PIDG. Later shareholders/backers include KfW, AfDB, InfraCo Africa, AFC, insurers, and Nigerian pension shareholders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="16">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Construction Finance Warehouse Facility (CFWF)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>InfraCredit / NSIA</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NGN 10bn anchor; NGN 100bn target capacity</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Infrastructure construction finance / credit enhancement</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NSIA Nigeria</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NSIA provided NGN 10bn anchor funding; FSD Africa supported facility set-up costs through technical assistance rather than a disclosed LP/co-investment commitment.</t>
+        </is>
+      </c>
+    </row>
     <row r="42" ht="45.75" customHeight="1" s="16"/>
     <row r="43" ht="45.75" customHeight="1" s="16"/>
     <row r="44" ht="57" customHeight="1" s="16"/>
@@ -36185,7 +36708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="16" min="1" max="1"/>
@@ -36261,11 +36784,11 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Africa50 (general); Africa50 Infrastructure Acceleration Fund (IAF); Mediterrania Capital II / III / IV; Nigeria Infrastructure Fund (NIF, NSIA sub-fund); Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Africa Food Security Fund (AFSF)</t>
+          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Africa50 (general); Africa50 Infrastructure Acceleration Fund (IAF); Mediterrania Capital II / III / IV; Nigeria Infrastructure Fund (NIF, NSIA sub-fund); Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Africa Food Security Fund (AFSF); InfraCredit</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -36461,11 +36984,11 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Oyass Capital</t>
+          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Oyass Capital; InfraCredit</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -36991,6 +37514,56 @@
         </is>
       </c>
       <c r="E50" t="inlineStr">
+        <is>
+          <t>3 (Selective / TA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>GuarantCo / PIDG</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>InfraCredit</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Guarantee/catalytic capital provider that established InfraCredit with NSIA via PIDG/GuarantCo.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3 (Selective / TA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>InfraCo Africa</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>InfraCredit</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PIDG project-development arm/shareholder capital provider to InfraCredit.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>3 (Selective / TA)</t>
         </is>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -2044,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="16" min="1" max="1"/>
@@ -4415,6 +4415,46 @@
       <c r="H64" t="inlineStr">
         <is>
           <t>https://infracredit.ng/nsia-invests-ngn10-billion-into-an-innovative-construction-finance-warehouse-facility-in-collaboration-with-infracredit-to-support-bankable-greenfield-infrastructure-project-finance-in-nigeria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>42</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Oasis Africa VC Fund (OAF)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Venture Capital Trust Fund (VCTF)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>VCTF is a Ghanaian government-backed venture capital fund of funds; VCTF 2015 annual report confirms USD 2m commitment and DGGF research confirms the fund was locally domiciled to access VCTF co-investment.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://vctf.com.gh/wp-content/uploads/2022/09/Venture-Capital-Annual-report-2015.pdf; https://english.dggf.nl/site/binaries/site-content/collections/documents/2025/11/17/getting-sme-risk-capital-funds-to-first-close/dggf-knowledge-product-getting-sme-risk-capital-funds-to-first-close.pdf</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F199"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -11019,6 +11059,230 @@
       <c r="F192" t="inlineStr">
         <is>
           <t>NSIA retained InfraCredit ownership interest; Access ARM Pensions, CardinalStone, AFC and insurers as shareholders</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>VCTF Ghana / Oasis Capital</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Media / impact report coverage</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Graphic Online - Venture Capital Fund invests over GHc359m in local businesses</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.graphic.com.gh/news/general-news/ghana-news-venture-capital-fund-invests-over-ghc359m-in-local-businesses.html</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>VCTF impact report coverage; GHc359.6m invested, GHc2bn leveraged; Oasis Capital and Injaro Ghana Venture Fund identified as anchored/impactful funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Oasis Africa VC Fund</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>DFI research report</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>DGGF - Getting SME Risk Capital Funds to First Close</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://english.dggf.nl/site/binaries/site-content/collections/documents/2025/11/17/getting-sme-risk-capital-funds-to-first-close/dggf-knowledge-product-getting-sme-risk-capital-funds-to-first-close.pdf</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Oasis Africa VC Fund Ghana domicile, VCTF government co-investment rationale, DGGF legal TA and subsequent DFI crowd-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Oasis Africa VC Fund</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>DFI announcement</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>DGGF - Oasis Capital Ghana first close Oasis Africa VC Fund USD 27 million</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://english.dggf.nl/latest/news/2018/5/31/oasis-capital-ghana-first-close-oasis-africa-vc-fund-usd-27-million</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>OAF first close amount and DGGF role</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Oasis Africa VC Fund</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>GP announcement</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Oasis Capital Ghana - Oasis Africa VC Fund first close</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://oasiscapitalghana.com/v2/oasis-capital-ghana-has-completed-the-first-close-of-its-second-fund-oasis-africa-vc-fund-oaf/</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>OAF first close: USD 27m, DGGF USD 5m, IFC USD 7m and local investor base over USD 15m</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Oasis Africa VC Fund</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>DFI fund profile</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>EIB - Oasis Africa SME Fund</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.eib.org/en/products/equity/funds/oasis-africa-sme-fund</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Oasis Africa VC Fund final fund size USD 50.5m and EIB USD 8m commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>VCTF Ghana / Oasis Capital</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Allocator annual report</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Venture Capital Trust Fund - Annual Report 2015</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://vctf.com.gh/wp-content/uploads/2022/09/Venture-Capital-Annual-report-2015.pdf</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>VCTF USD 2m commitment to Oasis Africa Fund Limited and Ebankese Venture Fund portfolio context</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>VCTF Ghana</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Allocator profile</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Venture Capital Trust Fund - About Us</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://vctf.com.gh/about-us/</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>VCTF mandate as government-backed venture capital fund of funds focused on SME venture funds</t>
         </is>
       </c>
     </row>
@@ -26000,7 +26264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -33167,9 +33431,233 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="79.5" customHeight="1" s="16"/>
-    <row r="96" ht="34.5" customHeight="1" s="16"/>
-    <row r="97" ht="45.75" customHeight="1" s="16"/>
+    <row r="95" ht="79.5" customHeight="1" s="16">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Venture Capital Trust Fund (VCTF) Ghana</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Government-backed VC fund of funds</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Fund LP / Anchor</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Oasis Capital Ghana</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Oasis Africa VC Fund (OAF)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PE / SME / VC</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Ghana + Cote d'Ivoire</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2015/2016</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>USD 2m VCTF commitment; OAF first close USD 27m; final/target size ~USD 50m</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Annual report / DFI report / fund announcement</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>VCTF 2015 Annual Report; DGGF Oasis first-close announcement; DGGF catalytic-capital paper</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>VCTF 2015 annual report states VCTF made a USD 2m commitment to Oasis Africa Fund Limited, Oasis Capital Partners second fund. DGGF later described OAF as Ghana-domiciled to access VCTF government co-investment and noted the structure helped crowd in international DFIs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="34.5" customHeight="1" s="16">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Venture Capital Trust Fund (VCTF) Ghana</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Government-backed VC fund of funds</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Fund LP / Anchor</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Mirepa Investment Advisors</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mirepa Capital SME Fund I</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>PE / SME growth</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Part of GHS 120m initial close / reported USD 10.5m VCTF-led investment</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>GHS / USD</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Press / trade press</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Mirepa initial-close sources; Afrikan Heroes VCTF lead role</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>VCTF is named in the Mirepa LP group alongside Petra Trust, Axis Pensions and CAMCOL-managed pension schemes; public coverage describes VCTF as leading the investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="45.75" customHeight="1" s="16">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Venture Capital Trust Fund (VCTF) Ghana</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Government-backed VC fund of funds</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Fund LP / Anchor</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Injaro Investment Advisors</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Injaro Ghana Venture Capital Fund (IGVCF)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>PE / SME / VC</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Ghana + Cote d'Ivoire</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Part of GHS 216m final close; VCTF participation disclosed</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>GHS</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Press / impact-report coverage</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Injaro final-close sources; Graphic VCTF impact-report coverage</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>VCTF is disclosed as an LP/other named investor for IGVCF, and Graphic coverage of the VCTF impact report identifies Injaro Ghana Venture Fund as one of the impactful funds anchored by VCTF.</t>
+        </is>
+      </c>
+    </row>
     <row r="98" ht="57" customHeight="1" s="16"/>
   </sheetData>
   <autoFilter ref="A1:O98"/>
@@ -34446,7 +34934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -36209,7 +36697,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>VCTF is a Ghanaian quasi-government VC fund (not strictly a DFI)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -36267,7 +36755,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Venture Capital Trust Fund (VCTF) of Ghana</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -36679,15 +37167,70 @@
       <c r="I41" t="n">
         <v>0</v>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>NSIA provided NGN 10bn anchor funding; FSD Africa supported facility set-up costs through technical assistance rather than a disclosed LP/co-investment commitment.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="45.75" customHeight="1" s="16"/>
+    <row r="42" ht="45.75" customHeight="1" s="16">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Oasis Africa VC Fund (OAF)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Oasis Capital Ghana</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2015/2016</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PE / SME / VC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ghana + Cote d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Venture Capital Trust Fund (VCTF)</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Dutch Good Growth Fund (DGGF); IFC; EIB</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Local investor base of five institutions and individuals at first close</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>VCTF government co-investment helped Oasis domicile the fund locally in Ghana. DGGF TA/legal work helped make the Ghana structure bankable for international DFIs; first close included DGGF, IFC and local investors, with EIB later disclosing an USD 8m commitment.</t>
+        </is>
+      </c>
+    </row>
     <row r="43" ht="45.75" customHeight="1" s="16"/>
     <row r="44" ht="57" customHeight="1" s="16"/>
     <row r="45" ht="45.75" customHeight="1" s="16"/>
@@ -36834,11 +37377,11 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>Adenia Capital V; Africa50 Infrastructure Acceleration Fund (IAF); Ascent Rift Valley Fund II (ARVF II); Catalyst Fund II; Vantage Mezzanine IV (Pan-African sub-fund)</t>
+          <t>Adenia Capital V; Africa50 Infrastructure Acceleration Fund (IAF); Ascent Rift Valley Fund II (ARVF II); Catalyst Fund II; Vantage Mezzanine IV (Pan-African sub-fund); Oasis Africa VC Fund (OAF)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -36859,11 +37402,11 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Adenia Capital V; Catalyst Fund II; Mediterrania Capital II / III / IV; Vantage Mezzanine IV (Pan-African sub-fund)</t>
+          <t>Adenia Capital V; Catalyst Fund II; Mediterrania Capital II / III / IV; Vantage Mezzanine IV (Pan-African sub-fund); Oasis Africa VC Fund (OAF)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -37259,11 +37802,11 @@
         </is>
       </c>
       <c r="B24" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Africa Food Security Fund (AFSF)</t>
+          <t>Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Africa Food Security Fund (AFSF); Oasis Africa VC Fund (OAF)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -26264,7 +26264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -26359,6 +26359,21 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Asset class normalized</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Sector / thematic focus</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Investment approach</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="23.25" customHeight="1" s="16">
       <c r="A2" s="2" t="inlineStr">
@@ -26434,6 +26449,21 @@
           <t>PIC became 36th shareholder of Africa50 with USD 40m investment, signalling continental infrastructure commitment.</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="2" t="inlineStr">
@@ -26511,6 +26541,21 @@
           <t>PIC has been a recurring LP in Helios funds dating back to Helios II; specific commitment sizes not publicly disclosed.</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="16">
       <c r="A4" s="2" t="inlineStr">
@@ -26586,6 +26631,21 @@
           <t>PIC was an anchor LP at fund formation.</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="23.25" customHeight="1" s="16">
       <c r="A5" s="2" t="inlineStr">
@@ -26663,6 +26723,21 @@
           <t>PIC participated in Convergence Partners' digital infrastructure platform.</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Infrastructure; Digital / Technology</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="23.25" customHeight="1" s="16">
       <c r="A6" s="2" t="inlineStr">
@@ -26740,6 +26815,21 @@
           <t>Isibaya programme deploys to unlisted equity and infrastructure across SA and rest of Africa; PIC reports ~20% to alternatives overall.</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="16">
       <c r="A7" s="2" t="inlineStr">
@@ -26817,6 +26907,21 @@
           <t>EPPF has been investing in PE for 10+ years; ~10% to alts total, ~4% to PE; selectively includes pan-Africa funds.</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mixed / Multi-Asset</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="16">
       <c r="A8" s="2" t="inlineStr">
@@ -26892,6 +26997,21 @@
           <t>GEPF is ultimate asset owner; PIC executes.</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Infrastructure; Financial Inclusion / Financial Services</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Platform / Anchor Sponsor</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="23.25" customHeight="1" s="16">
       <c r="A9" s="2" t="inlineStr">
@@ -26967,6 +27087,21 @@
           <t>Latest committed fund LP investment; aligns with NIF sub-fund mandate.</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="23.25" customHeight="1" s="16">
       <c r="A10" s="2" t="inlineStr">
@@ -27044,6 +27179,21 @@
           <t>Federal Government injected USD 550m to scale energy infra; NIF is the direct-deal vehicle.</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" s="16">
       <c r="A11" s="2" t="inlineStr">
@@ -27121,6 +27271,21 @@
           <t>Notable NIF direct PPP equity stake.</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" s="16">
       <c r="A12" s="2" t="inlineStr">
@@ -27198,6 +27363,21 @@
           <t>NIF agribusiness anchor investment.</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" s="16">
       <c r="A13" s="2" t="inlineStr">
@@ -27275,6 +27455,21 @@
           <t>NSIA has been an LP in Nigerian-focused PE funds; sizes not disclosed.</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" s="16">
       <c r="A14" s="2" t="inlineStr">
@@ -27350,6 +27545,21 @@
           <t>Landmark first Nigerian-pension-funded infra fund.</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="34.5" customHeight="1" s="16">
       <c r="A15" s="2" t="inlineStr">
@@ -27427,6 +27637,21 @@
           <t>Largest PFA; alts are growing portion of portfolio under Multi-Fund Structure but per-fund sizes are not publicly disclosed.</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" s="16">
       <c r="A16" s="2" t="inlineStr">
@@ -27504,6 +27729,21 @@
           <t>ARM Pension and ARM-Harith are part of the same group; intra-group LP commitments are an obvious starting point.</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="23.25" customHeight="1" s="16">
       <c r="A17" s="2" t="inlineStr">
@@ -27579,6 +27819,21 @@
           <t>Co-invested via Healthcare &amp; Pharma Subfund with B Investments and El-Ezaby Pharmacy.</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Co-investment</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="23.25" customHeight="1" s="16">
       <c r="A18" s="2" t="inlineStr">
@@ -27656,6 +27911,21 @@
           <t>Strategic healthcare platform co-developed with ADQ.</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Platform / Anchor Sponsor</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.25" customHeight="1" s="16">
       <c r="A19" s="2" t="inlineStr">
@@ -27733,6 +28003,21 @@
           <t>TSFE has been the on-ground co-investment vehicle for Gulf SWF deployment into Egypt across financial services, healthcare, infra.</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Infrastructure; Financial Inclusion / Financial Services; Healthcare; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Platform / Anchor Sponsor</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23.25" customHeight="1" s="16">
       <c r="A20" s="2" t="inlineStr">
@@ -27810,6 +28095,21 @@
           <t>CDG Invest's direct-equity portfolio of Moroccan corporate stakes.</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.25" customHeight="1" s="16">
       <c r="A21" s="2" t="inlineStr">
@@ -27887,6 +28187,21 @@
           <t>CDG Invest manages CapMezzanine III, a mezzanine fund for Moroccan SMEs.</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="23.25" customHeight="1" s="16">
       <c r="A22" s="2" t="inlineStr">
@@ -27964,6 +28279,21 @@
           <t>CDG-managed infra investment vehicle.</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="23.25" customHeight="1" s="16">
       <c r="A23" s="2" t="inlineStr">
@@ -28041,6 +28371,21 @@
           <t>CDG has historically been an LP in Mediterrania PE funds focused on Maghreb mid-market.</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="23.25" customHeight="1" s="16">
       <c r="A24" s="2" t="inlineStr">
@@ -28116,6 +28461,21 @@
           <t>Joint investment with IFC and Fipar-Holding in retail/food platform.</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23.25" customHeight="1" s="16">
       <c r="A25" s="2" t="inlineStr">
@@ -28193,6 +28553,21 @@
           <t>Ithmar describes Wessal as an investment vehicle / joint venture equally owned by five SWFs, not a conventional GP-managed fund. Named projects include Wessal Bouregreg and Wessal Casa-Port.</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Infrastructure; Real Estate / Housing</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Platform / Anchor Sponsor</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23.25" customHeight="1" s="16">
       <c r="A26" s="2" t="inlineStr">
@@ -28270,6 +28645,21 @@
           <t>Newly-capitalised; intended as anchor for Moroccan sectoral funds.</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mixed / Multi-Asset</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Platform / Anchor Sponsor</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="23.25" customHeight="1" s="16">
       <c r="A27" s="2" t="inlineStr">
@@ -28347,6 +28737,21 @@
           <t>GIPF Unlisted Investment Policy mandates ~10% PE + 5% RE; 307 underlying companies.</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="16">
       <c r="A28" s="2" t="inlineStr">
@@ -28424,6 +28829,21 @@
           <t>Stimulus is a flagship Namibian unlisted manager; GIPF is an anchor LP.</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="23.25" customHeight="1" s="16">
       <c r="A29" s="2" t="inlineStr">
@@ -28501,6 +28921,21 @@
           <t>Eos manages multiple unlisted funds anchored by GIPF.</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="23.25" customHeight="1" s="16">
       <c r="A30" s="2" t="inlineStr">
@@ -28574,6 +29009,21 @@
         </is>
       </c>
       <c r="O30" s="2" t="n"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23.25" customHeight="1" s="16">
       <c r="A31" s="2" t="inlineStr">
@@ -28651,6 +29101,21 @@
           <t>Domestic housing facility — a developmental-investment direct programme.</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Infrastructure; Real Estate / Housing</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="23.25" customHeight="1" s="16">
       <c r="A32" s="2" t="inlineStr">
@@ -28726,6 +29191,21 @@
           <t>Part of BPOPF's domestic PE incubation programme.</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="23.25" customHeight="1" s="16">
       <c r="A33" s="2" t="inlineStr">
@@ -28801,6 +29281,21 @@
           <t>Part of BPOPF's incubation programme; anchor LP.</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="23.25" customHeight="1" s="16">
       <c r="A34" s="2" t="inlineStr">
@@ -28878,6 +29373,21 @@
           <t>Disclosed in industry sources; sizes not public.</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="23.25" customHeight="1" s="16">
       <c r="A35" s="2" t="inlineStr">
@@ -28955,6 +29465,21 @@
           <t>BPOPF targets ~10% in alternatives including PE, infra, RE.</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="23.25" customHeight="1" s="16">
       <c r="A36" s="2" t="inlineStr">
@@ -29030,6 +29555,21 @@
           <t>NSSF Uganda was a founding LP alongside EU and IFAD; fund now at EUR 20m total commitments. [CORRECTED in Phase 6: NSSF Uganda's actual founding ticket was EUR 2m, alongside EUR 10m from EU/IFAD, for the EUR 12m total first close. Fund subsequently grew to EUR 20m via FCA Investments + Soros Economic Development Fund.]</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="23.25" customHeight="1" s="16">
       <c r="A37" s="2" t="inlineStr">
@@ -29107,6 +29647,21 @@
           <t>NSSF Uganda discloses ~20% alts; real estate dominant historically, infra/PE growing.</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Infrastructure; Real Estate / Housing; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="23.25" customHeight="1" s="16">
       <c r="A38" s="2" t="inlineStr">
@@ -29182,6 +29737,21 @@
           <t>Reported among Catalyst II's LPs.</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="23.25" customHeight="1" s="16">
       <c r="A39" s="2" t="inlineStr">
@@ -29257,6 +29827,21 @@
           <t>Joint pan-African infra fund with Gemcorp.</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Platform / Holding Company</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Platform / Anchor Sponsor</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="23.25" customHeight="1" s="16">
       <c r="A40" s="2" t="inlineStr">
@@ -29332,6 +29917,21 @@
           <t>Multi-party rail-and-port infrastructure development.</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="23.25" customHeight="1" s="16">
       <c r="A41" s="2" t="inlineStr">
@@ -29409,6 +30009,21 @@
           <t>FSDEA portfolio includes PE funds among other asset classes; per-fund detail not publicly disclosed.</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mixed / Multi-Asset</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="23.25" customHeight="1" s="16">
       <c r="A42" s="2" t="inlineStr">
@@ -29484,6 +30099,21 @@
           <t>FONSIS and KfW/World Bank launched Oyass Capital as an SME-focused private-equity fund/financing vehicle; FONSIS says SEAF received the management mandate after an international tender.</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>SME Finance; Financial Inclusion / Financial Services</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Platform / Anchor Sponsor</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="23.25" customHeight="1" s="16">
       <c r="A43" s="2" t="inlineStr">
@@ -29561,6 +30191,21 @@
           <t>FONSIS's primary mandate is direct strategic investment in Senegalese transformational projects.</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Infrastructure; Agriculture / Food Security; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="23.25" customHeight="1" s="16">
       <c r="A44" s="2" t="inlineStr">
@@ -29638,6 +30283,21 @@
           <t>AgDF holds equity in selected Rwandan strategic companies.</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="23.25" customHeight="1" s="16">
       <c r="A45" s="2" t="inlineStr">
@@ -29715,6 +30375,21 @@
           <t>RSSB holds significant direct equity in Rwandan strategic enterprises.</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="16">
       <c r="A46" s="2" t="inlineStr">
@@ -29790,6 +30465,21 @@
           <t>34% of portfolio in alts as of 2023; 2024 strategy shift to rebalance toward fixed income announced.</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Infrastructure; Real Estate / Housing; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="23.25" customHeight="1" s="16">
       <c r="A47" s="2" t="inlineStr">
@@ -29867,6 +30557,21 @@
           <t>Significant historic direct-equity holdings in listed and unlisted Ghanaian firms.</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security; Financial Inclusion / Financial Services; Real Estate / Housing</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="23.25" customHeight="1" s="16">
       <c r="A48" s="2" t="inlineStr">
@@ -29944,6 +30649,21 @@
           <t>Domestic infrastructure direct-deal mandate.</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="23.25" customHeight="1" s="16">
       <c r="A49" s="2" t="inlineStr">
@@ -30021,6 +30741,21 @@
           <t>FGIS has built equity stakes in Gabonese banking and infrastructure.</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Infrastructure; Financial Inclusion / Financial Services; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="23.25" customHeight="1" s="16">
       <c r="A50" s="2" t="inlineStr">
@@ -30098,6 +30833,21 @@
           <t>Mandate includes strategic co-investments.</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Platform / Anchor Sponsor</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="16">
       <c r="A51" s="2" t="inlineStr">
@@ -30173,6 +30923,21 @@
           <t>First disclosed Ghanaian pension trustee commitment to SME debt under Ghana's new 5% alternative-assets rule. Co-committed alongside Norfund (USD 15m); GIP capital base raised to ~USD 70m.</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Co-investment</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="16">
       <c r="A52" s="2" t="inlineStr">
@@ -30248,6 +31013,21 @@
           <t>Ghanaian pension capital is &gt;2/3 of Ci Gaba's first-close commitments. West Africa's first domestically-domiciled private fund of funds; target size GHS 1bn / USD 91m.</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Fund of Funds</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Fund of Funds LP</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="34.5" customHeight="1" s="16">
       <c r="A53" s="2" t="inlineStr">
@@ -30323,6 +31103,21 @@
           <t>One of Ghana's largest private trustees; LP alongside AXIS, Stanbic IMS, CAL Asset Management, FSDAi, Small Foundation, FMO.</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fund of Funds</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Fund of Funds LP</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="23.25" customHeight="1" s="16">
       <c r="A54" s="2" t="inlineStr">
@@ -30398,6 +31193,21 @@
           <t>Separate from the 2025 PIC-Africa50 commitment. PIC's largest disclosed pan-African institutional equity position.</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="23.25" customHeight="1" s="16">
       <c r="A55" s="2" t="inlineStr">
@@ -30475,6 +31285,21 @@
           <t>First Indian Ocean shareholder of AFC; joined with Sierra Leone and GIIF Ghana.</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="23.25" customHeight="1" s="16">
       <c r="A56" s="2" t="inlineStr">
@@ -30552,6 +31377,21 @@
           <t>GIIF deploys its own balance sheet into AFC; aligns with GIIF's domestic-infra mandate.</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="34.5" customHeight="1" s="16">
       <c r="A57" s="2" t="inlineStr">
@@ -30629,6 +31469,21 @@
           <t>Mauritius participates via NPF and NSF jointly.</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="34.5" customHeight="1" s="16">
       <c r="A58" s="2" t="inlineStr">
@@ -30706,6 +31561,21 @@
           <t>Joint Mauritian participation alongside NPF.</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="23.25" customHeight="1" s="16">
       <c r="A59" s="2" t="inlineStr">
@@ -30783,6 +31653,21 @@
           <t>First Central African pension fund to take AFC equity. Important precedent for CIPRES-supervised funds.</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="34.5" customHeight="1" s="16">
       <c r="A60" s="2" t="inlineStr">
@@ -30860,6 +31745,21 @@
           <t>Distinct from CNSS Gabon and FGIS. NEW entity vs Phase 1 roster — should be added to Pension Funds tab.</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="23.25" customHeight="1" s="16">
       <c r="A61" s="2" t="inlineStr">
@@ -30937,6 +31837,21 @@
           <t>Ivorian sovereign equity participation.</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="23.25" customHeight="1" s="16">
       <c r="A62" s="2" t="inlineStr">
@@ -31010,6 +31925,21 @@
         </is>
       </c>
       <c r="O62" s="2" t="n"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="23.25" customHeight="1" s="16">
       <c r="A63" s="2" t="inlineStr">
@@ -31085,6 +32015,21 @@
           <t>First North African shareholder of AFC; widens TSFE-NOSI Egypt's institutional alts footprint outside the country.</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="23.25" customHeight="1" s="16">
       <c r="A64" s="2" t="inlineStr">
@@ -31160,6 +32105,21 @@
           <t>Distinct from FONSIS; Senegal's civil-service deposit institution. Africa50-IAF was named 'African first' as it was majority African-LP funded.</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="23.25" customHeight="1" s="16">
       <c r="A65" s="2" t="inlineStr">
@@ -31235,6 +32195,21 @@
           <t>Beninese deposit-and-investment institution joining Africa50-IAF.</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="23.25" customHeight="1" s="16">
       <c r="A66" s="2" t="inlineStr">
@@ -31310,6 +32285,21 @@
           <t>First disclosed CIPRES-zone pension fund LP commitment to a pan-African PE-style infrastructure fund.</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="23.25" customHeight="1" s="16">
       <c r="A67" s="2" t="inlineStr">
@@ -31385,6 +32375,21 @@
           <t>CDG Invest is the asset-management subsidiary of CDG Morocco.</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="23.25" customHeight="1" s="16">
       <c r="A68" s="2" t="inlineStr">
@@ -31460,6 +32465,21 @@
           <t>CBK Pension Fund (Central Bank of Kenya staff pension) committed alongside Norfund and IFU. CBK PF remained LP through subsequent closes.</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Financial Inclusion / Financial Services</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="23.25" customHeight="1" s="16">
       <c r="A69" s="2" t="inlineStr">
@@ -31535,6 +32555,21 @@
           <t>NAPSA is the third anchor alongside BII (USD 37.5m) and Swedfund (USD 15m); GIP Zambia plans to deploy USD 300m over 15 years to ~150 Zambian SMEs in local currency. Largest single disclosed Zambian-pension alts commitment.</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="23.25" customHeight="1" s="16">
       <c r="A70" s="2" t="inlineStr">
@@ -31610,6 +32645,21 @@
           <t>Adenia Capital V LP roster includes 'Kenyan pension funds' but no specific funds named at close-disclosure level. Likely candidates: schemes that participate via KEPFIC consortium.</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="23.25" customHeight="1" s="16">
       <c r="A71" s="2" t="inlineStr">
@@ -31685,6 +32735,21 @@
           <t>Adenia Capital V LP roster includes 'Ghanaian pension funds' but no specific trustees named at close-disclosure level.</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="23.25" customHeight="1" s="16">
       <c r="A72" s="2" t="inlineStr">
@@ -31760,6 +32825,21 @@
           <t>Specifically named as LP in Adenia V's hard-cap close; PIC commitment size not disclosed.</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="23.25" customHeight="1" s="16">
       <c r="A73" s="2" t="inlineStr">
@@ -31837,6 +32917,21 @@
           <t>Catalyst Fund II disclosed 'local pension funds and family offices' as LPs alongside CDC/BII USD 30m, EIB, IFC, Proparco, Swedfund. NSSF Uganda is known to have committed (per earlier industry reporting); other names not publicly disclosed.</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="23.25" customHeight="1" s="16">
       <c r="A74" s="2" t="inlineStr">
@@ -31914,6 +33009,21 @@
           <t>Retained as an aggregate consortium archetype only. IFC reports KEPFIC mobilized $113m into two housing projects and facilitated two member-fund investments, with a road infrastructure bond near closing. Individual KEPFIC member-only rows removed because membership alone is not allocator-to-vehicle commitment evidence.</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Infrastructure; Real Estate / Housing; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="23.25" customHeight="1" s="16">
       <c r="A75" s="2" t="inlineStr">
@@ -31989,6 +33099,21 @@
           <t>Historical first: described as 'the first pension fund in East African private equity'. ARVF I total first close USD 50m.</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="23.25" customHeight="1" s="16">
       <c r="A76" s="2" t="inlineStr">
@@ -32064,6 +33189,21 @@
           <t>Commitment made via STANLIB Kenya as fund manager. Trustee Wallace Kantai: 'first of many investments of this kind by our fund'.</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="23.25" customHeight="1" s="16">
       <c r="A77" s="2" t="inlineStr">
@@ -32141,6 +33281,21 @@
           <t>Source notes 'three pension funds (two from Kenya Power Pension Fund and one from Nation Media Group Staff Pension Fund)'. Two KPLC PF commitments likely reflect the KPLC main scheme + KPLC Staff Retirement Benefits Scheme separately.</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="34.5" customHeight="1" s="16">
       <c r="A78" s="2" t="inlineStr">
@@ -32218,6 +33373,21 @@
           <t>Re-up after ARVF I; NMG remains an LP.</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="45.75" customHeight="1" s="16">
       <c r="A79" s="2" t="inlineStr">
@@ -32293,6 +33463,21 @@
           <t>NSIA was an LP alongside AfDB, CDC Group/BII, and Dutch Good Growth Fund (DGGF) in Sahel's FAFIN. NSIA's earliest disclosed PE fund LP position alongside DFIs.</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="23.25" customHeight="1" s="16">
       <c r="A80" s="2" t="inlineStr">
@@ -32370,6 +33555,21 @@
           <t>ACA historically championed PE inclusion as allowable Nigerian pension asset class. Some PFA commitments to CAPE funds confirmed by ACA's stated 'institutional investor base, primarily pension funds and DFIs'; specific PFA names not individually disclosed.</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="34.5" customHeight="1" s="16">
       <c r="A81" s="2" t="inlineStr">
@@ -32445,6 +33645,21 @@
           <t>Three regional firsts per RSSB CEO Regis Rugemanshuro: (i) FIRST public pension-fund-led initiative focused exclusively on SME financing; (ii) FIRST permanent capital vehicle anchored by a pension fund; (iii) FIRST pension fund dedicating a TA facility in a fund. Fund target USD 100m. Enko Capital parent has USD 1.6bn AUM. FSDA structured the deal + potential guarantee facility.</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="23.25" customHeight="1" s="16">
       <c r="A82" s="2" t="inlineStr">
@@ -32522,6 +33737,21 @@
           <t>Retained as an aggregate consortium archetype only. Public sources report actual collective AOFSA member commitments; individual member-only rows removed because the public evidence does not allocate the commitments by named member fund.</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="23.25" customHeight="1" s="16">
       <c r="A83" s="2" t="inlineStr">
@@ -32597,6 +33827,21 @@
           <t>Second Ghana fund anchored solely by local investors (after Injaro IGVCF). Petra Trust named alongside Axis Pensions, VCTF, and CAMCOL schemes. Mirepa fund focuses on light manufacturing, technology, cleantech, agribusiness, healthcare, financial services.</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>SME Finance; Agriculture / Food Security; Financial Inclusion / Financial Services; Healthcare; Climate / Energy Transition; Digital / Technology</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="45.75" customHeight="1" s="16">
       <c r="A84" s="2" t="inlineStr">
@@ -32672,6 +33917,21 @@
           <t>Axis Pensions named LP alongside Petra Trust, VCTF, CAMCOL schemes. Predates Axis's later commitments to GIP Ghana (Apr 2026) and Ci-Gaba FoF (Mar 2026).</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="90.75" customHeight="1" s="16">
       <c r="A85" s="2" t="inlineStr">
@@ -32747,6 +34007,21 @@
           <t>CAL Asset Management Company Limited (CAMCOL) is one of the major Ghanaian pension asset managers. Underlying pension scheme identities not individually disclosed.</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="34.5" customHeight="1" s="16">
       <c r="A86" s="2" t="inlineStr">
@@ -32822,6 +34097,21 @@
           <t>FIRST Ghana fund of its kind anchored by local pension funds (per Injaro press release). Predates Mirepa I (2023) and Ci-Gaba (2026). Specific Ghanaian pension fund names not disclosed in public sources but precedent-setting.</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="34.5" customHeight="1" s="16">
       <c r="A87" t="inlineStr">
@@ -32897,6 +34187,21 @@
           <t>DGGF names PIC on behalf of GEPF among first-round AFSF investors alongside AfDB, CDC Group/BII, DGGF, IFU, and EBID; Kuramo later joined, bringing fund commitments to USD 84m.</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="45.75" customHeight="1" s="16">
       <c r="A88" t="inlineStr">
@@ -32974,6 +34279,21 @@
           <t>NSIA names Alitheia IDF among investments supporting women-led and women-impacting businesses. Specific NSIA ticket size not publicly disclosed.</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Infrastructure; Gender Lens</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="34.5" customHeight="1" s="16">
       <c r="A89" t="inlineStr">
@@ -33051,6 +34371,21 @@
           <t>NSIA names Ingressive Capital among investments supporting women-led and women-impacting businesses. Public NSIA source does not identify a specific vintage, so retained as platform/fund exposure.</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Infrastructure; SME Finance; Digital / Technology</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="34.5" customHeight="1" s="16">
       <c r="A90" t="inlineStr">
@@ -33126,6 +34461,21 @@
           <t>NSIA impact report states the Authority invested USD 5m in Verod Growth Fund II in 2017.</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="23.25" customHeight="1" s="16">
       <c r="A91" t="inlineStr">
@@ -33203,6 +34553,21 @@
           <t>NSIA impact report states the Authority subsequently invested in Verod Growth Fund III, with 8% of the USD 7.5m commitment disbursed at the time of reporting.</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="23.25" customHeight="1" s="16">
       <c r="A92" t="inlineStr">
@@ -33278,6 +34643,21 @@
           <t>IFC and NSIA partnered to finance MedServe, NSIA's wholly owned healthcare subsidiary, to scale diagnostic centers, cancer care facilities and cath labs across Nigerian states.</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Direct Investment</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="124.5" customHeight="1" s="16">
       <c r="A93" t="inlineStr">
@@ -33355,6 +34735,21 @@
           <t>InfraCredit is a specialised infrastructure credit enhancement facility established by NSIA with GuarantCo/PIDG. NSIA FY2025 statements report a 43.88% retained ownership interest after shareholder changes.</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Guarantee / Credit Enhancement</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Guarantee-backed Instrument</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="124.5" customHeight="1" s="16">
       <c r="A94" t="inlineStr">
@@ -33430,6 +34825,21 @@
           <t>NSIA invested NGN 10bn into a multi-funder revolving construction finance facility developed with InfraCredit to support greenfield infrastructure projects backed by InfraCredit guarantees.</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Guarantee / Credit Enhancement</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Infrastructure; Climate / Energy Transition</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Guarantee-backed Instrument</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="79.5" customHeight="1" s="16">
       <c r="A95" t="inlineStr">
@@ -33507,6 +34917,21 @@
           <t>VCTF 2015 annual report states VCTF made a USD 2m commitment to Oasis Africa Fund Limited, Oasis Capital Partners second fund. DGGF later described OAF as Ghana-domiciled to access VCTF government co-investment and noted the structure helped crowd in international DFIs.</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Infrastructure; SME Finance</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="34.5" customHeight="1" s="16">
       <c r="A96" t="inlineStr">
@@ -33582,6 +35007,21 @@
           <t>VCTF is named in the Mirepa LP group alongside Petra Trust, Axis Pensions and CAMCOL-managed pension schemes; public coverage describes VCTF as leading the investment.</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="45.75" customHeight="1" s="16">
       <c r="A97" t="inlineStr">
@@ -33655,6 +35095,21 @@
       <c r="O97" t="inlineStr">
         <is>
           <t>VCTF is disclosed as an LP/other named investor for IGVCF, and Graphic coverage of the VCTF impact report identifies Injaro Ghana Venture Fund as one of the impactful funds anchored by VCTF.</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Infrastructure; SME Finance</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
         </is>
       </c>
     </row>
@@ -33683,7 +35138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="16" min="1" max="1"/>
@@ -33785,6 +35240,21 @@
           <t>Source URL</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Asset class normalized</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Sector / thematic focus</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Investment approach</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="26" t="inlineStr">
@@ -33865,6 +35335,21 @@
           <t>https://archive.fsdafrica.org/arm-harith-and-fsd-africa-investments-announce-gbp-10m-commitment-to-unlock-nigerian-pension-funds-and-catalyse-local-capital-for-infrastructure/</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Infrastructure; Climate / Energy Transition</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="26" t="inlineStr">
@@ -33947,6 +35432,21 @@
           <t>https://www.ecofinagency.com/news-finances/2502-53253-nigerian-investment-firm-sahel-capital-launches-55-million-fund-to-narrow-farm-finance-gap</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
@@ -34023,6 +35523,21 @@
         </is>
       </c>
       <c r="P4" s="26" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Fund of Funds</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -34101,6 +35616,21 @@
         </is>
       </c>
       <c r="P5" s="26" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Infrastructure; Climate / Energy Transition</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
@@ -34183,6 +35713,21 @@
           <t>https://www.ifc.org/en/stories/2023/pooling-pensions-in-kenya</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -34265,6 +35810,21 @@
           <t>https://www.ifc.org/en/stories/2023/pooling-pensions-in-kenya</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
@@ -34347,6 +35907,21 @@
           <t>https://www.ifc.org/en/stories/2023/pooling-pensions-in-kenya</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
@@ -34429,6 +36004,21 @@
           <t>https://www.ifc.org/en/stories/2023/pooling-pensions-in-kenya</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
@@ -34511,6 +36101,21 @@
           <t>https://www.engineeringnews.co.za/article/aofsa-exceeds-infrastructure-investment-target-as-it-marks-first-anniversary-2022-11-21</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
@@ -34593,6 +36198,21 @@
           <t>https://www.engineeringnews.co.za/article/aofsa-exceeds-infrastructure-investment-target-as-it-marks-first-anniversary-2022-11-21</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
@@ -34675,6 +36295,21 @@
           <t>https://www.engineeringnews.co.za/article/aofsa-exceeds-infrastructure-investment-target-as-it-marks-first-anniversary-2022-11-21</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
@@ -34757,6 +36392,21 @@
           <t>https://www.engineeringnews.co.za/article/aofsa-exceeds-infrastructure-investment-target-as-it-marks-first-anniversary-2022-11-21</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34839,6 +36489,21 @@
           <t>https://www.ifc.org/en/stories/2023/pooling-pensions-in-kenya ; https://www.midaadvisors.com/advisory-firm-financing-the-development-of-critical-infrastructure-in-kenya-with-local-institutional-capital</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34919,6 +36584,21 @@
       <c r="P15" t="inlineStr">
         <is>
           <t>https://www.engineeringnews.co.za/article/aofsa-exceeds-infrastructure-investment-target-as-it-marks-first-anniversary-2022-11-21 ; https://www.midaadvisors.com/advisory-firm-what-we-do/institutional-investors-capacity-development</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Infrastructure; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Mandate / Pipeline Only</t>
         </is>
       </c>
     </row>
@@ -34934,7 +36614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -35019,6 +36699,21 @@
           <t>Co-investor pattern note</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Asset class normalized</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Sector / thematic focus</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Investment approach</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="34.5" customHeight="1" s="16">
       <c r="A4" s="2" t="inlineStr">
@@ -35077,6 +36772,21 @@
           <t>BII-anchored DFI + 1 Ghanaian pension trustee. First Ghanaian PF commitment under 5% alts rule.</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="23.25" customHeight="1" s="16">
       <c r="A5" s="2" t="inlineStr">
@@ -35133,6 +36843,21 @@
           <t>Largest single disclosed Zambian-pension alts commitment. Trilateral DFI+pension anchor model.</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="23.25" customHeight="1" s="16">
       <c r="A6" s="2" t="inlineStr">
@@ -35193,6 +36918,21 @@
           <t>West Africa's first domestically-domiciled private FoF. Ghanaian pensions &gt;2/3 of first close.</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Fund of Funds</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Fund of Funds LP</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="16">
       <c r="A7" s="2" t="inlineStr">
@@ -35253,6 +36993,21 @@
           <t>Landmark first-Nigerian-pension-funded infra fund.</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="34.5" customHeight="1" s="16">
       <c r="A8" s="2" t="inlineStr">
@@ -35311,6 +37066,21 @@
           <t>FONSIS source describes Oyass Capital as an SME-focused private-equity fund/financing vehicle set up with KfW/World Bank support; management mandate awarded to SEAF.</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Infrastructure; SME Finance; Financial Inclusion / Financial Services</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="23.25" customHeight="1" s="16">
       <c r="A9" s="2" t="inlineStr">
@@ -35369,6 +37139,21 @@
           <t>NSSF Uganda founding LP alongside EU + IFAD. [Phase 6 correction: NSSF Uganda's founding contribution was EUR 2m (not EUR 12m); EUR 12m was the TOTAL first close including EU/IFAD EUR 10m. Later EUR 8m added by Soros Economic Development Fund + FCA Investments brought total to EUR 20m.]</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="34.5" customHeight="1" s="16">
       <c r="A10" s="2" t="inlineStr">
@@ -35425,6 +37210,21 @@
           <t>Historical pioneer fund for East African pension PE participation.</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" s="16">
       <c r="A11" s="2" t="inlineStr">
@@ -35485,6 +37285,21 @@
           <t>Strong DFI cluster alongside re-up of East African pension LPs. Source narrative: ARVF was 'the only local PE fund continually unlocking local pension investment' as of 2015.</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="34.5" customHeight="1" s="16">
       <c r="A12" s="2" t="inlineStr">
@@ -35541,6 +37356,21 @@
           <t>~30 LPs total; &gt;60% historical DFI re-ups; categorical 'Kenyan + Ghanaian pension funds' mentioned in press release but not individually named. [Phase 6 update: comprehensive LP list confirmed via EIB disclosure. 10 DFIs + PIC SA + categorical Kenyan/Ghanaian PFs + family offices = ~30 LP entities total.]</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="34.5" customHeight="1" s="16">
       <c r="A13" s="2" t="inlineStr">
@@ -35597,6 +37427,21 @@
           <t>Single largest East African PE fund with disclosed local-pension cohort.</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" s="16">
       <c r="A14" s="2" t="inlineStr">
@@ -35657,6 +37502,21 @@
           <t>PIC has been recurring LP since Helios II; sizes not publicly disclosed.</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" s="16">
       <c r="A15" s="2" t="inlineStr">
@@ -35715,6 +37575,21 @@
           <t>Vantage's 'historical pattern' of substantial SA pension LP base; specific names not publicly itemised.</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" s="16">
       <c r="A16" s="2" t="inlineStr">
@@ -35775,6 +37650,21 @@
           <t>Maghreb-focused; CDG Morocco historical LP.</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="34.5" customHeight="1" s="16">
       <c r="A17" s="2" t="inlineStr">
@@ -35833,6 +37723,21 @@
           <t>Evergreen platform; CBK Pension Fund Kenya was first African pension LP in 2018; multiple closes since.</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Platform / Holding Company</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Financial Inclusion / Financial Services; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="16">
       <c r="A18" s="2" t="inlineStr">
@@ -35889,6 +37794,21 @@
           <t>BPOPF domestic incubation programme — single-LP-anchor model.</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.25" customHeight="1" s="16">
       <c r="A19" s="2" t="inlineStr">
@@ -35945,6 +37865,21 @@
           <t>Sister vehicle to Aleyo; BPOPF anchor.</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23.25" customHeight="1" s="16">
       <c r="A20" s="2" t="inlineStr">
@@ -36005,6 +37940,21 @@
           <t>Continental infrastructure platform. PIC's 2025 commitment is largest single PF equity shareholding.</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.25" customHeight="1" s="16">
       <c r="A21" s="2" t="inlineStr">
@@ -36063,6 +38013,21 @@
           <t>First major pan-African infra fund MAJORITY-funded by African institutions. Africa50's flagship LP-style vehicle.</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="23.25" customHeight="1" s="16">
       <c r="A22" s="2" t="inlineStr">
@@ -36125,6 +38090,21 @@
           <t>Continental institutional-equity vehicle. By count of institutions, AFC participation is the MOST COMMON form of cross-border African pension/SWF alts deployment.</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="16">
       <c r="A23" s="2" t="inlineStr">
@@ -36183,6 +38163,21 @@
           <t>PIC anchor; significant African-LP-funded infra fund.</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="23.25" customHeight="1" s="16">
       <c r="A24" s="2" t="inlineStr">
@@ -36243,6 +38238,21 @@
           <t>Digital infrastructure; PIC participant.</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Infrastructure; Digital / Technology</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="34.5" customHeight="1" s="16">
       <c r="A25" s="2" t="inlineStr">
@@ -36301,6 +38311,21 @@
           <t>Ithmar describes Wessal as a joint investment vehicle, equally owned by five SWFs. Specific launched projects: Wessal Bouregreg and Wessal Casa-Port.</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Infrastructure; Real Estate / Housing</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23.25" customHeight="1" s="16">
       <c r="A26" s="2" t="inlineStr">
@@ -36357,6 +38382,21 @@
           <t>Capitalised Moroccan strategic SWF — anchor for sub-funds.</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Mixed / Multi-Asset</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Multi-Sector</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="16">
       <c r="A27" s="2" t="inlineStr">
@@ -36417,6 +38457,21 @@
           <t>NIF is NSIA's direct-deal sub-fund; received USD 550m additional govt funding FY24.</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Infrastructure; Agriculture / Food Security; Healthcare</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="23.25" customHeight="1" s="16">
       <c r="A28" s="2" t="inlineStr">
@@ -36475,6 +38530,21 @@
           <t>Bilateral SWF healthcare platform.</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Platform / Anchor Sponsor</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="45.75" customHeight="1" s="16">
       <c r="A29" s="2" t="inlineStr">
@@ -36529,6 +38599,21 @@
           <t>NSIA's earliest disclosed PE fund LP position; alongside three DFIs.</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="90.75" customHeight="1" s="16">
       <c r="A30" s="2" t="inlineStr">
@@ -36591,6 +38676,21 @@
           <t>First Nigerian PE firm (founded 1997); CAPE I was Nigeria's first PE fund (1998). Continental pioneer of pension-PE inclusion.</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23.25" customHeight="1" s="16">
       <c r="A31" s="2" t="inlineStr">
@@ -36647,6 +38747,21 @@
           <t>First permanent capital vehicle anchored by an African pension fund (per RSSB CEO). Three regional firsts: pension-fund-led SME-only mandate, anchor permanent-capital vehicle, pension-fund TA facility.</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="23.25" customHeight="1" s="16">
       <c r="A32" s="2" t="inlineStr">
@@ -36705,6 +38820,21 @@
           <t>Second Ghana fund anchored solely by local investors (after Injaro IGVCF). 100% local-LP-funded. Confirms Ghana's emerging mandated-minimum-alts policy is producing real deal flow.</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="23.25" customHeight="1" s="16">
       <c r="A33" s="2" t="inlineStr">
@@ -36763,6 +38893,21 @@
           <t>FIRST Ghana fund of its kind anchored by local pension funds. Historical precedent for Mirepa I, Ci-Gaba, GIP Ghana model. Ghana cedi-denominated.</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="23.25" customHeight="1" s="16">
       <c r="A34" t="inlineStr">
@@ -36817,6 +38962,21 @@
           <t>DGGF news release names PIC/GEPF in first-round investor group alongside DFIs and DGGF; Kuramo subsequently joined to bring commitments to USD 84m.</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="23.25" customHeight="1" s="16">
       <c r="A35" t="inlineStr">
@@ -36870,6 +39030,21 @@
           <t>NSIA names Alitheia IDF as an investment; SEDF describes Alitheia IDF as a USD 100m gender-lens fund. NSIA ticket size not disclosed.</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Gender Lens</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="16">
       <c r="A36" t="inlineStr">
@@ -36918,6 +39093,21 @@
           <t>NSIA names Ingressive Capital as an investment; specific NSIA vehicle/vintage and ticket size not publicly disclosed.</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SME Finance; Digital / Technology</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="34.5" customHeight="1" s="16">
       <c r="A37" t="inlineStr">
@@ -36964,6 +39154,21 @@
           <t>NSIA impact report identifies a USD 5m FGF commitment to Verod Growth Fund II.</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="23.25" customHeight="1" s="16">
       <c r="A38" t="inlineStr">
@@ -37012,6 +39217,21 @@
           <t>NSIA impact report identifies a USD 7.5m FGF commitment to Verod Growth Fund III.</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="34.5" customHeight="1" s="16">
       <c r="A39" t="inlineStr">
@@ -37068,6 +39288,21 @@
           <t>IFC provided roughly NGN 14.2bn / USD 24.5m local-currency financing for NSIA's wholly owned MedServe expansion program.</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Direct Equity / Strategic Stake</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="34.5" customHeight="1" s="16">
       <c r="A40" t="inlineStr">
@@ -37126,6 +39361,21 @@
           <t>NSIA established InfraCredit with GuarantCo/PIDG. Later shareholders/backers include KfW, AfDB, InfraCo Africa, AFC, insurers, and Nigerian pension shareholders.</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Guarantee / Credit Enhancement</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Guarantee-backed Instrument</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="16">
       <c r="A41" t="inlineStr">
@@ -37172,6 +39422,21 @@
           <t>NSIA provided NGN 10bn anchor funding; FSD Africa supported facility set-up costs through technical assistance rather than a disclosed LP/co-investment commitment.</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Guarantee / Credit Enhancement</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Infrastructure; Digital / Technology</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Guarantee-backed Instrument</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="45.75" customHeight="1" s="16">
       <c r="A42" t="inlineStr">
@@ -37228,6 +39493,21 @@
       <c r="L42" t="inlineStr">
         <is>
           <t>VCTF government co-investment helped Oasis domicile the fund locally in Ghana. DGGF TA/legal work helped make the Ghana structure bankable for international DFIs; first close included DGGF, IFC and local investors, with EIB later disclosing an USD 8m commitment.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>SME Finance; Financial Inclusion / Financial Services</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
         </is>
       </c>
     </row>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -4908,7 +4908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F199"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -11283,6 +11283,38 @@
       <c r="F199" t="inlineStr">
         <is>
           <t>VCTF mandate as government-backed venture capital fund of funds focused on SME venture funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>RSSB Rwanda</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Fund launch / press release</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Kigali International Financial Centre establishes a $250M pan-African Virunga Africa Fund I</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.rssb.rw/fileadmin/user_upload/Kigali_International_Financial_Centre.pdf</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Virunga Africa Fund I launch; QIA and RSSB named as anchor/cornerstone investors; Admaius manager; USD 250m fund size and pan-African sector focus</t>
         </is>
       </c>
     </row>
@@ -26264,7 +26296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -35113,7 +35145,96 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="57" customHeight="1" s="16"/>
+    <row r="98" ht="57" customHeight="1" s="16">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Rwanda Social Security Board (RSSB)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Fund LP / Anchor</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Admaius Capital Partners</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Virunga Africa Fund I</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Private equity / growth / multi-sector</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Not separately disclosed (fund size USD 250m)</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>KIFC/RSSB press release / PDF</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>KIFC/RSSB - Virunga Africa Fund I launch (2 Nov 2021)</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>KIFC/RSSB PDF names QIA and RSSB as anchor/cornerstone investors. Fund managed by Admaius, headquartered in Kigali and domiciled in KIFC; targets healthcare, education, digital infrastructure, financial services, and wider economic transformation across Africa.</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Healthcare; Education; Digital / Technology; Financial Inclusion / Financial Services; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O98"/>
   <conditionalFormatting sqref="N2:N98">
@@ -36614,7 +36735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -39511,7 +39632,75 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="45.75" customHeight="1" s="16"/>
+    <row r="43" ht="45.75" customHeight="1" s="16">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Virunga Africa Fund I</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Admaius Capital Partners</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D43" t="n">
+        <v>250</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Private equity / growth / multi-sector</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>RSSB (Rwanda Social Security Board) - anchor investor (commitment amount not separately disclosed)</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Qatar Investment Authority (QIA)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>KIFC/RSSB launch announcement names QIA and RSSB as the two anchor/cornerstone investors in the USD 250m pan-African fund. Managed by Admaius and domiciled in KIFC.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Healthcare; Education; Digital / Technology; Financial Inclusion / Financial Services; Multi-Sector</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
     <row r="44" ht="57" customHeight="1" s="16"/>
     <row r="45" ht="45.75" customHeight="1" s="16"/>
     <row r="46" ht="45.75" customHeight="1" s="16"/>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -9,31 +9,33 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sovereign Wealth Funds" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pension Funds" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Candidates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commitments Database" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline &amp; Mandates" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funds &amp; LP Co-Investors" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DFI Co-Investor Patterns" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country Summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology &amp; Caveats" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inclusion Audit" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omission Candidates" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Library" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absentees Investigation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regulatory vs Behaviour" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVCA Aggregate vs Disclosed" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Disclosure Sweep" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commitments Database" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline &amp; Mandates" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funds &amp; LP Co-Investors" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DFI Co-Investor Patterns" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology &amp; Caveats" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inclusion Audit" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omission Candidates" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Library" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absentees Investigation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regulatory vs Behaviour" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVCA Aggregate vs Disclosed" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sovereign Wealth Funds'!$A$1:$K$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pension Funds'!$A$1:$K$230</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tier 1 Candidates'!$A$3:$G$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Commitments Database'!$A$1:$O$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pipeline &amp; Mandates'!$A$1:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Funds &amp; LP Co-Investors'!$A$1:$L$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DFI Co-Investor Patterns'!$A$3:$E$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Inclusion Audit'!$A$1:$H$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Source Library'!$A$1:$F$178</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Absentees Investigation'!$A$3:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Regulatory vs Behaviour'!$A$3:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tier 1 Disclosure Sweep'!$A$1:$V$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Commitments Database'!$A$1:$O$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Pipeline &amp; Mandates'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Funds &amp; LP Co-Investors'!$A$1:$L$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DFI Co-Investor Patterns'!$A$3:$E$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Inclusion Audit'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Source Library'!$A$1:$F$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Absentees Investigation'!$A$3:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Regulatory vs Behaviour'!$A$3:$H$22</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -104,7 +106,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -136,6 +138,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001A3A5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B183"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -204,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -273,6 +295,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2044,6 +2078,214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" style="16" min="1" max="1"/>
+    <col width="110" customWidth="1" style="16" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21.75" customHeight="1" s="16">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Methodology, sources, and important caveats</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="16">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="17" t="n"/>
+    </row>
+    <row r="3" ht="34.5" customHeight="1" s="16">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>All 54 African countries. Allocator universe: sovereign wealth funds (any mandate type) plus pension funds of any kind (public, private, multi-employer, umbrella). Real estate is excluded per scoping; alts of interest are PE/VC, private credit &amp; infrastructure, and direct/co-investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="16">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="17" t="n"/>
+    </row>
+    <row r="5" ht="34.5" customHeight="1" s="16">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>AUM figures</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>All AUM values are USD-converted approximations and should be treated as order-of-magnitude only. Currency basis (local) and as-of year are noted. Where the institution reports in a local currency, the USD value will move with FX as much as with portfolio performance. Confidence flags reflect source quality, not portfolio performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="16">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="34.5" customHeight="1" s="16">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Confidence flags</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>H = High: AUM published in audited annual report or regulator return within last 18 months. M = Medium: AUM from secondary databases, trade press, or older primary disclosure. L = Low: AUM is estimated, dated, or based on indirect inference (e.g., regulatory share of contributions). Low-confidence rows MUST be verified before academic publication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="16">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="57" customHeight="1" s="16">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Universe completeness</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Sovereign wealth funds: substantively complete (Africa has ~22 operational SWFs plus several proposed/planned). Pension funds: covers the largest scheme(s) per country plus the full PFA universe for Nigeria and the major schemes for South Africa, Morocco, and Kenya. Smaller occupational schemes (especially South Africa's ~1,400 registered schemes, Kenya's ~1,300, and Mauritius's standalone corporate schemes) are NOT individually listed — most are too small to make alts commitments. Aggregate AUM for these unlisted schemes is material in SA and Kenya and should be referenced via FSCA and RBA aggregate reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="16">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="57" customHeight="1" s="16">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Source priorities for verification</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Phase-2 verification should pull, in this order: (1) audited annual reports from each institution's website; (2) regulator returns (FSCA Reg 28, PenCom Q-reports, RBA industry reports, NPRA Ghana, CIPRES bulletins, ACAPS Morocco); (3) SWF databases (SWFI, Global SWF, IFSWF); (4) AVCA/SAVCA/EAVCA LP surveys; (5) trade press (African Private Equity News, Africa Capital Digest, *DealStreetAfrica*). Where access is available: Preqin and PitchBook LP profiles. Document the source URL + access date for each AUM figure before publication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="16">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="17" t="n"/>
+    </row>
+    <row r="13" ht="68.25" customHeight="1" s="16">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Known limitations</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>1) Several Francophone CIPRES funds and most North African public PFs do not publish portfolio-detail in English; verify via local-language sources. 2) Ethiopian Investment Holdings AUM is the book value of SOE stakes, not investable capital — apples-to-oranges with cash-funded SWFs. 3) South African umbrella DC funds (Sanlam Umbrella, Old Mutual SuperFund, Alexforbes) are intermediaries — alts commitments flow through underlying portfolio managers, not from the umbrella entity directly. 4) Several proposed SWFs (Kenya, Tanzania) and dormant SWFs (Zimbabwe SWFZ) are included for completeness but have no investable capital. 5) Libya's LIA is mostly under UN sanctions; pre-2011 alts holdings are partially documented but unlikely to be acted on currently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="16">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="17" t="n"/>
+    </row>
+    <row r="15" ht="57" customHeight="1" s="16">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Look-through note (CRITICAL)</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Many of the largest African pension pools (notably GEPF in South Africa and the Moroccan parastatal schemes managed by CDG) deploy alts via intermediary asset managers. When attributing alts commitments to allocators, the methodology choice is: (a) attribute to ultimate asset owner (e.g., 'GEPF committed via PIC to Helios IV'), or (b) attribute to the intermediary manager. Default rule for this research is (a) — ultimate asset owner — with the intermediary documented in the same row. This avoids double-counting and is more useful for the academic question of which institutions are deploying capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="17" t="n"/>
+    </row>
+    <row r="17" ht="45.75" customHeight="1" s="16">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Next phase</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Phase 2 (evidence layer) takes this roster, drops below USD 500m, and pursues for each remaining institution: (i) most recent annual report; (ii) regulator filing for the most recent reporting period; (iii) news search for LP mentions in African PE/infra fund closes over the past 7 years; (iv) GP-side disclosure: for each of the ~30 most active African-focused GPs, harvest every disclosed LP mention since 2018.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="16">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Commitments Database scope (clarified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="199.5" customHeight="1" s="16">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>The Commitments Database contains ONLY African pension fund and sovereign wealth fund allocator-to-fund-or-deal commitments. It also includes adjacent entities that are functionally allocator-like and integral to the SWF/pension narrative: (i) sovereign governments making direct AFC equity investments (Côte d'Ivoire, Sierra Leone, Egypt) — functionally similar to SWF deployment; (ii) the KEPFIC pension-fund consortium; (iii) categorical 'multiple Nigerian PFAs' / 'Kenyan pension funds' / 'Ghanaian pension funds' cohort entries where the source explicitly identifies pension fund participation but doesn't name individual schemes. 
+DFI catalytic capital providers (FSDAi, Soros Economic Development Fund, FCA Investments, etc.), asset managers acting as intermediaries (Old Mutual IG, Ninety One, Stanbic IMS Ghana, CAL Asset Management Ghana), and commercial banks (Rawbank, Attijariwafa, NIB Egypt) are NOT in the Commitments Database — they appear in the 'Funds &amp; LP Co-Investors' tab as fund-level co-LPs, and in the 'DFI Co-Investor Patterns' tab for frequency analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14 inclusion audit</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Rows now require evidence of actual African PF/SWF participation for the fund/vehicle. DFI-only, planned, expected, targeted, generic LP-base, and MoU-only rows were removed from the fund and commitment fact tables. KEPFIC and AOFSA are retained only as aggregate pooled-mandate archetypes because public sources evidence actual member-fund investments/commitments; individual member-only rows were removed from the Commitments Database. See Inclusion Audit tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Pipeline &amp; Mandates category</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Targeted/expected/planned rows are separated into the Pipeline &amp; Mandates tab and excluded from the Commitments Database until actual allocator-to-vehicle commitments are publicly evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DFI canonicalization</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DFI nomenclature is canonicalized for the web app network graph: each DFI has one node even when source text uses variants such as BII/CDC, CDC Group/BII, EIB Global, Findev Canada, FSDAi, or Proparco/FISEA.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4464,13 +4706,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="16" min="1" max="1"/>
@@ -4897,18 +5139,652 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Pipeline - monitor for first close / RSSB confirmation</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Virunga Africa Fund II</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Admaius Capital Partners</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>RSSB anchored predecessor Fund I; local press frames Fund II as following RSSB-anchored Fund I, but no confirmed RSSB Fund II commitment found as of 5 June 2026.</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>IFC proposed USD 25m equity investment plus up to USD 10m co-investment envelope; board date expected 10 June 2026.</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Growth equity / private equity</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>Egypt, Kenya, Morocco, Rwanda, South Africa / Africa</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>USD 500m target; proposed IFC commitment only.</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>M-H</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>Keep in Pipeline &amp; Mandates; do not count in confirmed commitments until first close or official RSSB commitment evidence is public.</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>IFC disclosure and local/trade coverage show Fund II is proposed/raising and follows the RSSB/QIA-anchored Fund I; no official RSSB Fund II commitment evidence located in this audit.</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>https://www.newtimes.co.rw/article/36220/news/featured/world-banks-ifc-to-back-admaius-500-million-virunga-africa-fund-ii</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>https://www.africaprivateequitynews.com/p/ifc-discloses-proposed-25m-investment</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>KIFC/RSSB financial-centre sweep 2026-06-05</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Reviewed - out of scope unless PF/SWF LP evidence emerges</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>FEDA fund / Afreximbank KIFC-domiciled fund</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Afreximbank / FEDA</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>None found in KIFC/RSSB audit; KIFC article lists FEDA as domiciled capital, not RSSB or African pension/SWF-backed LP evidence.</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Afreximbank/FEDA institutional platform.</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Trade / export development fund</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>KIFC article cites USD 350m domiciliation as part of USD 600m attracted to KIFC.</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>Exclude from confirmed commitments and funds unless a named African PF/SWF allocator commitment is found.</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>This explains a likely false-positive KIFC search result: KIFC-domiciled fund, but no named African PF/SWF LP evidence.</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>https://kifc.rw/how-kigali-international-financial-centre-aims-to-fast-track-rwanda-as-a-preferred-financial-centre-for-investments-in-africa/</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>KIFC/RSSB financial-centre sweep 2026-06-05</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Reviewed - out of scope unless PF/SWF LP evidence emerges</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Dakar Network of Angel Investors (DNA) Angel Investment SPV</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Dakar Network of Angel Investors / KIFC SPV</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>None found; KIFC article describes a regional angel-investor SPV registered in Kigali, not an African PF/SWF allocation.</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Angel investor network / SPV evidence only.</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>Angel / venture SPV</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>Regional Africa</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>KIFC article cites USD 10m SPV.</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>Exclude from confirmed commitments; only revisit if a pension fund or SWF LP is publicly named.</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>Useful negative-control result from KIFC domiciliation searches; not every KIFC vehicle is in scope for the dashboard.</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>https://kifc.rw/how-kigali-international-financial-centre-aims-to-fast-track-rwanda-as-a-preferred-financial-centre-for-investments-in-africa/</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="inlineStr"/>
+      <c r="O8" s="21" t="inlineStr">
+        <is>
+          <t>KIFC/RSSB financial-centre sweep 2026-06-05</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Candidate - scope decision needed</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Akobo Minerals AB private placement / Segele gold project stake</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>Akobo Minerals AB / Ethiopian Investment Holdings</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Ethiopian Investment Holdings subscribed USD 3m for 15m new shares, resulting in a 7.4% stake.</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>N/A - direct issuer private placement / listed-company equity context.</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Direct equity / mining</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>Ethiopia / international listed issuer</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>USD 3m private placement; 7.4% ownership stake.</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>Decide whether listed-company private placement by an African SWF into an Ethiopia-linked mining company belongs in Commitments Database or remains out of PE/infra fund scope.</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>Issuer and multiple local sources report EIH first international investment in Akobo Minerals; this is public direct-equity evidence but not a fund LP commitment.</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="inlineStr">
+        <is>
+          <t>https://news.cision.com/akobo-minerals-ab/r/akobo-minerals-secures-ethiopian-sovereign-fund-s-first-international-investment,c4216389</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>https://www.stockmarket.et/ethiopian-investment-holdings-invests-usd-3-million-for-7-4-stake-in-akobo-minerals/</t>
+        </is>
+      </c>
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>Tier 1 disclosure sweep - EIH 2026-06-05</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Candidate - research vehicle identity / likely pipeline only</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>CMR OPCI real-estate vehicles</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>Multiple OPCI management companies</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>Local French-language coverage says three OPCI approvals were issued for CMR as part of diversification.</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>Real estate / OPCI</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>Vehicle names and commitment sizes not resolved in initial sweep.</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>Research AMMC OPCI register and CMR reports for named vehicles; likely exclude unless real-estate vehicles are brought into dashboard scope.</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>CMR appears to have diversified into OPCI real-estate vehicles, but no named allocator-to-fund commitment row is yet available.</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>https://leseco.ma/business/retraite-la-cmr-diversifie-ses-placements.html</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>https://www.ammc.ma/</t>
+        </is>
+      </c>
+      <c r="O10" s="21" t="inlineStr">
+        <is>
+          <t>Tier 1 disclosure sweep - CMR 2026-06-05</t>
+        </is>
+      </c>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Pipeline / mandate evidence - research underlying vehicles</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>RCAR unlisted-participation and real-estate management mandates</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>CDG Invest; Ewane Assets; CDG Capital</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>RCAR 2023 activity report says portfolio management framework included mandates with CDG Invest for unlisted participations and Ewane Assets for real estate.</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>Unlisted participations / real estate / financial assets</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>Mandate evidence only; no named investment vehicle or ticket size found in initial sweep.</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>M-H</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>Keep out of Commitments Database until underlying vehicle/deal commitments are named; use as lead for CDG Invest/RCAR public-document review.</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>Official RCAR report supports an unlisted-participation mandate but not a specific allocator-to-vehicle commitment.</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>https://www.rcar.ma/uploads/rapport_dactivites/RA%20CNRA%20RCAR%202023%20VFr.pdf</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>https://medias24.com/2024/05/15/retraites-la-cdg-dresse-le-bilan-de-la-cnra-et-du-rcac-au-titre-de-lannee-2023/</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>Tier 1 disclosure sweep - RCAR 2026-06-05</t>
+        </is>
+      </c>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Candidate - likely add after amount/source detail check</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Ninety One Credit Fund - African Credit Opportunities Fund III</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Ninety One</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>GEPF 2024/25 annual report says an allocation to the fund was approved during the financial year inside the Pan-African private markets/Isibaya portfolio.</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Not yet checked in this sweep.</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>Private credit / African credit opportunities</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>Pan-Africa / Africa</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>GEPF annual report confirms approved allocation; commitment amount not yet isolated.</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>Research Ninety One/DFI fund-close disclosures and GEPF note 3.1 for commitment amount; likely add to Commitments Database if allocator-to-fund allocation is sufficiently specific.</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>Official GEPF report names a specific African private credit fund allocation approved in FY2024/25.</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>https://gepf.co.za/wp-content/uploads/2025/11/GEPF_AR_2025_digital.pdf</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>https://www.pic.gov.za/DocAnnualReports1/PIC%20Integrated%20Annual%20Report%202024.pdf</t>
+        </is>
+      </c>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>Tier 1 disclosure sweep - GEPF/PIC 2026-06-05</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Candidate - research vehicle identity / likely real-estate scope decision</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>CNSS OPCI state-asset acquisition vehicle</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>CNSS / OPCI manager TBC</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Local coverage says CNSS created an OPCI in 2024 dedicated to acquiring state assets under Morocco innovative-financing transactions.</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>Real estate / OPCI / state asset sale-leaseback</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>Part of 2024 state asset sale proceeds; CNSS vehicle size not isolated in initial sweep.</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>Search AMMC OPCI register and state-domain annual report for vehicle name and transaction size; likely exclude unless real estate/OPCI vehicles are in scope.</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>CNSS joined CDG/CMR as institutional investor in dedicated OPCI structure for state asset acquisitions, but named vehicle details are unresolved.</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>https://medias24.com/2025/07/15/financements-innovants-35-mmdh-en-2024/</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>https://www.ammc.ma/</t>
+        </is>
+      </c>
+      <c r="O13" s="21" t="inlineStr">
+        <is>
+          <t>Tier 1 disclosure sweep - CNSS Morocco 2026-06-05</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F200"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -11318,6 +12194,1094 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>RSSB Rwanda / Admaius Capital Partners</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Trade press</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>AllAfrica — World Bank's IFC to Back Admaius' $500M Virunga Africa Fund II (3 June 2026)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://allafrica.com/stories/202606030282.html</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Virunga Africa Fund II pipeline/watchlist evidence; IFC proposed USD 25m + USD 10m co-invest; fund target USD 500m; predecessor Fund I was RSSB/QIA-anchored, but no confirmed RSSB Fund II commitment as of 5 June 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>RSSB Rwanda / Admaius Capital Partners</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Trade press</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>TechInAfrica — Admaius Capital Partners Launches $500M Virunga Africa Fund II (May 2026)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.techinafrica.com/admaius-capital-partners-launches-500m-virunga-africa-fund-ii/</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Virunga Africa Fund II pipeline/watchlist details; target size, focus markets, sectors, and proposed IFC investment; not confirmation of RSSB commitment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>RSSB Rwanda / Admaius Capital Partners</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Trade press</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Africa Private Equity News — IFC discloses proposed USD 25m investment in Admaius' Virunga Africa Fund II (May 2026)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.africaprivateequitynews.com/p/ifc-discloses-proposed-25m-investment</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>IFC proposed USD 25m + USD 10m co-invest in Fund II; predecessor Fund I closed USD 280m in 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SSNIT Ghana / Multiple GPs</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Academic/DFI study</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>World Bank -- Ghana Private Equity and Venture Capital Ecosystem Study (June 2016)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://openknowledge.worldbank.org/server/api/core/bitstreams/d98e4fd6-3bf4-5258-b0a4-7f44b9a594b1/content</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Names SSNIT as LP in four PE funds: Fidelity Equity Fund II, ECP Africa Fund III, PAIDF, CIFA (USD 5.04m, June 2005)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SSNIT Ghana / Actis / Cordiant</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Government project database</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Canada.ca Project Browser -- Canada Investment Fund for Africa (CIFA)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://w05.international.gc.ca/projectbrowser-banqueprojets/project-projet/details/a032944001</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>CIFA fund details; USD 212m fund; Government of Canada anchor; SSNIT confirmed LP with USD 5.04m June 2005 commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SSNIT Ghana / Fidelity Capital Partners</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DFI portfolio listing</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SIFEM Portfolio -- Fidelity Equity Fund II</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://sifem.ch/investments/portfolio/detail/fidelity-equity-fund-ii</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Confirms SIFEM and SSNIT as LPs in Fidelity Equity Fund II; fund invests USD 500k-3.5m in unlisted Ghanaian SMEs</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>FSDEA Angola / Gemcorp</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Gemcorp Capital -- Gemcorp and FSDEA announce Pan-African Infrastructure Fund (9 Dec 2025)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://gemcorpcapital.com/news/gemcorp-capital-and-fsdea-announce-plans-for-new-pan-african-infrastructure-fund</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>FSDEA USD 50m seed (up to USD 200m); Gemcorp USD 50m; fund target USD 500m; Abu Dhabi domicile; sectors: critical minerals, water, food, energy transition</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>BPOPF / Thusano Capital</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Manager website</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Thusano Capital -- About / Fund mandate page</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://thusanocapital.com/</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Thusano Capital confirms management of BWP 1bn infrastructure fund on behalf of BPOPF. Sectors: energy, logistics, communications, agriculture, bulk infrastructure. 100% citizen-owned manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BPOPF / Multiple incubation managers</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Trade press</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Business Weekly -- Executives suspended at BDC over BPOPF P1bn tender</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://businessweekly.co.bw/news/executives-suspended-at-bdc-over-bpopfs-p1bn-tender</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Names all six BPOPF incubation programme beneficiaries: Africa Lighthouse Capital, Aleyo Capital (graduated), Thusano Capital, SeventyFive Degrees, 5th Quarter Investment Managers, K-Hill Property Developers. Six tenders ~P6bn awarded since inception. Minimum P500m per manager; current tender BPOPF/INV 008/2024-25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>NOSI / NSSA Egypt</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Official government summary / Arabic local disclosure</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Egypt Cabinet / SIS - NOSI annual report and final accounts FY2023/24 reviewed</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://sis.gov.eg/en/media-center/news/pm-reviews-social-insurance-finances-and-investment-growth/</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>NOSI official-public disclosure check; investment fund performance summary, no named African alternative-asset commitment found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>NOSI / NSSA Egypt</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Official Arabic government disclosure</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Egypt SIS Arabic - NOSI annual report and final accounts FY2022/23 reviewed by Cabinet</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://mediadr.sis.gov.eg/handle/123456789/51009</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Arabic local-language NOSI annual report/final account reference; aggregate investment growth but no named private fund/deal commitment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>NIB Egypt</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Official website / publications page</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>National Investment Bank Egypt - publications page</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.nib.gov.eg/Arabic/PUBLICATIONS-A/Publications-a.html</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>NIB public-disclosure check; publications relate to state investment plan/financing, not named pension alternative-asset commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Ethiopian Investment Holdings</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Company / issuer press release</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Akobo Minerals secures Ethiopian Sovereign Fund first international investment</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://news.cision.com/akobo-minerals-ab/r/akobo-minerals-secures-ethiopian-sovereign-fund-s-first-international-investment,c4216389</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>EIH USD 3m private placement / 7.4% Akobo Minerals stake; candidate direct equity item requiring scope decision because issuer is listed but project is Ethiopian mining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Ethiopian Investment Holdings</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Official / portfolio website</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Ethiopian Investment Holdings - Investment page</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://eih.et/?page_id=139</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>EIH mandate and investment approach; no fund LP commitments found in official investment page search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CMR Morocco</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Local-language trade press / annual report coverage</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>CMR published 2023 activity report; portfolio value and asset mix coverage</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://aujourdhui.ma/societe/cmr-la-pension-moyenne-mensuelle-des-nouveaux-retraites-etablie-a-10-966-dh</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>CMR public disclosure check; confirms activity report and portfolio values, no named African PE/infrastructure fund commitment found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CMR Morocco</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Local-language press / real estate allocation</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>CMR diversifies through OPCI real-estate vehicles</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://leseco.ma/business/retraite-la-cmr-diversifie-ses-placements.html</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>CMR candidate real-estate/OPCI alternative allocation; vehicle identities not yet resolved and likely outside core PE/infra scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>RCAR Morocco</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Allocator annual report</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CNRA-RCAR Rapport d?activit? 2023</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.rcar.ma/uploads/rapport_dactivites/RA%20CNRA%20RCAR%202023%20VFr.pdf</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>RCAR official report; evidence of mandates with CDG Capital, CDG Invest for unlisted participations, and Ewane Assets for real estate; no named allocator-to-fund commitment yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Sanlam Umbrella Fund</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Allocator trustee report</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Sanlam Umbrella Fund Annual Trustee Report 2024</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://seb-news.sanlam.co.za/wp-content/uploads/2025/03/Sanlam-Umbrella-Fund-Trustee-Report-2024_FINAL.pdf</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Sanlam Umbrella Fund official disclosure check; governance/responsible investment reporting reviewed, no named African alternative-asset fund/deal commitment found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Annual Report</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>GIPF 2023 Integrated Annual Report (year ended 31 March 2023)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.gipf.com.na/wp-content/uploads/2023/10/GIPF-2023-Integrated-Annual-Report.pdf</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Fund manager table (pp.84-85) and Unlisted Investment Fund Manager descriptions (pp.96-99). Identified: South Suez Capital (N$2.75bn), Investec Africa PE Fund 2, Neoma Africa Fund III (prev Abraaj), Actis Africa PE (N$101m), Growthpoint Investec Africa Properties Limited. Added as rows 104-108.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>GEPF / PIC</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Allocator annual report</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>GEPF Annual Report 2024/25</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://gepf.co.za/wp-content/uploads/2025/11/GEPF_AR_2025_digital.pdf</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>GEPF official disclosure sweep; Isibaya/unlisted portfolio and approved allocation to Ninety One Credit Fund - African Credit Opportunities Fund III.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>GEPF / PIC</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Asset manager annual report</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>PIC Integrated Annual Report 2024</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.pic.gov.za/DocAnnualReports1/PIC%20Integrated%20Annual%20Report%202024.pdf</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>PIC/GEPF unlisted investments and Africa ex-SA equity/developmental portfolio cross-check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Libyan Investment Authority</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>IFSWF self-assessment / official disclosure</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Libyan Investment Authority Santiago Principles Self-Assessment 2025</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.ifswf.org/assessment/lia-2025</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>LIA official governance/financial-disclosure sweep; confirms financial statements work and investment policy, but no named African fund commitment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Libyan Investment Authority</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Local press / official statement coverage</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>LIA announces 2025 direct financial assets results</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://libyaherald.com/2026/03/lia-announces-2025-direct-financial-assets-results-at-us-41-7-billion-generating-returns-of-us-2-billion-4-79/</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>LIA 2025 portfolio structure: time deposits, equities, and investment-fund portfolio; no named African private-market vehicle disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CDG Morocco</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Subsidiary annual financial report</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>CDG Capital Rapport Financier Annuel 2024</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.cdgcapital.ma/sites/default/files/RapportFinancier%20AnnuelCDG%20CapitalFY2024.pdf</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>CDG/CDG Capital official disclosure sweep; current activity and financial report, no new named pension/SWF LP commitment beyond existing CDG rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CDG Morocco</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Historical annual report</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>CDG Capital Annual Report 2016</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.cdgcapital.ma/sites/default/files/publication/2019-01/Rapport%20Annuel%202016.pdf</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Historical CDG Capital private-equity / CapMezzanine context; reviewed for possible older fund rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CNSS Morocco</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Local-language social security report coverage</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>CNSS AMO statistical report 2023 coverage</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://aujourdhui.ma/societe/amo-les-chiffres-de-la-cnss-en-2023</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>CNSS official/statistical disclosure sweep; operating/social-security data, no named alternative-asset commitment found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CNSS Morocco</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Local press / real-estate financing mechanism</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>State asset sales / innovative financing: CNSS creates OPCI in 2024</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://medias24.com/2025/07/15/financements-innovants-35-mmdh-en-2024/</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>CNSS candidate OPCI/state-asset real-estate vehicle lead; likely outside core PE/infra scope unless dashboard includes real estate vehicles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CIMR Morocco</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Allocator documentation page</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>CIMR documentation page - annual reports including 2024</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.cimr.ma/a-propos-cimr/espace-documentation/</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>CIMR public disclosure sweep; annual reports available, no named African alternative fund commitment found in initial pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CIMR Morocco</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Local financial press</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>CIMR 2023 portfolio value coverage</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://boursenews.ma/article/marches/CIMR-resultats-2023</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>CIMR placement portfolio size cross-check; no named private-market vehicle evidence in source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>BPOPF</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Allocator annual reports page</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>BPOPF Annual Reports page including Annual Report 2024/25</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.bpopf.co.bw/AnnualDisp</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>BPOPF official disclosure sweep; annual report page and existing unlisted/incubation programme context checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>BPOPF / Botswana funds</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Regulator annual report</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>NBFIRA Annual Report 2024</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.nbfira.org.bw/wp-content/uploads/2025/01/nbfira-annual-report-2024.pdf</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Botswana retirement-fund industry allocation cross-check, including unlisted equity category and BPOPF as top fund.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>PSSSF Tanzania</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Local press / official remarks</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PSSSF posts 1.3tri profit in government bonds</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://dailynews.co.tz/psssf-posts-1-3tri-profit-in-government-bonds/</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>PSSSF disclosure sweep; confirms conservative government-bond/securities focus and no named PE/infra fund commitment in reviewed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>EPPF South Africa</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Allocator annual reports page</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>EPPF Annual Reports page including 2025 Integrated Annual Report</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.eppf.co.za/governance/annual-reports</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>EPPF official disclosure sweep; reports available, no new named African alternative fund commitment found beyond existing PE exposure row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>FONSIS (Senegal)</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Fund manager website / Press release</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Teranga Capital – About Us; IETP fund launch announcement; Africa Global Funds coverage</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.terangacapital.com/en/about-us/</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>FONSIS confirmed as founding LP/shareholder in Teranga Capital (2016 impact SME fund, Senegal). Added as row 109.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11325,7 +13289,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11747,7 +13711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12623,7 +14587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26296,7 +28260,4632 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R98"/>
+  <dimension ref="A1:V49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="16" min="1" max="1"/>
+    <col width="34" customWidth="1" style="16" min="2" max="2"/>
+    <col width="16" customWidth="1" style="16" min="3" max="3"/>
+    <col width="36" customWidth="1" style="16" min="4" max="4"/>
+    <col width="26" customWidth="1" style="16" min="5" max="5"/>
+    <col width="15" customWidth="1" style="16" min="6" max="6"/>
+    <col width="11" customWidth="1" style="16" min="7" max="7"/>
+    <col width="24" customWidth="1" style="16" min="8" max="8"/>
+    <col width="42" customWidth="1" style="16" min="9" max="9"/>
+    <col width="48" customWidth="1" style="16" min="10" max="10"/>
+    <col width="46" customWidth="1" style="16" min="11" max="11"/>
+    <col width="14" customWidth="1" style="16" min="12" max="12"/>
+    <col width="14" customWidth="1" style="16" min="13" max="13"/>
+    <col width="14" customWidth="1" style="16" min="14" max="14"/>
+    <col width="28" customWidth="1" style="16" min="15" max="15"/>
+    <col width="24" customWidth="1" style="16" min="16" max="16"/>
+    <col width="22" customWidth="1" style="16" min="17" max="17"/>
+    <col width="30" customWidth="1" style="16" min="18" max="18"/>
+    <col width="32" customWidth="1" style="16" min="19" max="19"/>
+    <col width="52" customWidth="1" style="16" min="20" max="20"/>
+    <col width="14" customWidth="1" style="16" min="21" max="21"/>
+    <col width="56" customWidth="1" style="16" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Sweep priority</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Sweep status</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Institution</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>AUM (USD m, approx)</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>As-of year</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Disclosure language targets</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Aliases / local names to search</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Official disclosure targets</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Regulator / filing hints</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Current commitment rows matched</t>
+        </is>
+      </c>
+      <c r="M1" s="28" t="inlineStr">
+        <is>
+          <t>Current source-library rows matched</t>
+        </is>
+      </c>
+      <c r="N1" s="28" t="inlineStr">
+        <is>
+          <t>Official/source document rows matched</t>
+        </is>
+      </c>
+      <c r="O1" s="28" t="inlineStr">
+        <is>
+          <t>Public docs checked</t>
+        </is>
+      </c>
+      <c r="P1" s="28" t="inlineStr">
+        <is>
+          <t>Latest official doc checked</t>
+        </is>
+      </c>
+      <c r="Q1" s="28" t="inlineStr">
+        <is>
+          <t>Local-language docs checked</t>
+        </is>
+      </c>
+      <c r="R1" s="28" t="inlineStr">
+        <is>
+          <t>Candidate commitments found</t>
+        </is>
+      </c>
+      <c r="S1" s="28" t="inlineStr">
+        <is>
+          <t>No-evidence rationale</t>
+        </is>
+      </c>
+      <c r="T1" s="28" t="inlineStr">
+        <is>
+          <t>Recommended next action</t>
+        </is>
+      </c>
+      <c r="U1" s="28" t="inlineStr">
+        <is>
+          <t>Audit date seeded</t>
+        </is>
+      </c>
+      <c r="V1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Checked - candidate named fund allocation found</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>GEPF (managed by PIC)</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>Public PF (DB)</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="n">
+        <v>125000</v>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>GEPF (managed by PIC); GEPF; PIC; Public Investment Corporation; Government Employees Pension Fund</t>
+        </is>
+      </c>
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K2" s="21" t="inlineStr">
+        <is>
+          <t>FSCA; PIC/GEPF annual reports; parliamentary/PMG filings</t>
+        </is>
+      </c>
+      <c r="L2" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" s="21" t="inlineStr">
+        <is>
+          <t>Yes - GEPF 2024/25 annual report and PIC 2024 report checked</t>
+        </is>
+      </c>
+      <c r="P2" s="21" t="inlineStr">
+        <is>
+          <t>GEPF Annual Report 2024/25; PIC Integrated Annual Report 2024</t>
+        </is>
+      </c>
+      <c r="Q2" s="21" t="inlineStr">
+        <is>
+          <t>N/A - English disclosure</t>
+        </is>
+      </c>
+      <c r="R2" s="21" t="inlineStr">
+        <is>
+          <t>Ninety One Credit Fund - African Credit Opportunities Fund III</t>
+        </is>
+      </c>
+      <c r="S2" s="21" t="inlineStr"/>
+      <c r="T2" s="21" t="inlineStr">
+        <is>
+          <t>Resolve commitment amount and co-investors for Ninety One African Credit Opportunities Fund III; add confirmed row if amount/source detail is sufficient.</t>
+        </is>
+      </c>
+      <c r="U2" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V2" s="21" t="inlineStr">
+        <is>
+          <t>Disclosed PE/infra exposure including Africa-ex-SA via PIC's Isibaya programme; LP in DPI, Helios, others (historical).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Checked - no named alts commitment found in official/public summaries</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>NOSI / NSSA</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>Public PF (consolidated)</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="n">
+        <v>110000</v>
+      </c>
+      <c r="G3" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>Arabic; English</t>
+        </is>
+      </c>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>NOSI / NSSA; NOSI; NSSA; National Organization for Social Insurance</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>NOSI/NIB official publications; Ministry of Social Solidarity; Arabic annual reports</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="21" t="inlineStr">
+        <is>
+          <t>Partial - official Cabinet/SIS annual report summaries checked; full report PDF not found</t>
+        </is>
+      </c>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t>FY2023/24 Cabinet/SIS annual report and final accounts summary; FY2022/23 Arabic SIS summary</t>
+        </is>
+      </c>
+      <c r="Q3" s="21" t="inlineStr">
+        <is>
+          <t>Partial - Arabic SIS/Cabinet summaries checked</t>
+        </is>
+      </c>
+      <c r="R3" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S3" s="21" t="inlineStr">
+        <is>
+          <t>Public summaries report aggregate investment fund growth/returns but do not name fund, private equity, infrastructure, or direct-company commitments.</t>
+        </is>
+      </c>
+      <c r="T3" s="21" t="inlineStr">
+        <is>
+          <t>Find full NOSI annual report/final accounts PDF if publicly posted; otherwise retain as no named public commitment in available official summaries.</t>
+        </is>
+      </c>
+      <c r="U3" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V3" s="21" t="inlineStr">
+        <is>
+          <t>Predominantly EGP government securities; Africa alts exposure historically minimal but worth verifying post-2019 reforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Checked - no named African alts commitment found in latest public portfolio summaries</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Libya</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Libyan Investment Authority</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>SWF</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="n">
+        <v>67000</v>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Arabic; English</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Libyan Investment Authority; LIA</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>LIA reports; UN sanctions disclosures; Social Security Fund publications</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>Partial - IFSWF 2025 self-assessment and 2025 direct financial-assets statement coverage checked</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t>LIA Santiago Principles Self-Assessment 2025; 2025 direct financial assets statement coverage</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="inlineStr">
+        <is>
+          <t>Partial - English/Arabic-statement coverage checked via local press and IFSWF; no full consolidated AFS found</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Public summaries disclose aggregate time deposit, equity, and investment-fund portfolios but do not name African private-market funds or deals.</t>
+        </is>
+      </c>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t>Monitor consolidated financial statements and subsidiary reports; search LAIP/LTP/LAFICO for named Africa holdings if direct-stake scope expands.</t>
+        </is>
+      </c>
+      <c r="U4" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V4" s="21" t="inlineStr">
+        <is>
+          <t>Mostly frozen since 2011; Pre-2011 had direct African stakes (banking, telecoms) — investigate legacy holdings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Checked - candidate found, scope decision needed</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Ethiopian Investment Holdings (EIH)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Strategic SWF (SOE holding)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>Amharic; English</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>Ethiopian Investment Holdings (EIH); Ethiopian Investment Holdings; EIH</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>POESSA/PSSSA materials; Ministry of Finance; NBE/ESE reform documents</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="21" t="inlineStr">
+        <is>
+          <t>Partial - EIH investment page and issuer/local disclosures checked</t>
+        </is>
+      </c>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t>EIH investment page; Akobo Minerals 2025 private placement release</t>
+        </is>
+      </c>
+      <c r="Q5" s="21" t="inlineStr">
+        <is>
+          <t>Partial - English public disclosures checked; Amharic search did not reveal a fuller annual report in this pass</t>
+        </is>
+      </c>
+      <c r="R5" s="21" t="inlineStr">
+        <is>
+          <t>Akobo Minerals AB private placement / Segele gold project stake</t>
+        </is>
+      </c>
+      <c r="S5" s="21" t="inlineStr"/>
+      <c r="T5" s="21" t="inlineStr">
+        <is>
+          <t>Resolve scope for listed/private-placement mining stake; continue search for EIH consolidated financials/annual report.</t>
+        </is>
+      </c>
+      <c r="U5" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V5" s="21" t="inlineStr">
+        <is>
+          <t>AUM is book value of SOE stakes; not a traditional LP. Verify any third-party fund commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Checked - no named alts commitment found in public NIB/NOSI trail</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>NIB legacy pension assets</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Sovereign deposit</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>Arabic; English</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>NIB legacy pension assets; National Investment Bank; NIB; NIB Egypt</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>NOSI/NIB official publications; Ministry of Social Solidarity; Arabic annual reports</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>Partial - NIB official publications page and social-insurance/NIB relationship sources checked</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t>NIB publications page; Egyptian Tax Authority note on social insurance funds/NIB relationship</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>Partial - Arabic NIB publications page checked</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S6" s="21" t="inlineStr">
+        <is>
+          <t>NIB materials describe state investment-plan financing and historic pension-fund balances; no allocator-to-alternative-vehicle commitment found.</t>
+        </is>
+      </c>
+      <c r="T6" s="21" t="inlineStr">
+        <is>
+          <t>Check Ministry of Planning/NIB financial statements if later disclosed; otherwise keep out of commitments.</t>
+        </is>
+      </c>
+      <c r="U6" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V6" s="21" t="inlineStr">
+        <is>
+          <t>Structure under reform; verify current asset mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Caisse de Dépôt et de Gestion (CDG)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Sovereign + pension manager</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>French; Arabic</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>Caisse de Dépôt et de Gestion (CDG); Caisse de Dépôt et de Gestion; CDG; CDG Morocco</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>ACAPS; AMMC fund register; CDG/CMR/RCAR annual reports</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr"/>
+      <c r="Q7" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R7" s="21" t="inlineStr"/>
+      <c r="S7" s="21" t="inlineStr"/>
+      <c r="T7" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U7" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V7" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed LP in pan-African and Moroccan PE/infra (CDG Capital, Mediterrania Capital, AfricInvest funds).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Checked - candidate real-estate/OPCI lead found, no named PE/infra commitment</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Civil-service PF</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>14500</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>French; Arabic</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>CMR; Caisse Marocaine des Retraites</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>ACAPS; AMMC fund register; CDG/CMR/RCAR annual reports</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="21" t="inlineStr">
+        <is>
+          <t>Partial - 2023 activity-report coverage, Court of Accounts report, ACAPS/prudential trail checked</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t>CMR 2023 activity-report coverage; Court of Accounts CMR report</t>
+        </is>
+      </c>
+      <c r="Q8" s="21" t="inlineStr">
+        <is>
+          <t>Partial - French searches checked</t>
+        </is>
+      </c>
+      <c r="R8" s="21" t="inlineStr">
+        <is>
+          <t>CMR OPCI real-estate vehicles (vehicle names unresolved)</t>
+        </is>
+      </c>
+      <c r="S8" s="21" t="inlineStr">
+        <is>
+          <t>Available public sources describe portfolio values, asset mix and OPCI diversification but do not name a PE/infrastructure fund commitment.</t>
+        </is>
+      </c>
+      <c r="T8" s="21" t="inlineStr">
+        <is>
+          <t>Search AMMC OPCI register and CMR report PDFs for named OPCI vehicles; likely keep outside core scope unless real estate is included.</t>
+        </is>
+      </c>
+      <c r="U8" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V8" s="21" t="inlineStr">
+        <is>
+          <t>Verify alts mandate; recent reform allowing higher alts limit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Checked - mandate evidence found, no named commitment yet</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>RCAR (CDG-managed)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>Parastatal PF</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>French; Arabic</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>RCAR (CDG-managed); RCAR; Régime Collectif d'Allocation de Retraite</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>ACAPS; AMMC fund register; CDG/CMR/RCAR annual reports</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>Yes - RCAR 2023 activity report checked</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t>CNRA-RCAR Rapport d?activit? 2023</t>
+        </is>
+      </c>
+      <c r="Q9" s="21" t="inlineStr">
+        <is>
+          <t>Yes - French official report checked</t>
+        </is>
+      </c>
+      <c r="R9" s="21" t="inlineStr">
+        <is>
+          <t>RCAR unlisted-participation and real-estate management mandates</t>
+        </is>
+      </c>
+      <c r="S9" s="21" t="inlineStr"/>
+      <c r="T9" s="21" t="inlineStr">
+        <is>
+          <t>Research CDG Invest/Ewane Assets mandate details for named underlying vehicles/deals before adding commitment rows.</t>
+        </is>
+      </c>
+      <c r="U9" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V9" s="21" t="inlineStr">
+        <is>
+          <t>Alts exposure via CDG Capital infrastructure and PE funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>The Sovereign Fund of Egypt (TSFE)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>SWF (strategic)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>Arabic; English</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>The Sovereign Fund of Egypt (TSFE); The Sovereign Fund of Egypt; TSFE</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>NOSI/NIB official publications; Ministry of Social Solidarity; Arabic annual reports</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P10" s="21" t="inlineStr"/>
+      <c r="Q10" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R10" s="21" t="inlineStr"/>
+      <c r="S10" s="21" t="inlineStr"/>
+      <c r="T10" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U10" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V10" s="21" t="inlineStr">
+        <is>
+          <t>Joint platforms with ADQ, PIF; co-investments in renewables, healthcare, fintech.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>GIPF</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Public PF (DB)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>GIPF; Government Institutions Pension Fund</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>NAMFISA; GIPF annual reports; unlisted investment programme disclosures</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P11" s="21" t="inlineStr"/>
+      <c r="Q11" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R11" s="21" t="inlineStr"/>
+      <c r="S11" s="21" t="inlineStr"/>
+      <c r="T11" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U11" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V11" s="21" t="inlineStr">
+        <is>
+          <t>Mandatory unlisted-investment programme; ~10% to local SME/PE managers (Stimulus, Sanlam, Eos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Checked - no public named alts commitment found</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Libya</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>Social Security Fund of Libya</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>Arabic; English</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>Social Security Fund of Libya; Libya Social Security Fund</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>LIA reports; UN sanctions disclosures; Social Security Fund publications</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>Partial - public web/local-language search did not find official annual report or named commitments</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t>No current official annual report located in public search; LIA/Libya public finance context checked</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="inlineStr">
+        <is>
+          <t>Partial - Arabic/English public searches checked</t>
+        </is>
+      </c>
+      <c r="R12" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S12" s="21" t="inlineStr">
+        <is>
+          <t>Search found no public annual-report/portfolio disclosure naming alternative-asset vehicles; likely opaque domestic deposits/real estate unless official report emerges.</t>
+        </is>
+      </c>
+      <c r="T12" s="21" t="inlineStr">
+        <is>
+          <t>Monitor Libyan official publications and social-security fund disclosures; keep as disclosure gap.</t>
+        </is>
+      </c>
+      <c r="U12" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V12" s="21" t="inlineStr">
+        <is>
+          <t>Limited alts beyond domestic bank deposits and real estate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Checked - candidate OPCI real-estate lead found, no PE/infra fund commitment</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>CNSS Morocco</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>French; Arabic</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>CNSS Morocco; CNSS</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>ACAPS; AMMC fund register; CDG/CMR/RCAR annual reports</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="21" t="inlineStr">
+        <is>
+          <t>Partial - CNSS statistical report coverage and Morocco financial-stability/innovative-financing trail checked</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t>CNSS AMO statistical report 2023 coverage; Morocco 2024 financial-stability coverage</t>
+        </is>
+      </c>
+      <c r="Q13" s="21" t="inlineStr">
+        <is>
+          <t>Yes - French/Arabic public sources checked at search-result level</t>
+        </is>
+      </c>
+      <c r="R13" s="21" t="inlineStr">
+        <is>
+          <t>CNSS OPCI state-asset acquisition vehicle</t>
+        </is>
+      </c>
+      <c r="S13" s="21" t="inlineStr"/>
+      <c r="T13" s="21" t="inlineStr">
+        <is>
+          <t>Resolve OPCI vehicle name/size via AMMC/state-domain reports; likely exclude unless real estate/OPCI vehicles are included.</t>
+        </is>
+      </c>
+      <c r="U13" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V13" s="21" t="inlineStr">
+        <is>
+          <t>Verify recent allocations under post-2020 reform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Checked - no named African alts commitment found in initial official/public docs</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>CIMR</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>Private complementary PF</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>French; Arabic</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>CIMR</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>ACAPS; AMMC fund register; CDG/CMR/RCAR annual reports</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="21" t="inlineStr">
+        <is>
+          <t>Partial - CIMR documentation page and 2023 portfolio coverage checked</t>
+        </is>
+      </c>
+      <c r="P14" s="21" t="inlineStr">
+        <is>
+          <t>CIMR documentation page with 2024 annual report availability; 2023 portfolio coverage</t>
+        </is>
+      </c>
+      <c r="Q14" s="21" t="inlineStr">
+        <is>
+          <t>Yes - French sources checked</t>
+        </is>
+      </c>
+      <c r="R14" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S14" s="21" t="inlineStr">
+        <is>
+          <t>Public sources indicate portfolio size and annual reports, but no named private equity, infrastructure, or direct alternative vehicle found in initial sweep.</t>
+        </is>
+      </c>
+      <c r="T14" s="21" t="inlineStr">
+        <is>
+          <t>Open full CIMR annual report PDF for detailed asset schedule if available; otherwise retain as no named commitment found.</t>
+        </is>
+      </c>
+      <c r="U14" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V14" s="21" t="inlineStr">
+        <is>
+          <t>Verify Africa-alts exposure; primarily Moroccan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Checked - official annual/regulator sources reviewed, no additional named commitments found</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Botswana Public Officers Pension Fund (BPOPF)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>Botswana Public Officers Pension Fund (BPOPF)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="21" t="inlineStr">
+        <is>
+          <t>Partial - BPOPF annual reports page and NBFIRA 2024 annual report checked</t>
+        </is>
+      </c>
+      <c r="P15" s="21" t="inlineStr">
+        <is>
+          <t>BPOPF Annual Reports page 2024/25; NBFIRA Annual Report 2024</t>
+        </is>
+      </c>
+      <c r="Q15" s="21" t="inlineStr">
+        <is>
+          <t>N/A - English disclosure</t>
+        </is>
+      </c>
+      <c r="R15" s="21" t="inlineStr">
+        <is>
+          <t>None beyond existing BPOPF incubation/unlisted manager leads</t>
+        </is>
+      </c>
+      <c r="S15" s="21" t="inlineStr">
+        <is>
+          <t>Official/regulator sources support unlisted allocation context but no new named allocator-to-vehicle commitment beyond existing rows/leads.</t>
+        </is>
+      </c>
+      <c r="T15" s="21" t="inlineStr">
+        <is>
+          <t>Open full BPOPF 2024/25 report for detailed manager schedule if needed; continue following BPOPF incubation tender disclosures.</t>
+        </is>
+      </c>
+      <c r="U15" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V15" s="21" t="inlineStr">
+        <is>
+          <t>Has used mandates for African private equity (e.g., RMB, Vantage, local SA managers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Checked - no named alts commitment found; conservative bond/securities focus</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>PSSSF</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>Consolidated public PF</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>English; Swahili</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>PSSSF</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>Bank of Tanzania social security investment guidelines; PSSSF/NSSF annual reports</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="21" t="inlineStr">
+        <is>
+          <t>Partial - local official-remarks coverage checked</t>
+        </is>
+      </c>
+      <c r="P16" s="21" t="inlineStr">
+        <is>
+          <t>Daily News coverage of PSSSF 2024/25 bond/securities investment performance</t>
+        </is>
+      </c>
+      <c r="Q16" s="21" t="inlineStr">
+        <is>
+          <t>N/A/Partial - English local source checked; Swahili source not needed for identified disclosure</t>
+        </is>
+      </c>
+      <c r="R16" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S16" s="21" t="inlineStr">
+        <is>
+          <t>Reviewed source emphasizes government bonds/securities and Bank of Tanzania guideline alignment; no private equity/infrastructure fund commitment found.</t>
+        </is>
+      </c>
+      <c r="T16" s="21" t="inlineStr">
+        <is>
+          <t>Locate full PSSSF annual report/investment schedule if public; otherwise retain no named commitment.</t>
+        </is>
+      </c>
+      <c r="U16" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V16" s="21" t="inlineStr">
+        <is>
+          <t>Historically conservative; verify any alts commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>NSSF Uganda</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G17" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>NSSF Uganda; National Social Security Fund Uganda</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>URBRA; NSSF annual reports; CMA/USE disclosures</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="N17" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P17" s="21" t="inlineStr"/>
+      <c r="Q17" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R17" s="21" t="inlineStr"/>
+      <c r="S17" s="21" t="inlineStr"/>
+      <c r="T17" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U17" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V17" s="21" t="inlineStr">
+        <is>
+          <t>Disclosed commitments to PE/VC funds (Catalyst Fund II historically, etc.); verify current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Sentinel</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>Sentinel Retirement Fund (SA)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>Multi-employer PF</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>Sentinel Retirement Fund (SA)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P18" s="21" t="inlineStr"/>
+      <c r="Q18" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R18" s="21" t="inlineStr"/>
+      <c r="S18" s="21" t="inlineStr"/>
+      <c r="T18" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U18" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V18" s="21" t="inlineStr">
+        <is>
+          <t>Uses alts mandate managers (Old Mutual Alternative Investments, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>Transnet Retirement Fund</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>Parastatal PF</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>Transnet Retirement Fund</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>FSCA; PIC/GEPF annual reports; parliamentary/PMG filings</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P19" s="21" t="inlineStr"/>
+      <c r="Q19" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R19" s="21" t="inlineStr"/>
+      <c r="S19" s="21" t="inlineStr"/>
+      <c r="T19" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U19" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V19" s="21" t="inlineStr">
+        <is>
+          <t>PIC and external alts managers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>Pula Fund</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>SWF (savings)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>Pula Fund</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P20" s="21" t="inlineStr"/>
+      <c r="Q20" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R20" s="21" t="inlineStr"/>
+      <c r="S20" s="21" t="inlineStr"/>
+      <c r="T20" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U20" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V20" s="21" t="inlineStr">
+        <is>
+          <t>Predominantly global fixed income and equities; minimal Africa-alts exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>Checked - no named African alts commitment found in trustee report</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Sanlam Umbrella Fund</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>Umbrella DC</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G21" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>Sanlam Umbrella Fund</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>FSCA; PIC/GEPF annual reports; parliamentary/PMG filings</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="21" t="inlineStr">
+        <is>
+          <t>Yes - 2024 Annual Trustee Report checked at summary/search level</t>
+        </is>
+      </c>
+      <c r="P21" s="21" t="inlineStr">
+        <is>
+          <t>Sanlam Umbrella Fund Annual Trustee Report 2024</t>
+        </is>
+      </c>
+      <c r="Q21" s="21" t="inlineStr">
+        <is>
+          <t>N/A - English disclosure</t>
+        </is>
+      </c>
+      <c r="R21" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S21" s="21" t="inlineStr">
+        <is>
+          <t>Trustee report covers governance/responsible investment and member fund operations, but no named African PE/infra/private-credit/direct-investment commitments were found.</t>
+        </is>
+      </c>
+      <c r="T21" s="21" t="inlineStr">
+        <is>
+          <t>If needed, inspect full summarized financial statements/fund option reports for underlying asset-manager exposure, but no allocator-to-vehicle evidence found.</t>
+        </is>
+      </c>
+      <c r="U21" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V21" s="21" t="inlineStr">
+        <is>
+          <t>Alts allocation handled by underlying portfolio managers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Checked - official annual reports available, no new named commitment found in initial pass</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>Eskom Pension and Provident Fund (EPPF)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>Parastatal PF</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G22" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>Eskom Pension and Provident Fund (EPPF)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>FSCA; PIC/GEPF annual reports; parliamentary/PMG filings</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="21" t="inlineStr">
+        <is>
+          <t>Partial - EPPF annual reports page and 2024/2025 report availability checked</t>
+        </is>
+      </c>
+      <c r="P22" s="21" t="inlineStr">
+        <is>
+          <t>EPPF Annual Reports page including 2025 Integrated Annual Report; 2024 IAR/AFS links</t>
+        </is>
+      </c>
+      <c r="Q22" s="21" t="inlineStr">
+        <is>
+          <t>N/A - English disclosure</t>
+        </is>
+      </c>
+      <c r="R22" s="21" t="inlineStr">
+        <is>
+          <t>None beyond existing multiple PE funds row</t>
+        </is>
+      </c>
+      <c r="S22" s="21" t="inlineStr">
+        <is>
+          <t>EPPF discloses report availability and broad investment material; initial sweep did not find a new named African fund/deal commitment beyond existing PE exposure.</t>
+        </is>
+      </c>
+      <c r="T22" s="21" t="inlineStr">
+        <is>
+          <t>Open full 2025 IAR/AFS investment schedule for named manager/fund detail if available.</t>
+        </is>
+      </c>
+      <c r="U22" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V22" s="21" t="inlineStr">
+        <is>
+          <t>Disclosed alts mandates including unlisted equity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>SSNIT</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>Public PF (mandatory)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>SSNIT; Social Security and National Insurance Trust</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>NPRA; SSNIT annual reports; VCTF annual reports</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P23" s="21" t="inlineStr"/>
+      <c r="Q23" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R23" s="21" t="inlineStr"/>
+      <c r="S23" s="21" t="inlineStr"/>
+      <c r="T23" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U23" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V23" s="21" t="inlineStr">
+        <is>
+          <t>Has made direct equity investments in Ghanaian listed/unlisted firms (banking, real estate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>NSSF Kenya</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>Public PF (mandatory)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>English; Swahili</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>NSSF Kenya; National Social Security Fund Kenya</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>RBA; NSSF annual reports; KEPFIC member disclosures</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P24" s="21" t="inlineStr"/>
+      <c r="Q24" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R24" s="21" t="inlineStr"/>
+      <c r="S24" s="21" t="inlineStr"/>
+      <c r="T24" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U24" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V24" s="21" t="inlineStr">
+        <is>
+          <t>Mostly bonds/equities; verify any PE fund commitments (historically limited).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>CNR Algeria</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G25" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>French; Arabic</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>CNR Algeria</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>CNR/CASNOS/ministry disclosures; French/Arabic public reports</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P25" s="21" t="inlineStr"/>
+      <c r="Q25" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R25" s="21" t="inlineStr"/>
+      <c r="S25" s="21" t="inlineStr"/>
+      <c r="T25" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U25" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V25" s="21" t="inlineStr">
+        <is>
+          <t>Limited disclosure; alts likely minimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>National Pensions Fund (NPF)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>National Pensions Fund (NPF)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P26" s="21" t="inlineStr"/>
+      <c r="Q26" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R26" s="21" t="inlineStr"/>
+      <c r="S26" s="21" t="inlineStr"/>
+      <c r="T26" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U26" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V26" s="21" t="inlineStr">
+        <is>
+          <t>Verify exposure to Mauritian-domiciled Africa funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>Stanbic IBTC Pension Managers</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>PFA (DC)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>Stanbic IBTC Pension Managers</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>PenCom; NSIA annual reports; PFA annual reports where public</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P27" s="21" t="inlineStr"/>
+      <c r="Q27" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R27" s="21" t="inlineStr"/>
+      <c r="S27" s="21" t="inlineStr"/>
+      <c r="T27" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U27" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V27" s="21" t="inlineStr">
+        <is>
+          <t>PenCom Multi-Fund Structure permits alts; Stanbic has made disclosed PE/infra fund commitments (e.g., African Capital Alliance, Vetiva, Sahel Capital).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>FSDEA</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>SWF</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>Portuguese</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>FSDEA</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>ARSEG; FSDEA annual reports; Portuguese public filings</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P28" s="21" t="inlineStr"/>
+      <c r="Q28" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R28" s="21" t="inlineStr"/>
+      <c r="S28" s="21" t="inlineStr"/>
+      <c r="T28" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U28" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V28" s="21" t="inlineStr">
+        <is>
+          <t>Has disclosed African PE/infra exposure (Quantum Global era under prior management; new mandate post-2018).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>POESSA</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>Civil-service PF</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>Amharic; English</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>POESSA</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>POESSA/PSSSA materials; Ministry of Finance; NBE/ESE reform documents</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P29" s="21" t="inlineStr"/>
+      <c r="Q29" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R29" s="21" t="inlineStr"/>
+      <c r="S29" s="21" t="inlineStr"/>
+      <c r="T29" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U29" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V29" s="21" t="inlineStr">
+        <is>
+          <t>Verify any non-government-securities allocation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>NAPSA</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>Public PF (mandatory)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G30" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>NAPSA</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L30" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P30" s="21" t="inlineStr"/>
+      <c r="Q30" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R30" s="21" t="inlineStr"/>
+      <c r="S30" s="21" t="inlineStr"/>
+      <c r="T30" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U30" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V30" s="21" t="inlineStr">
+        <is>
+          <t>Has invested in domestic infrastructure (toll roads, real estate); verify PE fund commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>NSIA</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>SWF (3 sub-funds)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G31" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>NSIA; Nigeria Sovereign Investment Authority</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>PenCom; NSIA annual reports; PFA annual reports where public</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="M31" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="N31" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P31" s="21" t="inlineStr"/>
+      <c r="Q31" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R31" s="21" t="inlineStr"/>
+      <c r="S31" s="21" t="inlineStr"/>
+      <c r="T31" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U31" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V31" s="21" t="inlineStr">
+        <is>
+          <t>NIF sub-fund has co-invested in Nigerian infra, agribusiness, healthcare; LP in PE funds (e.g., Verod, African Capital Alliance).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>CGRAE</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>Civil-service PF</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>CGRAE</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P32" s="21" t="inlineStr"/>
+      <c r="Q32" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R32" s="21" t="inlineStr"/>
+      <c r="S32" s="21" t="inlineStr"/>
+      <c r="T32" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U32" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V32" s="21" t="inlineStr">
+        <is>
+          <t>Verify if any alts allocation under recent reform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>ARM Pension Managers</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>PFA</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>ARM Pension Managers</t>
+        </is>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K33" s="21" t="inlineStr">
+        <is>
+          <t>PenCom; NSIA annual reports; PFA annual reports where public</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P33" s="21" t="inlineStr"/>
+      <c r="Q33" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R33" s="21" t="inlineStr"/>
+      <c r="S33" s="21" t="inlineStr"/>
+      <c r="T33" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U33" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V33" s="21" t="inlineStr">
+        <is>
+          <t>ARM affiliate is a major Nigerian PE manager (ARM-Harith); intra-group commitments are an obvious starting point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>CNPS-CI</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>Private-sector PF</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>CNPS-CI</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P34" s="21" t="inlineStr"/>
+      <c r="Q34" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R34" s="21" t="inlineStr"/>
+      <c r="S34" s="21" t="inlineStr"/>
+      <c r="T34" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U34" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V34" s="21" t="inlineStr">
+        <is>
+          <t>Verify alts exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>Debswana Pension Fund</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>Corporate PF (mining JV)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G35" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>Debswana Pension Fund</t>
+        </is>
+      </c>
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K35" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P35" s="21" t="inlineStr"/>
+      <c r="Q35" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R35" s="21" t="inlineStr"/>
+      <c r="S35" s="21" t="inlineStr"/>
+      <c r="T35" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U35" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V35" s="21" t="inlineStr">
+        <is>
+          <t>Long-running alts programme; LP in African PE funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>CNRPS</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>Civil-service PF</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G36" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>CNRPS</t>
+        </is>
+      </c>
+      <c r="J36" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K36" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P36" s="21" t="inlineStr"/>
+      <c r="Q36" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R36" s="21" t="inlineStr"/>
+      <c r="S36" s="21" t="inlineStr"/>
+      <c r="T36" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U36" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V36" s="21" t="inlineStr">
+        <is>
+          <t>Limited disclosure; verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>TSFE see above</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
+        <is>
+          <t>Arabic; English</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>TSFE see above</t>
+        </is>
+      </c>
+      <c r="J37" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K37" s="21" t="inlineStr">
+        <is>
+          <t>NOSI/NIB official publications; Ministry of Social Solidarity; Arabic annual reports</t>
+        </is>
+      </c>
+      <c r="L37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P37" s="21" t="inlineStr"/>
+      <c r="Q37" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R37" s="21" t="inlineStr"/>
+      <c r="S37" s="21" t="inlineStr"/>
+      <c r="T37" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U37" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V37" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>RSSB</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G38" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>English; French; Kinyarwanda</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
+        <is>
+          <t>RSSB; Rwanda Social Security Board</t>
+        </is>
+      </c>
+      <c r="J38" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K38" s="21" t="inlineStr">
+        <is>
+          <t>RSSB annual reports; CMA Rwanda; KIFC/Rwanda Finance disclosures</t>
+        </is>
+      </c>
+      <c r="L38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="N38" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P38" s="21" t="inlineStr"/>
+      <c r="Q38" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R38" s="21" t="inlineStr"/>
+      <c r="S38" s="21" t="inlineStr"/>
+      <c r="T38" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U38" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V38" s="21" t="inlineStr">
+        <is>
+          <t>Active in Rwandan strategic investments; has equity stakes in BK Group, Rwandair, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>CNSS Tunisia</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G39" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>CNSS Tunisia</t>
+        </is>
+      </c>
+      <c r="J39" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K39" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P39" s="21" t="inlineStr"/>
+      <c r="Q39" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R39" s="21" t="inlineStr"/>
+      <c r="S39" s="21" t="inlineStr"/>
+      <c r="T39" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U39" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V39" s="21" t="inlineStr">
+        <is>
+          <t>Limited disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>CNAS Algeria</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G40" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H40" s="21" t="inlineStr">
+        <is>
+          <t>French; Arabic</t>
+        </is>
+      </c>
+      <c r="I40" s="21" t="inlineStr">
+        <is>
+          <t>CNAS Algeria</t>
+        </is>
+      </c>
+      <c r="J40" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K40" s="21" t="inlineStr">
+        <is>
+          <t>CNR/CASNOS/ministry disclosures; French/Arabic public reports</t>
+        </is>
+      </c>
+      <c r="L40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P40" s="21" t="inlineStr"/>
+      <c r="Q40" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R40" s="21" t="inlineStr"/>
+      <c r="S40" s="21" t="inlineStr"/>
+      <c r="T40" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U40" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V40" s="21" t="inlineStr">
+        <is>
+          <t>Limited disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>POSSA</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>Private-sector PF</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G41" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H41" s="21" t="inlineStr">
+        <is>
+          <t>Amharic; English</t>
+        </is>
+      </c>
+      <c r="I41" s="21" t="inlineStr">
+        <is>
+          <t>POSSA</t>
+        </is>
+      </c>
+      <c r="J41" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K41" s="21" t="inlineStr">
+        <is>
+          <t>POESSA/PSSSA materials; Ministry of Finance; NBE/ESE reform documents</t>
+        </is>
+      </c>
+      <c r="L41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P41" s="21" t="inlineStr"/>
+      <c r="Q41" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R41" s="21" t="inlineStr"/>
+      <c r="S41" s="21" t="inlineStr"/>
+      <c r="T41" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U41" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V41" s="21" t="inlineStr">
+        <is>
+          <t>Verify any non-government allocation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>FONSIS</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>SWF (strategic)</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G42" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H42" s="21" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="inlineStr">
+        <is>
+          <t>FONSIS</t>
+        </is>
+      </c>
+      <c r="J42" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K42" s="21" t="inlineStr">
+        <is>
+          <t>CIPRES; FONSIS annual reports; CDC Senegal disclosures</t>
+        </is>
+      </c>
+      <c r="L42" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P42" s="21" t="inlineStr"/>
+      <c r="Q42" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R42" s="21" t="inlineStr"/>
+      <c r="S42" s="21" t="inlineStr"/>
+      <c r="T42" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U42" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V42" s="21" t="inlineStr">
+        <is>
+          <t>Direct equity in hotels, agribusiness, infra; co-invests with DFIs and African PE funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>Gabon</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>FGIS</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>SWF (strategic)</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G43" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H43" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I43" s="21" t="inlineStr">
+        <is>
+          <t>FGIS</t>
+        </is>
+      </c>
+      <c r="J43" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K43" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L43" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P43" s="21" t="inlineStr"/>
+      <c r="Q43" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R43" s="21" t="inlineStr"/>
+      <c r="S43" s="21" t="inlineStr"/>
+      <c r="T43" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U43" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V43" s="21" t="inlineStr">
+        <is>
+          <t>Stakes in Gabonese financial sector and Africa-focused infra platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>Seeded - official/source docs exist, verify latest local-language disclosures</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>Djibouti</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>FSD</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>SWF (strategic)</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G44" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H44" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I44" s="21" t="inlineStr">
+        <is>
+          <t>FSD</t>
+        </is>
+      </c>
+      <c r="J44" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K44" s="21" t="inlineStr">
+        <is>
+          <t>Allocator site; regulator site; ministry or parliamentary filings</t>
+        </is>
+      </c>
+      <c r="L44" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="M44" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="N44" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O44" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P44" s="21" t="inlineStr"/>
+      <c r="Q44" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R44" s="21" t="inlineStr"/>
+      <c r="S44" s="21" t="inlineStr"/>
+      <c r="T44" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U44" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V44" s="21" t="inlineStr">
+        <is>
+          <t>Mandate includes domestic strategic investments and partnerships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>Ithmar Capital</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>SWF (sector-strategic)</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G45" s="21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H45" s="21" t="inlineStr">
+        <is>
+          <t>French; Arabic</t>
+        </is>
+      </c>
+      <c r="I45" s="21" t="inlineStr">
+        <is>
+          <t>Ithmar Capital</t>
+        </is>
+      </c>
+      <c r="J45" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K45" s="21" t="inlineStr">
+        <is>
+          <t>ACAPS; AMMC fund register; CDG/CMR/RCAR annual reports</t>
+        </is>
+      </c>
+      <c r="L45" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P45" s="21" t="inlineStr"/>
+      <c r="Q45" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R45" s="21" t="inlineStr"/>
+      <c r="S45" s="21" t="inlineStr"/>
+      <c r="T45" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U45" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V45" s="21" t="inlineStr">
+        <is>
+          <t>Co-investor with Green Africa Investment, AfDB, Morocco's Mohammed VI Fund.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>Premium Pension</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>PFA</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G46" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H46" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I46" s="21" t="inlineStr">
+        <is>
+          <t>Premium Pension</t>
+        </is>
+      </c>
+      <c r="J46" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K46" s="21" t="inlineStr">
+        <is>
+          <t>PenCom; NSIA annual reports; PFA annual reports where public</t>
+        </is>
+      </c>
+      <c r="L46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P46" s="21" t="inlineStr"/>
+      <c r="Q46" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R46" s="21" t="inlineStr"/>
+      <c r="S46" s="21" t="inlineStr"/>
+      <c r="T46" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U46" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V46" s="21" t="inlineStr">
+        <is>
+          <t>PenCom Multi-Fund Structure permits alts; verify commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>Sigma / Access Pensions</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>PFA</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G47" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H47" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I47" s="21" t="inlineStr">
+        <is>
+          <t>Sigma / Access Pensions</t>
+        </is>
+      </c>
+      <c r="J47" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K47" s="21" t="inlineStr">
+        <is>
+          <t>PenCom; NSIA annual reports; PFA annual reports where public</t>
+        </is>
+      </c>
+      <c r="L47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P47" s="21" t="inlineStr"/>
+      <c r="Q47" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R47" s="21" t="inlineStr"/>
+      <c r="S47" s="21" t="inlineStr"/>
+      <c r="T47" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U47" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V47" s="21" t="inlineStr">
+        <is>
+          <t>Access Holdings ownership; verify intra-group alts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>Tangerine APT Pensions</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="inlineStr">
+        <is>
+          <t>PFA</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G48" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H48" s="21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I48" s="21" t="inlineStr">
+        <is>
+          <t>Tangerine APT Pensions</t>
+        </is>
+      </c>
+      <c r="J48" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K48" s="21" t="inlineStr">
+        <is>
+          <t>PenCom; NSIA annual reports; PFA annual reports where public</t>
+        </is>
+      </c>
+      <c r="L48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P48" s="21" t="inlineStr"/>
+      <c r="Q48" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R48" s="21" t="inlineStr"/>
+      <c r="S48" s="21" t="inlineStr"/>
+      <c r="T48" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U48" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V48" s="21" t="inlineStr">
+        <is>
+          <t>Post-merger entity; verify commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>Not started - official disclosure sweep required</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>Mohammed VI Fund for Investment</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>SWF (strategic)</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G49" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H49" s="21" t="inlineStr">
+        <is>
+          <t>French; Arabic</t>
+        </is>
+      </c>
+      <c r="I49" s="21" t="inlineStr">
+        <is>
+          <t>Mohammed VI Fund for Investment</t>
+        </is>
+      </c>
+      <c r="J49" s="21" t="inlineStr">
+        <is>
+          <t>annual report; audited financial statements; investment policy; portfolio holdings; public fund register; regulator filing</t>
+        </is>
+      </c>
+      <c r="K49" s="21" t="inlineStr">
+        <is>
+          <t>ACAPS; AMMC fund register; CDG/CMR/RCAR annual reports</t>
+        </is>
+      </c>
+      <c r="L49" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="21" t="inlineStr">
+        <is>
+          <t>No - sweep row seeded only</t>
+        </is>
+      </c>
+      <c r="P49" s="21" t="inlineStr"/>
+      <c r="Q49" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R49" s="21" t="inlineStr"/>
+      <c r="S49" s="21" t="inlineStr"/>
+      <c r="T49" s="21" t="inlineStr">
+        <is>
+          <t>Run official-document and local-language query batch; record latest docs checked and add candidate rows where allocator-to-vehicle evidence appears.</t>
+        </is>
+      </c>
+      <c r="U49" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V49" s="21" t="inlineStr">
+        <is>
+          <t>Anchor investor in domestic sectoral funds and PPP platforms.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:V49"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -29827,11 +36416,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>USD ~500m target</t>
+          <t>USD 50m initial (up to USD 200m); fund target USD 500m</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -29856,7 +36445,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Joint pan-African infra fund with Gemcorp.</t>
+          <t>Joint pan-African infra fund announced 9 December 2025. FSDEA seeds with USD 50m (rising to USD 200m subject to conditions); Gemcorp commits up to USD 50m. Fund targets critical minerals, water, food security, energy transition across Africa. Domiciled in Abu Dhabi to tap Gulf institutional capital. Kassai asset management (Walter Pacheco, former Bodiva CEO) launched in late 2025 to mobilise complementary Angolan capital.</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -35230,6 +41819,1008 @@
         </is>
       </c>
       <c r="R98" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Social Security and National Insurance Trust (SSNIT)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Public PF (mandatory)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Actis / Cordiant (co-managed)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Canada Investment Fund for Africa (CIFA)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Private equity</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>2005</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>USD 5.04m (June 2005)</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Allocator disclosure</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>World Bank Ghana PE/VC Ecosystem Study (2016); SSNIT investment disclosures</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>CIFA was a USD 212m pan-African PE fund co-managed by Actis and Cordiant, anchored by the Government of Canada (USD 81m) and CDC (USD 40m). SSNIT committed USD 5.04m in June 2005 -- one of the earliest documented Ghanaian pension LP commitments to an international PE fund. Fund is now liquidated.</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Social Security and National Insurance Trust (SSNIT)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Public PF (mandatory)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Emerging Capital Partners</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ECP Africa Fund III</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Private equity / growth equity</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Not separately disclosed (fund total USD 613m)</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Allocator disclosure / World Bank study</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>World Bank Ghana PE/VC Ecosystem Study (2016); SSNIT investment disclosures</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>ECP Africa Fund III closed at USD 613m in 2008, one of the largest Africa-focused PE funds at the time. SSNIT named as LP in the World Bank 2016 Ghana PE/VC Ecosystem Study. Other DFI LPs include AfDB, IFC, OPIC, and CDC. ECP sought controlling or influential minority positions across financial services, media, insurance, and food processing.</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Social Security and National Insurance Trust (SSNIT)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Public PF (mandatory)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Harith General Partners</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Pan-African Infrastructure Development Fund (PAIDF)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>2007</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Not separately disclosed (fund total USD 625m)</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Allocator disclosure / World Bank study</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>World Bank Ghana PE/VC Ecosystem Study (2016); SSNIT investment disclosures; AfDB project documentation</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>PAIDF commenced operations September 2007 with USD 625m from nine investors including GEPF (via PIC) and AfDB. Invested in energy, transport, and ICT infrastructure across Africa. SSNIT named as LP in World Bank 2016 Ghana PE/VC Ecosystem Study; SSNIT-specific commitment not separately confirmed by fund disclosures. Fund later sold assets to Harith InfraCo for USD 360m (2023).</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Social Security and National Insurance Trust (SSNIT)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Public PF (mandatory)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Fidelity Capital Partners Limited (FCPL)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Fidelity Equity Fund II</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Private equity / SME growth</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Ghana (up to 20% Liberia/Sierra Leone)</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Not separately disclosed</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Allocator disclosure / World Bank study</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>World Bank Ghana PE/VC Ecosystem Study (2016); SIFEM portfolio listing</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Fidelity Equity Fund II invests USD 500k-USD 3.5m in unlisted Ghanaian SMEs, managed by Fidelity Capital Partners Limited (FCPL), Accra. SSNIT named as LP in World Bank 2016 Ghana PE/VC Ecosystem Study. SIFEM (Switzerland) also confirmed as LP per their portfolio disclosure. Vintage estimated ~2012; exact close date not publicly confirmed.</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>SME Finance</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Botswana Public Officers Pension Fund (BPOPF)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Public PF (DB)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Fund LP / Sole anchor (incubation mandate)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Thusano Capital</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Thusano Capital Infrastructure Fund (BPOPF mandate)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>2020</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>BWP 1bn (~USD 71m)</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>BWP</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Manager disclosure</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Thusano Capital website; Business Weekly (BPOPF incubation programme reporting)</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>BPOPF incubation-programme vehicle. Thusano Capital website states explicitly: "specializing in the management of a P1 billion infrastructure fund on behalf of BPOPF." Thusano is 100% citizen-owned and managed. Investment sectors: energy (grid-scale and off-grid), logistics, communications (cell towers, data centres, fibre), agriculture (grain storage, cold chain), and bulk infrastructure/real estate. Geographic focus: Botswana. Same incubation structure as Africa Lighthouse Capital Fund I and Aleyo Capital Fund I (both now graduated). Vintage estimated ~2020; exact close date not publicly disclosed. BPOPF is sole LP. 5th Quarter Investment Managers is a further BPOPF incubation beneficiary but has no named fund or disclosed AUM yet -- flag for future monitoring.</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Infrastructure; Energy; Agriculture / Food Security; Digital / Technology</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Fund LP (Fund of Funds)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>South Suez Capital (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>South Suez Africa Fund (I, II + Managed Accounts)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PE Fund of Funds</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Multiple vintages (2006–2015 est.)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>N$2.75bn (FY2023 market value)</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>NAD</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Annual report</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>GIPF 2023 Annual Report – investment manager table</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Pan-African PE FoF (primaries, secondaries, co-investments in Sub-Saharan African PE). Sub-funds: South Suez Africa Fund I, II and Managed Account I &amp; II. N$2,747,787k at FY2023 = ~USD 151m at 18.2 NAD/USD. Reported current market value, not original commitment.</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Multi-Sector (Pan-African PE)</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Investec Asset Management (now Ninety-One)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Investec Africa Private Equity Fund 2 L.P.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Pan-African (AU member states + Morocco)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>c.2013 (est.)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Undisclosed</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Annual report</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>GIPF 2023 Annual Report – Unlisted Fund Manager descriptions</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>LP in Guernsey-domiciled fund investing in established African businesses (buyouts/growth). Invests across African Union countries and Morocco. Investec Asset Management rebranded as Ninety-One in 2020; fund predates rebrand. Commitment amount not separately disclosed in AR.</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Generalist (Pan-African PE)</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Neoma Capital Partners (formerly Abraaj Group)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Neoma Africa Fund III (B) L.P. (previously Abraaj Africa Fund III)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>c.2014 (est.; original Abraaj vintage)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Undisclosed</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Annual report</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>GIPF 2023 Annual Report – Unlisted Fund Manager descriptions</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Cayman Islands LP providing growth capital to Sub-Saharan Africa portfolio companies. Originally managed by Abraaj Group; renamed/transitioned to Neoma Capital Partners after Abraaj bankruptcy in 2018. Classified by GIPF within its unlisted investment programme.</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Generalist (Sub-Saharan Africa PE)</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Actis Investment Management Limited</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Actis Africa fund (specific fund not named in AR)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Africa (Pan-African)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>N$101.5m (FY2023 market value)</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>NAD</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Annual report</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>GIPF 2023 Annual Report – investment manager table</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Africa Private Equity mandate listed in GIPF FY2023 fund manager table. Current value N$101,534k (~USD 5.6m at 18.2 NAD/USD). Specific fund name not stated; Actis manages multiple Africa-focused vehicles (Africa 3, Energy 4, etc.).</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Multi-Sector</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Growthpoint Properties / Investec</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Growthpoint Investec Africa Properties Limited</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Africa (ex-South Africa): Ghana, Kenya, Morocco, Mozambique, Tanzania, Zambia</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>c.2016 (est.)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Undisclosed</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Annual report</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>GIPF 2023 Annual Report – Unlisted Fund Manager descriptions</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Pan-African real estate fund acquiring income-generating commercial real estate across Africa excluding South Africa. Primary targets: Ghana, Kenya, Morocco, Mozambique, Tanzania, Zambia. Secondary: Angola, Botswana, Côte d'Ivoire, Cameroon, Ethiopia, Gabon, Mauritius, Namibia, Nigeria, Rwanda, Uganda. Disclosed in GIPF unlisted investment programme.</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Commercial Real Estate (Pan-African)</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FONSIS (Senegal)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Sovereign Wealth Fund</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Fund LP / Co-founder</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>I&amp;P (Investisseurs &amp; Partenaires) / Local managers</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Teranga Capital</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Private Equity / Impact</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Domestic (Senegal)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Share of CFA 3.2bn initial close (~USD 5.5m total)</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>XOF</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Fund manager website / press</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Teranga Capital website; IETP fund launch announcement</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>FONSIS is a founding LP/shareholder alongside I&amp;P (via IPDEV2), Sonatel, SG Senegal, and ASKIA Insurance. Fund targets Senegalese SMEs via impact investing. Total initial raise CFA 3.2bn (~USD 5.5m). FONSIS's individual ticket undisclosed. Additional rounds raised since (CFA 2bn in 2025). Fund created 2016.</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>SME Finance / Impact</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
         <is>
           <t>Fund LP</t>
         </is>
@@ -35253,13 +42844,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="16" min="1" max="1"/>
@@ -36723,13 +44314,108 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rwanda Social Security Board (RSSB)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Public PF (mandatory)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pipeline / proposed fund - monitor for close</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Admaius Capital Partners</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Virunga Africa Fund II</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Private equity / growth equity</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pan-Africa (Egypt, Kenya, Morocco, Rwanda, South Africa primary)</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>USD 500m target; IFC proposed USD 25m equity + USD 10m co-investment envelope</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>IFC disclosure / trade press / local press</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>IFC / The New Times / TechInAfrica - Virunga Africa Fund II proposed IFC investment (May-June 2026)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>M-H</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>No public first close or RSSB commitment confirmation as of 5 June 2026; IFC board approval expected 10 June 2026. Keep as pipeline until an official close or named RSSB commitment is disclosed.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://www.newtimes.co.rw/article/36220/news/featured/world-banks-ifc-to-back-admaius-500-million-virunga-africa-fund-ii</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Healthcare; Education; Digital / Technology; Financial Inclusion / Financial Services; FMCG</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Fund LP (prospective)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39714,7 +47400,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40605,7 +48291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42152,212 +49838,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" style="16" min="1" max="1"/>
-    <col width="110" customWidth="1" style="16" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="21.75" customHeight="1" s="16">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Methodology, sources, and important caveats</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="16">
-      <c r="A2" s="6" t="n"/>
-      <c r="B2" s="17" t="n"/>
-    </row>
-    <row r="3" ht="34.5" customHeight="1" s="16">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>All 54 African countries. Allocator universe: sovereign wealth funds (any mandate type) plus pension funds of any kind (public, private, multi-employer, umbrella). Real estate is excluded per scoping; alts of interest are PE/VC, private credit &amp; infrastructure, and direct/co-investments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="16">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="17" t="n"/>
-    </row>
-    <row r="5" ht="34.5" customHeight="1" s="16">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>AUM figures</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>All AUM values are USD-converted approximations and should be treated as order-of-magnitude only. Currency basis (local) and as-of year are noted. Where the institution reports in a local currency, the USD value will move with FX as much as with portfolio performance. Confidence flags reflect source quality, not portfolio performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="16">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="17" t="n"/>
-    </row>
-    <row r="7" ht="34.5" customHeight="1" s="16">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Confidence flags</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>H = High: AUM published in audited annual report or regulator return within last 18 months. M = Medium: AUM from secondary databases, trade press, or older primary disclosure. L = Low: AUM is estimated, dated, or based on indirect inference (e.g., regulatory share of contributions). Low-confidence rows MUST be verified before academic publication.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="16">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="17" t="n"/>
-    </row>
-    <row r="9" ht="57" customHeight="1" s="16">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Universe completeness</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Sovereign wealth funds: substantively complete (Africa has ~22 operational SWFs plus several proposed/planned). Pension funds: covers the largest scheme(s) per country plus the full PFA universe for Nigeria and the major schemes for South Africa, Morocco, and Kenya. Smaller occupational schemes (especially South Africa's ~1,400 registered schemes, Kenya's ~1,300, and Mauritius's standalone corporate schemes) are NOT individually listed — most are too small to make alts commitments. Aggregate AUM for these unlisted schemes is material in SA and Kenya and should be referenced via FSCA and RBA aggregate reports.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="16">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="17" t="n"/>
-    </row>
-    <row r="11" ht="57" customHeight="1" s="16">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Source priorities for verification</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Phase-2 verification should pull, in this order: (1) audited annual reports from each institution's website; (2) regulator returns (FSCA Reg 28, PenCom Q-reports, RBA industry reports, NPRA Ghana, CIPRES bulletins, ACAPS Morocco); (3) SWF databases (SWFI, Global SWF, IFSWF); (4) AVCA/SAVCA/EAVCA LP surveys; (5) trade press (African Private Equity News, Africa Capital Digest, *DealStreetAfrica*). Where access is available: Preqin and PitchBook LP profiles. Document the source URL + access date for each AUM figure before publication.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="16">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="17" t="n"/>
-    </row>
-    <row r="13" ht="68.25" customHeight="1" s="16">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Known limitations</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>1) Several Francophone CIPRES funds and most North African public PFs do not publish portfolio-detail in English; verify via local-language sources. 2) Ethiopian Investment Holdings AUM is the book value of SOE stakes, not investable capital — apples-to-oranges with cash-funded SWFs. 3) South African umbrella DC funds (Sanlam Umbrella, Old Mutual SuperFund, Alexforbes) are intermediaries — alts commitments flow through underlying portfolio managers, not from the umbrella entity directly. 4) Several proposed SWFs (Kenya, Tanzania) and dormant SWFs (Zimbabwe SWFZ) are included for completeness but have no investable capital. 5) Libya's LIA is mostly under UN sanctions; pre-2011 alts holdings are partially documented but unlikely to be acted on currently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="16">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="17" t="n"/>
-    </row>
-    <row r="15" ht="57" customHeight="1" s="16">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Look-through note (CRITICAL)</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Many of the largest African pension pools (notably GEPF in South Africa and the Moroccan parastatal schemes managed by CDG) deploy alts via intermediary asset managers. When attributing alts commitments to allocators, the methodology choice is: (a) attribute to ultimate asset owner (e.g., 'GEPF committed via PIC to Helios IV'), or (b) attribute to the intermediary manager. Default rule for this research is (a) — ultimate asset owner — with the intermediary documented in the same row. This avoids double-counting and is more useful for the academic question of which institutions are deploying capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="17" t="n"/>
-    </row>
-    <row r="17" ht="45.75" customHeight="1" s="16">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Next phase</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Phase 2 (evidence layer) takes this roster, drops below USD 500m, and pursues for each remaining institution: (i) most recent annual report; (ii) regulator filing for the most recent reporting period; (iii) news search for LP mentions in African PE/infra fund closes over the past 7 years; (iv) GP-side disclosure: for each of the ~30 most active African-focused GPs, harvest every disclosed LP mention since 2018.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="16">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>Commitments Database scope (clarified)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="199.5" customHeight="1" s="16">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>The Commitments Database contains ONLY African pension fund and sovereign wealth fund allocator-to-fund-or-deal commitments. It also includes adjacent entities that are functionally allocator-like and integral to the SWF/pension narrative: (i) sovereign governments making direct AFC equity investments (Côte d'Ivoire, Sierra Leone, Egypt) — functionally similar to SWF deployment; (ii) the KEPFIC pension-fund consortium; (iii) categorical 'multiple Nigerian PFAs' / 'Kenyan pension funds' / 'Ghanaian pension funds' cohort entries where the source explicitly identifies pension fund participation but doesn't name individual schemes. 
-DFI catalytic capital providers (FSDAi, Soros Economic Development Fund, FCA Investments, etc.), asset managers acting as intermediaries (Old Mutual IG, Ninety One, Stanbic IMS Ghana, CAL Asset Management Ghana), and commercial banks (Rawbank, Attijariwafa, NIB Egypt) are NOT in the Commitments Database — they appear in the 'Funds &amp; LP Co-Investors' tab as fund-level co-LPs, and in the 'DFI Co-Investor Patterns' tab for frequency analysis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>2026-05-14 inclusion audit</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>Rows now require evidence of actual African PF/SWF participation for the fund/vehicle. DFI-only, planned, expected, targeted, generic LP-base, and MoU-only rows were removed from the fund and commitment fact tables. KEPFIC and AOFSA are retained only as aggregate pooled-mandate archetypes because public sources evidence actual member-fund investments/commitments; individual member-only rows were removed from the Commitments Database. See Inclusion Audit tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Pipeline &amp; Mandates category</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>Targeted/expected/planned rows are separated into the Pipeline &amp; Mandates tab and excluded from the Commitments Database until actual allocator-to-vehicle commitments are publicly evidenced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DFI canonicalization</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>DFI nomenclature is canonicalized for the web app network graph: each DFI has one node even when source text uses variants such as BII/CDC, CDC Group/BII, EIB Global, Findev Canada, FSDAi, or Proparco/FISEA.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A20:B20"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>
--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -44421,7 +44421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -47387,9 +47387,417 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="57" customHeight="1" s="16"/>
-    <row r="45" ht="45.75" customHeight="1" s="16"/>
-    <row r="46" ht="45.75" customHeight="1" s="16"/>
+    <row r="44" ht="57" customHeight="1" s="16">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>South Suez Africa Fund (I, II + Managed Accounts)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>South Suez Capital (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Multiple vintages (2006–2015 est.)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PE Fund of Funds</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>GIPF is the only named African PF/SWF LP disclosed. Pan-African PE FoF investing in primaries, secondaries, and co-investments. GIPF FY2023 market value N$2.75bn (~USD 151m). Source: GIPF 2023 Annual Report p.84.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Multi-Sector (Pan-African PE)</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Fund LP (Fund of Funds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45.75" customHeight="1" s="16">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Investec Africa Private Equity Fund 2 L.P.</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Investec Asset Management (now Ninety-One)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>c.2013 (est.)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pan-African (AU member states + Morocco)</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Guernsey-domiciled LP fund. Invests in established African businesses via buyout/growth transactions. Investec AM rebranded to Ninety-One in 2020. Commitment amount undisclosed; GIPF 2023 AR lists fund in unlisted investment programme (p.96).</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45.75" customHeight="1" s="16">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Neoma Africa Fund III (B) L.P. (previously Abraaj Africa Fund III)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Neoma Capital Partners (formerly Abraaj Group)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>c.2014 (est.; original Abraaj vintage)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Cayman Islands LP. Provides growth capital to Sub-Saharan Africa portfolio companies. Originally managed by Abraaj Group; fund transitioned to Neoma Capital Partners after Abraaj bankruptcy 2018. Source: GIPF 2023 AR p.97.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Actis Africa fund (specific fund not named in AR)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Actis Investment Management Limited</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Africa (Pan-African)</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>GIPF 2023 AR lists Actis IM Ltd with 'Africa Private Equity' mandate; specific fund name not stated. FY2023 market value N$101.5m (~USD 5.6m). Source: GIPF 2023 Annual Report p.84.</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Multi-Sector</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Growthpoint Investec Africa Properties Limited</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Growthpoint Properties / Investec</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>c.2016 (est.)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Africa (ex-South Africa): Ghana, Kenya, Morocco, Mozambique, Tanzania, Zambia</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Government Institutions Pension Fund (GIPF)</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Pan-African commercial real estate fund. Primary targets: Ghana, Kenya, Morocco, Mozambique, Tanzania, Zambia. Secondary: Angola, Botswana, Côte d'Ivoire, Cameroon, Ethiopia, Gabon, Mauritius, Namibia, Nigeria, Rwanda, Uganda. Source: GIPF 2023 AR p.96.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Commercial Real Estate (Pan-African)</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Teranga Capital</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>I&amp;P (Investisseurs &amp; Partenaires) / Local managers</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Private Equity / Impact</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Domestic (Senegal)</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>FONSIS (Senegal)</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>European Union / IFAD</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Sonatel; SG Senegal; ASKIA Insurance</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>FONSIS is a founding LP/shareholder alongside I&amp;P (via IPDEV2), Sonatel, SG Senegal, and ASKIA Insurance. EU is a governmental partner providing co-financing. Fund targets Senegalese SMEs via impact investing. Initial raise CFA 3.2bn (~USD 5.5m). Source: Teranga Capital website.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>SME Finance / Impact</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L46"/>
   <mergeCells count="1">

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -42737,7 +42737,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FONSIS (Senegal)</t>
+          <t>FONSIS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47761,7 +47761,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FONSIS (Senegal)</t>
+          <t>FONSIS</t>
         </is>
       </c>
       <c r="I49" t="n">

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -5784,7 +5784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F236"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -13279,6 +13279,70 @@
       <c r="F234" t="inlineStr">
         <is>
           <t>FONSIS confirmed as founding LP/shareholder in Teranga Capital (2016 impact SME fund, Senegal). Added as row 109.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CDC Gabon (State pension fund of Gabon)</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Fund manager press release</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Amethis Finance – Announces the Creation of Amethis West Africa (AWA)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://amethis.com/en/amethis-finance-announces-the-creation-of-amethis-west-africa/</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>CDC Gabon confirmed as named LP in Amethis West Africa fund (€40-45m, 2014, CIMA zone). Added as Commitments DB row 110.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Caisse Nationale de Prévoyance Sociale (CNPS-CI)</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Third-party report</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire's CNPS Assets Grow from $40M to $2B in 13 Years – Pension Policy International (citing Agence Ecofin)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://www.pensionpolicyinternational.com/cote-divoires-cnps-assets-grow-from-40m-to-2b-in-13-years/</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>CNPS-CI reported to invest in "investment funds such as one launched by Amethis and the Africa50 fund". Specific fund name unconfirmed. Added as Commitments DB row 111 with confidence M.</t>
         </is>
       </c>
     </row>
@@ -32885,7 +32949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R109"/>
+  <dimension ref="A1:R111"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -42821,6 +42885,188 @@
         </is>
       </c>
       <c r="R109" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>CDC Gabon (State pension fund of Gabon)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Gabon</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Civil-service PF</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Amethis Finance</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Amethis West Africa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>CIMA zone (Francophone West &amp; Central Africa)</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>2014</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Amethis West Africa creation announcement</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Named LP alongside BOAD (DFI) and Colina Group (Saham) in Amethis West Africa fund creation press release. First PE fund registered in Francophone Africa; structured under CIMA Code for insurance/pension technical reserves.</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Multi-sector</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Caisse Nationale de Prévoyance Sociale (CNPS-CI)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Amethis Finance</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Amethis fund (unspecified; likely Amethis West Africa)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>CIMA zone / Francophone Africa</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>c.2014 (est.)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Reported / Indirect</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Pension Policy International / Agence Ecofin</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>CNPS-CI reported to have placed assets in "investment funds such as one launched by Amethis and the Africa50 fund" (Agence Ecofin / Pension Policy International). Specific fund name not confirmed; Amethis West Africa most likely given geographic focus on CIMA zone.</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Multi-sector</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
         <is>
           <t>Fund LP</t>
         </is>
@@ -44421,7 +44667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -47793,6 +48039,75 @@
         </is>
       </c>
       <c r="O49" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Amethis West Africa</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Amethis Finance</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D50" t="n">
+        <v>50</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CIMA zone (Francophone West &amp; Central Africa)</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CDC Gabon (State pension fund of Gabon)</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>BOAD (Banque Ouest Africaine de Développement)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Colina Group (Saham)</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>First PE fund registered in Francophone Africa; CIMA Code–eligible structure; CNPS-CI (Côte d'Ivoire) also likely LP (M confidence per Pension Policy International).</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Multi-sector</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
         <is>
           <t>Fund LP</t>
         </is>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -5784,7 +5784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F236"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -13343,6 +13343,166 @@
       <c r="F236" t="inlineStr">
         <is>
           <t>CNPS-CI reported to invest in "investment funds such as one launched by Amethis and the Africa50 fund". Specific fund name unconfirmed. Added as Commitments DB row 111 with confidence M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Multiple (EPPF, KPLC PF, KenGen, CBK, Old Mutual Kenya)</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Industry association press release</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>APSA / Prosper Africa — U.S., Kenyan, and South African Pension Funds Commit Over $94 Million to African Private Equity &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.africapsa.org/news/u-s-kenyan-and-south-african-pension-funds-commit-over-94-million-to-african-private-equity-infrastructure/</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Named African pension LPs in DPI ADP III (EPPF USD 20m, KenGen, Banki Kuu/CBK, Old Mutual Umbrella Kenya) and EKIF (KPLC PF USD 9m). Added as Commitments DB rows 112-116.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Multiple Nigerian PFAs (consortium)</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Fund manager press release</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Chapel Hill Denham — NIDF raises N17.85 billion in sixth capital raise</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://chapelhilldenham.com/nidf-raises-n17-85-billion-in-sixth-capital-raise/</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>22 Nigerian PFAs invested in NIDF across Series 1-6; fund size N58bn (~USD 190m). Added as Commitments DB row 117.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>KEPFIC (Kenya Pension Funds Investment Consortium)</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>DFI case study</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>IFC — Pooling Pensions in Kenya</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://www.ifc.org/en/stories/2023/pooling-pensions-in-kenya</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>KEPFIC USD 11m investment in Acorn Student Accommodation D-REIT; blended return 18.3%. Added as Commitments DB row 118.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Public Officers' Defined Contribution Pension Fund (PODCPF)</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Industry study</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SAVCA / FSD Africa — Pension funds, private equity and private debt in Southern Africa (2022), Lesotho chapter pp.36-37</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://www.fsdafrica.org/wp-content/uploads/2022/08/SAVCA-Pension-fund-Study-22.08.22-2.pdf</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>PODCPF ~3% PE allocation managed by Mergence Lesotho (only PE manager in country). Added as Commitments DB row 119.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Public Officers' Defined Contribution Pension Fund (PODCPF)</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Fund manager website / Trade press</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Mergence Lesotho — Making An Impact; MFW4A — Innovative private equity model for Lesotho</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://www.mfw4a.org/news/innovative-private-equity-model-lesotho</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Corroborates Mergence Lesotho investing on behalf of largest Lesotho pension fund in local infrastructure &amp; development projects (medical agriculture, Maseru property).</t>
         </is>
       </c>
     </row>
@@ -32949,7 +33109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R111"/>
+  <dimension ref="A1:R119"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -43067,6 +43227,730 @@
         </is>
       </c>
       <c r="R111" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Kenya Power &amp; Lighting Co. Pension Fund (KPLC PF)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Occupational PF (parastatal)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Everstrong Capital</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Everstrong Kenya Infrastructure Fund (EKIF)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kenya / East Africa</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>9000000</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>APSA / Prosper Africa MiDA campaign release</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>USD 9m commitment via KEPFIC pioneer membership; part of USD 94m+ U.S.-Kenyan-South African pension campaign facilitated by MiDA Advisors / USAID INVEST. EKIF targets energy, transport, ICT, water, social infrastructure equity in Kenya &amp; East Africa.</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Multi-sector Infrastructure</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Eskom Pension and Provident Fund (EPPF)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Corporate PF (parastatal)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Development Partners International (DPI)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>African Development Partners III (ADP III)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>20000000</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>APSA / Prosper Africa MiDA campaign release</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>USD 20m commitment to DPI ADP III (USD 900m pan-African PE fund). Disclosed in MiDA Advisors / USAID-facilitated institutional investor campaign alongside U.S. public pension funds.</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Multi-sector</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>KenGen Staff Retirement Benefits Scheme</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Occupational PF (parastatal)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Development Partners International (DPI)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>African Development Partners III (ADP III)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>APSA / Prosper Africa MiDA campaign release</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Named investor in DPI ADP III (USD 900m pan-African PE fund) per APSA/Prosper Africa disclosure; amount unspecified. KEPFIC member.</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Multi-sector</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CBK Pension Fund (Kenya, Central Bank of Kenya)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Occupational PF (central bank staff)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Development Partners International (DPI)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>African Development Partners III (ADP III)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>APSA / Prosper Africa MiDA campaign release</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Disclosed as "Banki Kuu Pension Scheme 2021" (Central Bank of Kenya staff scheme) in APSA/Prosper Africa release; named investor in DPI ADP III; amount unspecified. Same institution as AfricInvest FIVE commitment (row 68).</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Multi-sector</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Old Mutual Umbrella Retirement Benefits Scheme (Kenya)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Umbrella retirement scheme</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Development Partners International (DPI)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>African Development Partners III (ADP III)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>APSA / Prosper Africa MiDA campaign release</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Named investor in DPI ADP III per APSA/Prosper Africa disclosure; amount unspecified.</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Multi-sector</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Multiple Nigerian PFAs (consortium)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Private PFAs</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Fund LP (listed infrastructure debt fund)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Chapel Hill Denham</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Nigeria Infrastructure Debt Fund (NIDF)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Infrastructure Debt</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2017-2021 (Series 1-6)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Majority of N58bn (~USD 190m) fund</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>NGN</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Fund manager press release</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Chapel Hill Denham NIDF Series 6 release</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>22 Nigerian PFAs invested across NIDF Series 1-6 capital raises (2 new PFAs in Series 6). NIDF is the first Naira-denominated listed infrastructure debt fund (NGX/FMDQ); pension funds form the large majority of the investor base. Power, digital infra, transport, gas, renewables, social infra.</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Infrastructure Debt</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>KEPFIC (Kenya Pension Funds Investment Consortium)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Pension consortium</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>REIT units (facilitated member commitments)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Acorn Holdings / Acorn Investment Management</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Acorn Student Accommodation D-REIT (ASA D-REIT)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Real Estate (student housing)</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>11000000</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>IFC case study</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>IFC "Pooling Pensions in Kenya" story</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>KEPFIC member funds invested USD 11m in Acorn ASA D-REIT (university student housing development REIT); blended return 18.3% reported by IFC. First KEPFIC-named vehicle-level commitment in DB.</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Student Housing</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Public Officers' Defined Contribution Pension Fund (PODCPF)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Lesotho</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Fund LP / managed account</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Mergence Investment Managers (Lesotho)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Mergence Lesotho unlisted PE &amp; infrastructure portfolio</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Private Equity / Infrastructure</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Lesotho (80% domestic)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>c.2018-ongoing</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>~3% of USD 616m AUM</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Industry study</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>SAVCA/FSD Africa Southern Africa pension study (2022)</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>PODCPF (largest Lesotho PF, USD 616m AUM) allocates ~3% to private equity via Mergence Investment Managers Lesotho — the only PE manager in the country. Investments span healthcare, property, agriculture, infrastructure, SMEs incl. medical agriculture project and Maseru office building. Specific fund vehicle name not publicly disclosed.</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Multi-sector / SME</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
         <is>
           <t>Fund LP</t>
         </is>
@@ -44667,7 +45551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -48108,6 +48992,350 @@
         </is>
       </c>
       <c r="O50" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Everstrong Kenya Infrastructure Fund (EKIF)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Everstrong Capital</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kenya / East Africa</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kenya Power &amp; Lighting Co. Pension Fund (KPLC PF) (USD 9m)</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>U.S. public pension funds (via MiDA Advisors campaign)</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>MiDA Advisors / USAID INVEST-facilitated U.S.-African pension campaign; KEPFIC pioneer-member entry point. Linked to Usahihi Nairobi-Mombasa Expressway pipeline.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Multi-sector Infrastructure</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>African Development Partners III (ADP III)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Development Partners International (DPI)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D52" t="n">
+        <v>900</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Eskom Pension and Provident Fund (EPPF) (USD 20m); KenGen Staff Retirement Benefits Scheme; CBK Pension Fund (Kenya, Central Bank of Kenya); Old Mutual Umbrella Retirement Benefits Scheme (Kenya)</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Chicago Public School Teachers Pension (USD 10m); City of Philadelphia Board of Pensions (USD 50m); City of Hartford Pension Commission (USD 5m)</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Rare case of multiple named African pension LPs in a USD 900m pan-African PE fund, disclosed via MiDA Advisors / USAID INVEST campaign rather than GP press release.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Multi-sector</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Nigeria Infrastructure Debt Fund (NIDF)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Chapel Hill Denham</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D53" t="n">
+        <v>190</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Infrastructure Debt</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>22</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Multiple Nigerian PFAs (22 PFAs across Series 1-6; not individually named)</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>AfDB (USD 10m naira-equivalent)</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>First Naira-denominated listed infrastructure debt fund (NGX/FMDQ). Pension funds are the dominant investor base; 6 capital raises since June 2017.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Infrastructure Debt</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Acorn Student Accommodation D-REIT (ASA D-REIT)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Acorn Holdings / Acorn Investment Management</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D54" t="n">
+        <v>60</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Real Estate (student housing)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>KEPFIC (Kenya Pension Funds Investment Consortium) (USD 11m pooled)</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>InfraCo Africa (development REIT co-investor)</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Kenya first development REIT; KEPFIC pooled pension entry; blended return 18.3% per IFC.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Student Housing</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Mergence Lesotho unlisted PE &amp; infrastructure portfolio</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Mergence Investment Managers (Lesotho)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2018-ongoing</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Private Equity / Infrastructure</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lesotho (80% domestic)</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Public Officers' Defined Contribution Pension Fund (PODCPF)</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Only PE manager licensed in Lesotho; manages PODCPF ~3% unlisted allocation. Healthcare, agriculture, property, SMEs.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Multi-sector / SME</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
         <is>
           <t>Fund LP</t>
         </is>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -46126,7 +46126,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>KPLC Pension Fund (USD 4m, 2014 — 'first East African pension LP in PE'), NMG Pension Fund (USD 1m, 2015 via STANLIB)</t>
+          <t>Kenya Power &amp; Lighting Co. Pension Fund (KPLC PF) (USD 4m, 2014 — 'first East African pension LP in PE'), NMG Pension Fund (USD 1m, 2015 via STANLIB)</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -46201,7 +46201,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>KPLC Pension Fund x2 (likely main + Staff RBS), NMG Pension Fund</t>
+          <t>Kenya Power &amp; Lighting Co. Pension Fund (KPLC PF) x2 (likely main + Staff RBS), NMG Pension Fund</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
@@ -46639,7 +46639,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>CBK Pension Fund Kenya (since Oct 2018 second close)</t>
+          <t>CBK Pension Fund (Kenya, Central Bank of Kenya)</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
@@ -46657,7 +46657,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Evergreen platform; CBK Pension Fund Kenya was first African pension LP in 2018; multiple closes since.</t>
+          <t>Evergreen platform; CBK Pension Fund Kenya was first African pension LP in 2018; multiple closes since. CBK Pension Fund LP since Oct 2018 second close.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -43882,7 +43882,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Fund LP / managed account</t>
+          <t>Investment mandate / managed account</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -43892,7 +43892,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mergence Lesotho unlisted PE &amp; infrastructure portfolio</t>
+          <t>Mergence Lesotho unlisted investment mandate (PE &amp; infrastructure)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>PODCPF (largest Lesotho PF, USD 616m AUM) allocates ~3% to private equity via Mergence Investment Managers Lesotho — the only PE manager in the country. Investments span healthcare, property, agriculture, infrastructure, SMEs incl. medical agriculture project and Maseru office building. Specific fund vehicle name not publicly disclosed.</t>
+          <t>PODCPF (largest Lesotho PF, USD 616m AUM) allocates ~3% to private equity via Mergence Investment Managers Lesotho — the only PE manager in the country. Investments span healthcare, property, agriculture, infrastructure, SMEs incl. medical agriculture project and Maseru office building. Specific fund vehicle name not publicly disclosed. Recorded as a mandate, not a fund vehicle: Mergence manages the allocation via direct unlisted deals; no discrete fund vehicle publicly named.</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -45551,7 +45551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -49268,74 +49268,6 @@
         </is>
       </c>
       <c r="O54" t="inlineStr">
-        <is>
-          <t>Fund LP</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Mergence Lesotho unlisted PE &amp; infrastructure portfolio</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Mergence Investment Managers (Lesotho)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2018-ongoing</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Private Equity / Infrastructure</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Lesotho (80% domestic)</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Public Officers' Defined Contribution Pension Fund (PODCPF)</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Only PE manager licensed in Lesotho; manages PODCPF ~3% unlisted allocation. Healthcare, agriculture, property, SMEs.</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Multi-sector / SME</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
         <is>
           <t>Fund LP</t>
         </is>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -5784,7 +5784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F241"/>
+  <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -5825,6 +5825,11 @@
           <t>Used for</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Source ID</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="23.25" customHeight="1" s="16">
       <c r="A2" s="2" t="inlineStr">
@@ -5857,6 +5862,11 @@
           <t>PIC USD 40m Africa50 investment April 2025</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="16">
       <c r="A3" s="2" t="inlineStr">
@@ -5889,6 +5899,11 @@
           <t>PIC mandate restructuring; alts allocation programme</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>S002</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="23.25" customHeight="1" s="16">
       <c r="A4" s="2" t="inlineStr">
@@ -5921,6 +5936,11 @@
           <t>PIC strategy shift toward private assets; prior R70bn PE allocation</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="23.25" customHeight="1" s="16">
       <c r="A5" s="2" t="inlineStr">
@@ -5953,6 +5973,11 @@
           <t>NSIA latest fund LP investment Feb 2026</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>S004</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="16">
       <c r="A6" s="2" t="inlineStr">
@@ -5985,6 +6010,11 @@
           <t>NSIA AUM and sub-fund structure</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="16">
       <c r="A7" s="2" t="inlineStr">
@@ -6017,6 +6047,11 @@
           <t>AfDB co-financing with NSIA</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="23.25" customHeight="1" s="16">
       <c r="A8" s="2" t="inlineStr">
@@ -6049,6 +6084,11 @@
           <t>GIPF alts portfolio detail (41 managers, 77 funds, 307 companies)</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>S007</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="16">
       <c r="A9" s="2" t="inlineStr">
@@ -6081,6 +6121,11 @@
           <t>GIPF alts portfolio size and structure</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="16">
       <c r="A10" s="2" t="inlineStr">
@@ -6113,6 +6158,11 @@
           <t>Unlisted Investment Policy detail</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>S009</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" s="16">
       <c r="A11" s="2" t="inlineStr">
@@ -6145,6 +6195,11 @@
           <t>Helios CLEAR Fund first close; African pension LPs cited generically</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S010</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="16">
       <c r="A12" s="2" t="inlineStr">
@@ -6177,6 +6232,11 @@
           <t>Helios portfolio and LP composition</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="16">
       <c r="A13" s="2" t="inlineStr">
@@ -6209,6 +6269,11 @@
           <t>NSSF Uganda investment beliefs and alts split</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>S012</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="16">
       <c r="A14" s="2" t="inlineStr">
@@ -6241,6 +6306,11 @@
           <t>NSSF Uganda alts allocation</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" s="16">
       <c r="A15" s="2" t="inlineStr">
@@ -6273,6 +6343,11 @@
           <t>Yield Uganda Investment Fund detail; NSSF Uganda founding LP</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" s="16">
       <c r="A16" s="2" t="inlineStr">
@@ -6305,6 +6380,11 @@
           <t>NSSF Uganda's domestic alts strategy</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>S015</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="16">
       <c r="A17" s="2" t="inlineStr">
@@ -6337,6 +6417,11 @@
           <t>BPOPF alts strategy and target allocation</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="23.25" customHeight="1" s="16">
       <c r="A18" s="2" t="inlineStr">
@@ -6369,6 +6454,11 @@
           <t>BPOPF Aleyo Capital and Africa Lighthouse 2017 commitments</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.25" customHeight="1" s="16">
       <c r="A19" s="2" t="inlineStr">
@@ -6401,6 +6491,11 @@
           <t>Southern African pension PE/PD allocation study; BPOPF, GIPF, GEPF coverage</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23.25" customHeight="1" s="16">
       <c r="A20" s="2" t="inlineStr">
@@ -6433,6 +6528,11 @@
           <t>FSDEA-Gemcorp pan-African infra fund partnership</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>S019</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="16">
       <c r="A21" s="2" t="inlineStr">
@@ -6465,6 +6565,11 @@
           <t>FSDEA AUM and portfolio</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>S020</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="16">
       <c r="A22" s="2" t="inlineStr">
@@ -6497,6 +6602,11 @@
           <t>FSDEA governance, disclosure and investment policy</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>S021</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="23.25" customHeight="1" s="16">
       <c r="A23" s="2" t="inlineStr">
@@ -6529,6 +6639,11 @@
           <t>FSDEA reset toward alternative assets</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>S022</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="16">
       <c r="A24" s="2" t="inlineStr">
@@ -6561,6 +6676,11 @@
           <t>TSFE press releases and portfolio detail</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>S023</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="16">
       <c r="A25" s="2" t="inlineStr">
@@ -6593,6 +6713,11 @@
           <t>TSFE sub-fund structure and co-investment model</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>S024</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="16">
       <c r="A26" s="2" t="inlineStr">
@@ -6625,6 +6750,11 @@
           <t>Oyass Capital as FONSIS/KfW/World Bank-backed SME fund/financing vehicle; management mandate awarded to SEAF</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>S025</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="23.25" customHeight="1" s="16">
       <c r="A27" s="2" t="inlineStr">
@@ -6657,6 +6787,11 @@
           <t>FONSIS strategic-investment model</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>S026</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="23.25" customHeight="1" s="16">
       <c r="A28" s="2" t="inlineStr">
@@ -6689,6 +6824,11 @@
           <t>CDG Invest funds (Fipar-Holding, Nama, CapMezzanine III, InfraMaroc)</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>S027</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="23.25" customHeight="1" s="16">
       <c r="A29" s="2" t="inlineStr">
@@ -6721,6 +6861,11 @@
           <t>CDG / Fipar-Holding 2024 cross-border investment</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S028</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="23.25" customHeight="1" s="16">
       <c r="A30" s="2" t="inlineStr">
@@ -6753,6 +6898,11 @@
           <t>Mediterrania Capital IV LP composition (CDP, not CDG, but useful for tracking)</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S029</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="34.5" customHeight="1" s="16">
       <c r="A31" s="2" t="inlineStr">
@@ -6785,6 +6935,11 @@
           <t>ARM-Harith ACT Fund; designed to unlock Nigerian pension LPs</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S030</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="23.25" customHeight="1" s="16">
       <c r="A32" s="2" t="inlineStr">
@@ -6817,6 +6972,11 @@
           <t>ARM-Harith ACT Fund structure for pension FX risk mitigation</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S031</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="16">
       <c r="A33" s="2" t="inlineStr">
@@ -6849,6 +7009,11 @@
           <t>EPPF alts allocation; 10%+ to alternatives, ~4% to PE</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S032</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="23.25" customHeight="1" s="16">
       <c r="A34" s="2" t="inlineStr">
@@ -6881,6 +7046,11 @@
           <t>EPPF strategy direction and PE allocation</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S033</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="16">
       <c r="A35" s="2" t="inlineStr">
@@ -6913,6 +7083,11 @@
           <t>SSNIT portfolio composition; alts share</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S034</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="16">
       <c r="A36" s="2" t="inlineStr">
@@ -6945,6 +7120,11 @@
           <t>SSNIT 2024 rebalancing announcement</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S035</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="23.25" customHeight="1" s="16">
       <c r="A37" s="2" t="inlineStr">
@@ -6977,6 +7157,11 @@
           <t>Nigerian PFA investment limits including alts</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S036</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="16">
       <c r="A38" s="2" t="inlineStr">
@@ -7009,6 +7194,11 @@
           <t>Nigerian PFA aggregate portfolio composition</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S037</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="16">
       <c r="A39" s="2" t="inlineStr">
@@ -7041,6 +7231,11 @@
           <t>Industry LP survey aggregates</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S038</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="23.25" customHeight="1" s="16">
       <c r="A40" s="2" t="inlineStr">
@@ -7073,6 +7268,11 @@
           <t>African PE/VC deal and fundraising data</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S039</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="16">
       <c r="A41" s="2" t="inlineStr">
@@ -7105,6 +7305,11 @@
           <t>NSSF Kenya asset mix; PE allocation 597.8% YoY growth</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S040</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="16">
       <c r="A42" s="2" t="inlineStr">
@@ -7137,6 +7342,11 @@
           <t>Kenya pension industry aggregate composition</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>S041</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="16">
       <c r="A43" s="2" t="inlineStr">
@@ -7169,6 +7379,11 @@
           <t>Kenya retirement benefits industry composition</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S042</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="23.25" customHeight="1" s="16">
       <c r="A44" s="2" t="inlineStr">
@@ -7201,6 +7416,11 @@
           <t>Kenyan regulatory framework for pension PE/VC</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S043</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="23.25" customHeight="1" s="16">
       <c r="A45" s="2" t="inlineStr">
@@ -7233,6 +7453,11 @@
           <t>NSSF MD David Koros statements on PE prioritisation</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S044</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="23.25" customHeight="1" s="16">
       <c r="A46" s="2" t="inlineStr">
@@ -7265,6 +7490,11 @@
           <t>POESSA 2022 statutory liberalisation</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S045</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="16">
       <c r="A47" s="2" t="inlineStr">
@@ -7297,6 +7527,11 @@
           <t>Ethiopian pension regulatory environment</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S046</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="34.5" customHeight="1" s="16">
       <c r="A48" s="2" t="inlineStr">
@@ -7329,6 +7564,11 @@
           <t>Recent actuarial dissemination for the two Ethiopian SSAs</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S047</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="16">
       <c r="A49" s="2" t="inlineStr">
@@ -7361,6 +7601,11 @@
           <t>PSSSF investment guidelines reference</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S048</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="16">
       <c r="A50" s="2" t="inlineStr">
@@ -7393,6 +7638,11 @@
           <t>PSSSF–TADB direct partnership instead of fund LP</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S049</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="23.25" customHeight="1" s="16">
       <c r="A51" s="2" t="inlineStr">
@@ -7425,6 +7675,11 @@
           <t>Egyptian pension regulatory constraint (1% capital-market cap; surplus-to-NIB rule)</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S050</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="16">
       <c r="A52" s="2" t="inlineStr">
@@ -7457,6 +7712,11 @@
           <t>NOSI structure and scope</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S051</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="23.25" customHeight="1" s="16">
       <c r="A53" s="2" t="inlineStr">
@@ -7489,6 +7749,11 @@
           <t>Reg 28 PE cap raised from 10% to 15% effective Jan 2023</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S052</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="16">
       <c r="A54" s="2" t="inlineStr">
@@ -7521,6 +7786,11 @@
           <t>Industry interpretation of Reg 28 changes</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S053</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="16">
       <c r="A55" s="2" t="inlineStr">
@@ -7553,6 +7823,11 @@
           <t>Detailed Reg 28 breakdown</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S054</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="23.25" customHeight="1" s="16">
       <c r="A56" s="2" t="inlineStr">
@@ -7585,6 +7860,11 @@
           <t>Pre-2025 PenCom regulation</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S055</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="23.25" customHeight="1" s="16">
       <c r="A57" s="2" t="inlineStr">
@@ -7617,6 +7897,11 @@
           <t>Coverage of PenCom 2025 revision</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S056</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="23.25" customHeight="1" s="16">
       <c r="A58" s="2" t="inlineStr">
@@ -7649,6 +7934,11 @@
           <t>PenCom Feb 2026 addendum to investment regulation</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S057</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="23.25" customHeight="1" s="16">
       <c r="A59" s="2" t="inlineStr">
@@ -7681,6 +7971,11 @@
           <t>URBRA investment guidelines and PE 15% cap in EAC</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S058</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="23.25" customHeight="1" s="16">
       <c r="A60" s="2" t="inlineStr">
@@ -7713,6 +8008,11 @@
           <t>Uganda retirement assets reached UGX 30tn</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S059</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="16">
       <c r="A61" s="2" t="inlineStr">
@@ -7745,6 +8045,11 @@
           <t>URBRA regulatory framework</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S060</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="16">
       <c r="A62" s="2" t="inlineStr">
@@ -7777,6 +8082,11 @@
           <t>Namibian Reg 28/29 statutory text</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S061</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="23.25" customHeight="1" s="16">
       <c r="A63" s="2" t="inlineStr">
@@ -7809,6 +8119,11 @@
           <t>Interpretation of Reg 28: 35% min domestic; 3.5% max via SPV</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S062</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="23.25" customHeight="1" s="16">
       <c r="A64" s="2" t="inlineStr">
@@ -7841,6 +8156,11 @@
           <t>Detailed analysis of Namibia's mandated-unlisted regime</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S063</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="23.25" customHeight="1" s="16">
       <c r="A65" s="2" t="inlineStr">
@@ -7873,6 +8193,11 @@
           <t>Ghanaian pension regulatory framework; 10% alts sub-asset cap</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S064</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="23.25" customHeight="1" s="16">
       <c r="A66" s="2" t="inlineStr">
@@ -7905,6 +8230,11 @@
           <t>Critique of Ghana pension investment guidelines</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S065</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="23.25" customHeight="1" s="16">
       <c r="A67" s="2" t="inlineStr">
@@ -7937,6 +8267,11 @@
           <t>Botswana PFR2: 15% VC/PE, 50% minimum domestic by Dec 2027</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S066</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="23.25" customHeight="1" s="16">
       <c r="A68" s="2" t="inlineStr">
@@ -7969,6 +8304,11 @@
           <t>Botswana pension and capital markets context</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S067</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="16">
       <c r="A69" s="2" t="inlineStr">
@@ -8001,6 +8341,11 @@
           <t>Industry view on Botswana pension reforms</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S068</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="16">
       <c r="A70" s="2" t="inlineStr">
@@ -8033,6 +8378,11 @@
           <t>Moroccan pension regulatory framework</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S069</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="16">
       <c r="A71" s="2" t="inlineStr">
@@ -8065,6 +8415,11 @@
           <t>ACAPS supervisory scope</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S070</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="23.25" customHeight="1" s="16">
       <c r="A72" s="2" t="inlineStr">
@@ -8097,6 +8452,11 @@
           <t>AVCA 2024 aggregate; African investor share 14%→19%, $171m→$639m</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S071</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="23.25" customHeight="1" s="16">
       <c r="A73" s="2" t="inlineStr">
@@ -8129,6 +8489,11 @@
           <t>Aggregate trend analysis</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S072</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="16">
       <c r="A74" s="2" t="inlineStr">
@@ -8161,6 +8526,11 @@
           <t>Industry sentiment on African LP participation</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S073</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="16">
       <c r="A75" s="2" t="inlineStr">
@@ -8193,6 +8563,11 @@
           <t>NSSF Uganda 80%/13.3%/6.2% strategic asset allocation</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S074</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="34.5" customHeight="1" s="16">
       <c r="A76" s="2" t="inlineStr">
@@ -8225,6 +8600,11 @@
           <t>Axis Pension Trust USD 5m commitment to BII's GIP platform</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S075</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="23.25" customHeight="1" s="16">
       <c r="A77" s="2" t="inlineStr">
@@ -8257,6 +8637,11 @@
           <t>Coverage of Axis–Norfund commitment to GIP; first Ghanaian pension capital under 5% alts rule</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S076</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="23.25" customHeight="1" s="16">
       <c r="A78" s="2" t="inlineStr">
@@ -8289,6 +8674,11 @@
           <t>Joint USD 20m commitment headline detail</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S077</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="23.25" customHeight="1" s="16">
       <c r="A79" s="2" t="inlineStr">
@@ -8321,6 +8711,11 @@
           <t>Ghana media coverage</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S078</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="23.25" customHeight="1" s="16">
       <c r="A80" s="2" t="inlineStr">
@@ -8353,6 +8748,11 @@
           <t>Industry coverage</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S079</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="23.25" customHeight="1" s="16">
       <c r="A81" s="2" t="inlineStr">
@@ -8385,6 +8785,11 @@
           <t>Ci Gaba FoF first close; LP composition incl. Axis, Enterprise, Stanbic IMS, CAL AM, FSDAi, Small Foundation, FMO</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S080</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="16">
       <c r="A82" s="2" t="inlineStr">
@@ -8417,6 +8822,11 @@
           <t>Ci Gaba FoF manager profile</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S081</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="23.25" customHeight="1" s="16">
       <c r="A83" s="2" t="inlineStr">
@@ -8449,6 +8859,11 @@
           <t>CNPS Cameroon shareholder accession</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S082</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="23.25" customHeight="1" s="16">
       <c r="A84" s="2" t="inlineStr">
@@ -8481,6 +8896,11 @@
           <t>GIIF Ghana, Sierra Leone govt, Seychelles Pension Fund — USD 35.5m group commitment</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S083</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="23.25" customHeight="1" s="16">
       <c r="A85" s="2" t="inlineStr">
@@ -8513,6 +8933,11 @@
           <t>Côte d'Ivoire, Mauritius NPF/NSF, Africa Re</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S084</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="23.25" customHeight="1" s="16">
       <c r="A86" s="2" t="inlineStr">
@@ -8545,6 +8970,11 @@
           <t>Egypt government AFC accession (2024)</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S085</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="34.5" customHeight="1" s="16">
       <c r="A87" s="2" t="inlineStr">
@@ -8577,6 +9007,11 @@
           <t>Rawbank DRC AFC shareholding</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S086</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="16">
       <c r="A88" s="2" t="inlineStr">
@@ -8609,6 +9044,11 @@
           <t>Complete AFC shareholder roster</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S087</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="23.25" customHeight="1" s="16">
       <c r="A89" s="2" t="inlineStr">
@@ -8641,6 +9081,11 @@
           <t>Africa50-IAF LP roster: NSIA, CDC Sénégal, CDC Benin, CNSS Togo, CDG Invest, Attijariwafa, etc.</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S088</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="23.25" customHeight="1" s="16">
       <c r="A90" s="2" t="inlineStr">
@@ -8673,6 +9118,11 @@
           <t>AfDB framing of Africa50-IAF</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S089</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="23.25" customHeight="1" s="16">
       <c r="A91" s="2" t="inlineStr">
@@ -8705,6 +9155,11 @@
           <t>IFC participation in Africa50-IAF</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S090</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="23.25" customHeight="1" s="16">
       <c r="A92" s="2" t="inlineStr">
@@ -8737,6 +9192,11 @@
           <t>Africa50 AUM milestone</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S091</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="23.25" customHeight="1" s="16">
       <c r="A93" s="2" t="inlineStr">
@@ -8769,6 +9229,11 @@
           <t>CBK Pension Fund Kenya commitment to AfricInvest FIVE</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S092</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="23.25" customHeight="1" s="16">
       <c r="A94" s="2" t="inlineStr">
@@ -8801,6 +9266,11 @@
           <t>Direct allocator-side source</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S093</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="16">
       <c r="A95" s="2" t="inlineStr">
@@ -8833,6 +9303,11 @@
           <t>Confirmation of continuing LP composition</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S094</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="23.25" customHeight="1" s="16">
       <c r="A96" s="2" t="inlineStr">
@@ -8865,6 +9340,11 @@
           <t>AfDB participation in FIVE</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S095</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="23.25" customHeight="1" s="16">
       <c r="A97" s="2" t="inlineStr">
@@ -8897,6 +9377,11 @@
           <t>NAPSA Zambia USD 17.5m commitment to GIP Zambia</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S096</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="23.25" customHeight="1" s="16">
       <c r="A98" s="2" t="inlineStr">
@@ -8929,6 +9414,11 @@
           <t>Swedish DFI side disclosure</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>S097</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="16">
       <c r="A99" s="2" t="inlineStr">
@@ -8961,6 +9451,11 @@
           <t>NAPSA-side disclosure</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>S098</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="16">
       <c r="A100" s="2" t="inlineStr">
@@ -8993,6 +9488,11 @@
           <t>FSDAi USD 7.5m commitment to Ci-Gaba</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>S099</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="16">
       <c r="A101" s="2" t="inlineStr">
@@ -9025,6 +9525,11 @@
           <t>FSDAi cumulative portfolio summary</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>S100</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="16">
       <c r="A102" s="2" t="inlineStr">
@@ -9057,6 +9562,11 @@
           <t>BII's $30m commitment to Catalyst Fund II</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>S101</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="23.25" customHeight="1" s="16">
       <c r="A103" s="2" t="inlineStr">
@@ -9089,6 +9599,11 @@
           <t>Catalyst Fund II close detail including LP composition reference</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>S102</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="23.25" customHeight="1" s="16">
       <c r="A104" s="2" t="inlineStr">
@@ -9121,6 +9636,11 @@
           <t>Adenia V close; LP categories include PIC and Kenyan/Ghanaian pension funds</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>S103</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="23.25" customHeight="1" s="16">
       <c r="A105" s="2" t="inlineStr">
@@ -9153,6 +9673,11 @@
           <t>Coverage of Adenia V LP roster</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>S104</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="16">
       <c r="A106" s="2" t="inlineStr">
@@ -9185,6 +9710,11 @@
           <t>KEPFIC consortium overview</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>S105</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="16">
       <c r="A107" s="2" t="inlineStr">
@@ -9217,6 +9747,11 @@
           <t>KEPFIC formation history, structure and 24-member scale</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>S106</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="23.25" customHeight="1" s="16">
       <c r="A108" s="2" t="inlineStr">
@@ -9249,6 +9784,11 @@
           <t>USAID-backed KEPFIC infra investment mandate</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>S107</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="23.25" customHeight="1" s="16">
       <c r="A109" s="2" t="inlineStr">
@@ -9281,6 +9821,11 @@
           <t>Fund Managers Association of Kenya MOU with KEPFIC on alts</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>S108</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="34.5" customHeight="1" s="16">
       <c r="A110" s="2" t="inlineStr">
@@ -9313,6 +9858,11 @@
           <t>OECD analysis of African pension/insurance institutional investor role</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>S109</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="23.25" customHeight="1" s="16">
       <c r="A111" s="2" t="inlineStr">
@@ -9345,6 +9895,11 @@
           <t>European DFI fund; African LPs not named</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>S110</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="23.25" customHeight="1" s="16">
       <c r="A112" s="2" t="inlineStr">
@@ -9377,6 +9932,11 @@
           <t>Adenia AEF first close; smaller fund alongside Adenia V</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>S111</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="16">
       <c r="A113" s="2" t="inlineStr">
@@ -9409,6 +9969,11 @@
           <t>Aggregate analysis on African LP participation</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>S112</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="23.25" customHeight="1" s="16">
       <c r="A114" s="2" t="inlineStr">
@@ -9441,6 +10006,11 @@
           <t>NMG Pension Fund $1m via STANLIB Kenya to ARVF I; KPLC PF $4m at first close (first East African pension LP)</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>S113</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="16">
       <c r="A115" s="2" t="inlineStr">
@@ -9473,6 +10043,11 @@
           <t>Ascent Africa firm profile</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>S114</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="16">
       <c r="A116" s="2" t="inlineStr">
@@ -9505,6 +10080,11 @@
           <t>ARVF II first close LP composition</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>S115</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="16">
       <c r="A117" s="2" t="inlineStr">
@@ -9537,6 +10117,11 @@
           <t>IFC commitment + co-investors detail</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>S116</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="23.25" customHeight="1" s="16">
       <c r="A118" s="2" t="inlineStr">
@@ -9569,6 +10154,11 @@
           <t>ARVF II fundraising context</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>S117</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="23.25" customHeight="1" s="16">
       <c r="A119" s="2" t="inlineStr">
@@ -9601,6 +10191,11 @@
           <t>Helios CLEAR Fund first close LP roster</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>S118</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="16">
       <c r="A120" s="2" t="inlineStr">
@@ -9633,6 +10228,11 @@
           <t>BII USD 20m to Helios CLEAR</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>S119</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="16">
       <c r="A121" s="2" t="inlineStr">
@@ -9665,6 +10265,11 @@
           <t>EIB investment in Helios CLEAR</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>S120</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="23.25" customHeight="1" s="16">
       <c r="A122" s="2" t="inlineStr">
@@ -9697,6 +10302,11 @@
           <t>SIFEM co-anchor commitment</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="23.25" customHeight="1" s="16">
       <c r="A123" s="2" t="inlineStr">
@@ -9729,6 +10339,11 @@
           <t>EIB Helios V commitment</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="23.25" customHeight="1" s="16">
       <c r="A124" s="2" t="inlineStr">
@@ -9761,6 +10376,11 @@
           <t>ADP IV first close detail</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>S123</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="16">
       <c r="A125" s="2" t="inlineStr">
@@ -9793,6 +10413,11 @@
           <t>IFC ADP IV disclosure</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>S124</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="16">
       <c r="A126" s="2" t="inlineStr">
@@ -9825,6 +10450,11 @@
           <t>Proparco USD 42m commitment to ADP IV</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>S125</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="23.25" customHeight="1" s="16">
       <c r="A127" s="2" t="inlineStr">
@@ -9857,6 +10487,11 @@
           <t>Phatisa PFF3 LP roster</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>S126</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="23.25" customHeight="1" s="16">
       <c r="A128" s="2" t="inlineStr">
@@ -9889,6 +10524,11 @@
           <t>Vantage IV Pan-African sub-fund EIB participation</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>S127</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="23.25" customHeight="1" s="16">
       <c r="A129" s="2" t="inlineStr">
@@ -9921,6 +10561,11 @@
           <t>BII Vantage IV commitment</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>S128</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="16">
       <c r="A130" s="2" t="inlineStr">
@@ -9953,6 +10598,11 @@
           <t>Swedfund Vantage IV commitment</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>S129</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="23.25" customHeight="1" s="16">
       <c r="A131" s="2" t="inlineStr">
@@ -9985,6 +10635,11 @@
           <t>Vantage IV close + LP narrative incl. 'Southern African pension funds'</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>S130</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="23.25" customHeight="1" s="16">
       <c r="A132" s="2" t="inlineStr">
@@ -10017,6 +10672,11 @@
           <t>IFC Vantage commitment</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>S131</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="23.25" customHeight="1" s="16">
       <c r="A133" s="2" t="inlineStr">
@@ -10049,6 +10709,11 @@
           <t>Verod-Kepple Africa VC Fund I close</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>S132</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="34.5" customHeight="1" s="16">
       <c r="A134" s="2" t="inlineStr">
@@ -10081,6 +10746,11 @@
           <t>Comprehensive named LP list: Blue Earth, Bpifrance, Casey Family, DEG, DFC, EIB, FMO, IFC, Norfund, Findev Canada, PIC, Proparco, SIFEM, South Suez Capital</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>S133</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="16">
       <c r="A135" s="2" t="inlineStr">
@@ -10113,6 +10783,11 @@
           <t>IFC Adenia V SII</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>S134</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="16">
       <c r="A136" s="2" t="inlineStr">
@@ -10145,6 +10820,11 @@
           <t>Civil-society tracking of IFC project</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>S135</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="23.25" customHeight="1" s="16">
       <c r="A137" s="2" t="inlineStr">
@@ -10177,6 +10857,11 @@
           <t>IFC USD 75m commitment to ADP IV; up to 20% of total; USD 50m co-invest envelope. Target USD 1bn.</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>S136</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="16">
       <c r="A138" s="2" t="inlineStr">
@@ -10209,6 +10894,11 @@
           <t>IFC commitment to Vantage IV</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>S137</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="23.25" customHeight="1" s="16">
       <c r="A139" s="2" t="inlineStr">
@@ -10241,6 +10931,11 @@
           <t>Vantage Mezz IV USD 377m final close</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>S138</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="23.25" customHeight="1" s="16">
       <c r="A140" s="2" t="inlineStr">
@@ -10273,6 +10968,11 @@
           <t>NSIA confirmation as FAFIN LP; LPs: AfDB, CDC/BII, DGGF, NSIA</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>S139</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="23.25" customHeight="1" s="16">
       <c r="A141" s="2" t="inlineStr">
@@ -10305,6 +11005,11 @@
           <t>Sahel Capital fund family</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>S140</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="16">
       <c r="A142" s="2" t="inlineStr">
@@ -10337,6 +11042,11 @@
           <t>BII/CDC commitment to FAFIN</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>S141</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="23.25" customHeight="1" s="16">
       <c r="A143" s="2" t="inlineStr">
@@ -10369,6 +11079,11 @@
           <t>NGN 75bn fund; eligible investors include pension funds; Stanbic IBTC in partner consortium</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>S142</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="34.5" customHeight="1" s="16">
       <c r="A144" s="2" t="inlineStr">
@@ -10401,6 +11116,11 @@
           <t>Yield Uganda full LP list: EU/IFAD, NSSF Uganda (EUR 2m), FCA Investments, Soros Economic Development Fund; total EUR 20m</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>S143</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="23.25" customHeight="1" s="16">
       <c r="A145" s="2" t="inlineStr">
@@ -10433,6 +11153,11 @@
           <t>EU/IFAD EUR 10m + NSSF Uganda EUR 2m founding</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>S144</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="23.25" customHeight="1" s="16">
       <c r="A146" s="2" t="inlineStr">
@@ -10465,6 +11190,11 @@
           <t>ACA history; CAPE I-IV; &gt;USD 1bn cumulative; championed Nigerian pension PE inclusion</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>S145</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="23.25" customHeight="1" s="16">
       <c r="A147" s="2" t="inlineStr">
@@ -10497,6 +11227,11 @@
           <t>ACA narrative and PE-pension history in Nigeria</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>S146</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="16">
       <c r="A148" s="2" t="inlineStr">
@@ -10529,6 +11264,11 @@
           <t>BII commitment to CAPE IV</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>S147</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="16">
       <c r="A149" s="2" t="inlineStr">
@@ -10561,6 +11301,11 @@
           <t>KEPFIC founding and US/USAID support</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>S148</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="23.25" customHeight="1" s="16">
       <c r="A150" s="2" t="inlineStr">
@@ -10593,6 +11338,11 @@
           <t>KEPFIC investment plan launch</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>S149</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="23.25" customHeight="1" s="16">
       <c r="A151" s="2" t="inlineStr">
@@ -10625,6 +11375,11 @@
           <t>KEPFIC member context</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>S150</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="23.25" customHeight="1" s="16">
       <c r="A152" s="2" t="inlineStr">
@@ -10657,6 +11412,11 @@
           <t>KEPFIC progress coverage</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>S151</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="15" customHeight="1" s="16">
       <c r="A153" s="2" t="inlineStr">
@@ -10689,6 +11449,11 @@
           <t>Adenia AEF first close $180m</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>S152</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="23.25" customHeight="1" s="16">
       <c r="A154" s="2" t="inlineStr">
@@ -10721,6 +11486,11 @@
           <t>RSSB USD 30m anchor + USD 3m TA seed to Enko Capital Rwanda SME Growth Fund</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>S153</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="23.25" customHeight="1" s="16">
       <c r="A155" s="2" t="inlineStr">
@@ -10753,6 +11523,11 @@
           <t>Coverage of RSSB-Enko commitment</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>S154</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="23.25" customHeight="1" s="16">
       <c r="A156" s="2" t="inlineStr">
@@ -10785,6 +11560,11 @@
           <t>Local Rwandan coverage of RSSB SME Growth Fund</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>S155</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="15" customHeight="1" s="16">
       <c r="A157" s="2" t="inlineStr">
@@ -10817,6 +11597,11 @@
           <t>AOFSA launch announcement; founding member context</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>S156</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="16">
       <c r="A158" s="2" t="inlineStr">
@@ -10849,6 +11634,11 @@
           <t>Batseta secretariat / AOFSA detail</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>S157</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="15" customHeight="1" s="16">
       <c r="A159" s="2" t="inlineStr">
@@ -10881,6 +11671,11 @@
           <t>MiDA technical assistance to AOFSA</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>S158</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="23.25" customHeight="1" s="16">
       <c r="A160" s="2" t="inlineStr">
@@ -10913,6 +11708,11 @@
           <t>AOFSA founding member coverage</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>S159</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="23.25" customHeight="1" s="16">
       <c r="A161" s="2" t="inlineStr">
@@ -10945,6 +11745,11 @@
           <t>AOFSA exceeded R3.75bn target in first year</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>S160</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="23.25" customHeight="1" s="16">
       <c r="A162" s="2" t="inlineStr">
@@ -10977,6 +11782,11 @@
           <t>AOFSA member coverage</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>S161</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="23.25" customHeight="1" s="16">
       <c r="A163" s="2" t="inlineStr">
@@ -11009,6 +11819,11 @@
           <t>Prosper Africa / USAID context for KEPFIC + AOFSA</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>S162</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="23.25" customHeight="1" s="16">
       <c r="A164" s="2" t="inlineStr">
@@ -11041,6 +11856,11 @@
           <t>African Pension Supervisors Association coverage</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>S163</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="23.25" customHeight="1" s="16">
       <c r="A165" s="2" t="inlineStr">
@@ -11073,6 +11893,11 @@
           <t>CrossBoundary advisory engagement with AOFSA</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>S164</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="23.25" customHeight="1" s="16">
       <c r="A166" s="2" t="inlineStr">
@@ -11105,6 +11930,11 @@
           <t>Mirepa initial close detail; LPs: Petra Trust, Axis Pensions, CAMCOL schemes, VCTF</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>S165</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="23.25" customHeight="1" s="16">
       <c r="A167" s="2" t="inlineStr">
@@ -11137,6 +11967,11 @@
           <t>Mirepa LP composition</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>S166</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="23.25" customHeight="1" s="16">
       <c r="A168" s="2" t="inlineStr">
@@ -11169,6 +12004,11 @@
           <t>Ghanaian local-LP-only model</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>S167</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="23.25" customHeight="1" s="16">
       <c r="A169" s="2" t="inlineStr">
@@ -11201,6 +12041,11 @@
           <t>VCTF lead role</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>S168</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="23.25" customHeight="1" s="16">
       <c r="A170" s="2" t="inlineStr">
@@ -11233,6 +12078,11 @@
           <t>Injaro Ghana VC Fund first close</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>S169</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="23.25" customHeight="1" s="16">
       <c r="A171" s="2" t="inlineStr">
@@ -11265,6 +12115,11 @@
           <t>IGVCF GHS 216m final close, first Ghana fund anchored by local pensions</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>S170</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="15" customHeight="1" s="16">
       <c r="A172" s="2" t="inlineStr">
@@ -11297,6 +12152,11 @@
           <t>IGVCF profile</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>S171</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="23.25" customHeight="1" s="16">
       <c r="A173" s="2" t="inlineStr">
@@ -11329,6 +12189,11 @@
           <t>AVCA coverage of IGVCF close</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>S172</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="23.25" customHeight="1" s="16">
       <c r="A174" s="2" t="inlineStr">
@@ -11361,6 +12226,11 @@
           <t>NSSF Uganda planned FoF: USD 15m+ anchor, USD 100m target, before March 2026 launch</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>S173</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="23.25" customHeight="1" s="16">
       <c r="A175" s="2" t="inlineStr">
@@ -11393,6 +12263,11 @@
           <t>Enko Capital profile context (linked via FSDA press release)</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>S174</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="23.25" customHeight="1" s="16">
       <c r="A176" s="2" t="inlineStr">
@@ -11425,6 +12300,11 @@
           <t>USAID INVEST framing of KEPFIC + AOFSA</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>S175</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="23.25" customHeight="1" s="16">
       <c r="A177" s="2" t="inlineStr">
@@ -11457,6 +12337,11 @@
           <t>KEPFIC formation detail</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>S176</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="23.25" customHeight="1" s="16">
       <c r="A178" s="2" t="inlineStr">
@@ -11489,6 +12374,11 @@
           <t>Kenya Cabinet-approved National Infrastructure Fund + SWF; KPC IPO planned March 2026</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>S177</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11521,6 +12411,11 @@
           <t>PIC/GEPF LP confirmation in Africa Food Security Fund; co-investors AfDB, CDC/BII, DGGF, IFU, EBID and Kuramo</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>S178</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11553,6 +12448,11 @@
           <t>Wessal as SWF joint investment vehicle; EUR 2.5bn equity commitment; projects Wessal Bouregreg and Wessal Casa-Port</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>S179</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11585,6 +12485,11 @@
           <t>NSIA investments in Alitheia IDF, Ingressive Capital and Verod Capital; MedServe impact reference</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>S180</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11617,6 +12522,11 @@
           <t>Verod Growth Fund II USD 5m commitment and Verod Growth Fund III USD 7.5m commitment</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>S181</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11649,6 +12559,11 @@
           <t>MedServe expansion project size USD 154.1m; IFC USD 24.5m local-currency financing</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>S182</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11681,6 +12596,11 @@
           <t>Alitheia IDF as USD 100m gender-lens fund and SEDF co-investor</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>S183</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11713,6 +12633,11 @@
           <t>Ingressive Capital strategy and geographic focus</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>S184</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11745,6 +12670,11 @@
           <t>Verod Growth fund manager profile and AUM context</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>S185</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11777,6 +12707,11 @@
           <t>InfraCredit business model and project-inception funding context</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>S186</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11809,6 +12744,11 @@
           <t>InfraCredit as NSIA/GuarantCo participant vehicle catalysing pension and insurance investment</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>S187</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11841,6 +12781,11 @@
           <t>NSIA NGN10bn anchor investment; CFWF target NGN100bn capacity; InfraCredit capitalization USD237m+</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>S188</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11873,6 +12818,11 @@
           <t>KfW subordinated capital and InfraCredit establishment by NSIA with GuarantCo/PIDG</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>S189</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11905,6 +12855,11 @@
           <t>PIDG/NSIA establishment, GuarantCo initial contingent capital, InfraCo Africa and domestic institutional mobilization</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>S190</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11937,6 +12892,11 @@
           <t>NSIA retained InfraCredit ownership interest; Access ARM Pensions, CardinalStone, AFC and insurers as shareholders</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>S191</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11969,6 +12929,11 @@
           <t>VCTF impact report coverage; GHc359.6m invested, GHc2bn leveraged; Oasis Capital and Injaro Ghana Venture Fund identified as anchored/impactful funds</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>S192</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12001,6 +12966,11 @@
           <t>Oasis Africa VC Fund Ghana domicile, VCTF government co-investment rationale, DGGF legal TA and subsequent DFI crowd-in</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>S193</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12033,6 +13003,11 @@
           <t>OAF first close amount and DGGF role</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>S194</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12065,6 +13040,11 @@
           <t>OAF first close: USD 27m, DGGF USD 5m, IFC USD 7m and local investor base over USD 15m</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>S195</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12097,6 +13077,11 @@
           <t>Oasis Africa VC Fund final fund size USD 50.5m and EIB USD 8m commitment</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>S196</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12129,6 +13114,11 @@
           <t>VCTF USD 2m commitment to Oasis Africa Fund Limited and Ebankese Venture Fund portfolio context</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>S197</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12161,6 +13151,11 @@
           <t>VCTF mandate as government-backed venture capital fund of funds focused on SME venture funds</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>S198</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12193,6 +13188,11 @@
           <t>Virunga Africa Fund I launch; QIA and RSSB named as anchor/cornerstone investors; Admaius manager; USD 250m fund size and pan-African sector focus</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>S199</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12225,6 +13225,11 @@
           <t>Virunga Africa Fund II pipeline/watchlist evidence; IFC proposed USD 25m + USD 10m co-invest; fund target USD 500m; predecessor Fund I was RSSB/QIA-anchored, but no confirmed RSSB Fund II commitment as of 5 June 2026.</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>S200</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12257,6 +13262,11 @@
           <t>Virunga Africa Fund II pipeline/watchlist details; target size, focus markets, sectors, and proposed IFC investment; not confirmation of RSSB commitment.</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>S201</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12289,6 +13299,11 @@
           <t>IFC proposed USD 25m + USD 10m co-invest in Fund II; predecessor Fund I closed USD 280m in 2022</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>S202</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12321,6 +13336,11 @@
           <t>Names SSNIT as LP in four PE funds: Fidelity Equity Fund II, ECP Africa Fund III, PAIDF, CIFA (USD 5.04m, June 2005)</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>S203</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12353,6 +13373,11 @@
           <t>CIFA fund details; USD 212m fund; Government of Canada anchor; SSNIT confirmed LP with USD 5.04m June 2005 commitment</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>S204</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12385,6 +13410,11 @@
           <t>Confirms SIFEM and SSNIT as LPs in Fidelity Equity Fund II; fund invests USD 500k-3.5m in unlisted Ghanaian SMEs</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>S205</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12417,6 +13447,11 @@
           <t>FSDEA USD 50m seed (up to USD 200m); Gemcorp USD 50m; fund target USD 500m; Abu Dhabi domicile; sectors: critical minerals, water, food, energy transition</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>S206</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12449,6 +13484,11 @@
           <t>Thusano Capital confirms management of BWP 1bn infrastructure fund on behalf of BPOPF. Sectors: energy, logistics, communications, agriculture, bulk infrastructure. 100% citizen-owned manager.</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>S207</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12481,6 +13521,11 @@
           <t>Names all six BPOPF incubation programme beneficiaries: Africa Lighthouse Capital, Aleyo Capital (graduated), Thusano Capital, SeventyFive Degrees, 5th Quarter Investment Managers, K-Hill Property Developers. Six tenders ~P6bn awarded since inception. Minimum P500m per manager; current tender BPOPF/INV 008/2024-25.</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>S208</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12513,6 +13558,11 @@
           <t>NOSI official-public disclosure check; investment fund performance summary, no named African alternative-asset commitment found.</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>S209</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12545,6 +13595,11 @@
           <t>Arabic local-language NOSI annual report/final account reference; aggregate investment growth but no named private fund/deal commitment.</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>S210</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12577,6 +13632,11 @@
           <t>NIB public-disclosure check; publications relate to state investment plan/financing, not named pension alternative-asset commitments.</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>S211</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12609,6 +13669,11 @@
           <t>EIH USD 3m private placement / 7.4% Akobo Minerals stake; candidate direct equity item requiring scope decision because issuer is listed but project is Ethiopian mining.</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>S212</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12641,6 +13706,11 @@
           <t>EIH mandate and investment approach; no fund LP commitments found in official investment page search.</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>S213</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12673,6 +13743,11 @@
           <t>CMR public disclosure check; confirms activity report and portfolio values, no named African PE/infrastructure fund commitment found.</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>S214</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12705,6 +13780,11 @@
           <t>CMR candidate real-estate/OPCI alternative allocation; vehicle identities not yet resolved and likely outside core PE/infra scope.</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>S215</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12737,6 +13817,11 @@
           <t>RCAR official report; evidence of mandates with CDG Capital, CDG Invest for unlisted participations, and Ewane Assets for real estate; no named allocator-to-fund commitment yet.</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>S216</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12769,6 +13854,11 @@
           <t>Sanlam Umbrella Fund official disclosure check; governance/responsible investment reporting reviewed, no named African alternative-asset fund/deal commitment found.</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>S217</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12801,6 +13891,11 @@
           <t>Fund manager table (pp.84-85) and Unlisted Investment Fund Manager descriptions (pp.96-99). Identified: South Suez Capital (N$2.75bn), Investec Africa PE Fund 2, Neoma Africa Fund III (prev Abraaj), Actis Africa PE (N$101m), Growthpoint Investec Africa Properties Limited. Added as rows 104-108.</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>S218</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12833,6 +13928,11 @@
           <t>GEPF official disclosure sweep; Isibaya/unlisted portfolio and approved allocation to Ninety One Credit Fund - African Credit Opportunities Fund III.</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>S219</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12865,6 +13965,11 @@
           <t>PIC/GEPF unlisted investments and Africa ex-SA equity/developmental portfolio cross-check.</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>S220</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12897,6 +14002,11 @@
           <t>LIA official governance/financial-disclosure sweep; confirms financial statements work and investment policy, but no named African fund commitment.</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>S221</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12929,6 +14039,11 @@
           <t>LIA 2025 portfolio structure: time deposits, equities, and investment-fund portfolio; no named African private-market vehicle disclosed.</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>S222</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12961,6 +14076,11 @@
           <t>CDG/CDG Capital official disclosure sweep; current activity and financial report, no new named pension/SWF LP commitment beyond existing CDG rows.</t>
         </is>
       </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>S223</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12993,6 +14113,11 @@
           <t>Historical CDG Capital private-equity / CapMezzanine context; reviewed for possible older fund rows.</t>
         </is>
       </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>S224</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13025,6 +14150,11 @@
           <t>CNSS official/statistical disclosure sweep; operating/social-security data, no named alternative-asset commitment found.</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>S225</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13057,6 +14187,11 @@
           <t>CNSS candidate OPCI/state-asset real-estate vehicle lead; likely outside core PE/infra scope unless dashboard includes real estate vehicles.</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>S226</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13089,6 +14224,11 @@
           <t>CIMR public disclosure sweep; annual reports available, no named African alternative fund commitment found in initial pass.</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>S227</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13121,6 +14261,11 @@
           <t>CIMR placement portfolio size cross-check; no named private-market vehicle evidence in source.</t>
         </is>
       </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>S228</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13153,6 +14298,11 @@
           <t>BPOPF official disclosure sweep; annual report page and existing unlisted/incubation programme context checked.</t>
         </is>
       </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>S229</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13185,6 +14335,11 @@
           <t>Botswana retirement-fund industry allocation cross-check, including unlisted equity category and BPOPF as top fund.</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>S230</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13217,6 +14372,11 @@
           <t>PSSSF disclosure sweep; confirms conservative government-bond/securities focus and no named PE/infra fund commitment in reviewed source.</t>
         </is>
       </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>S231</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13249,6 +14409,11 @@
           <t>EPPF official disclosure sweep; reports available, no new named African alternative fund commitment found beyond existing PE exposure row.</t>
         </is>
       </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>S232</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13281,6 +14446,11 @@
           <t>FONSIS confirmed as founding LP/shareholder in Teranga Capital (2016 impact SME fund, Senegal). Added as row 109.</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>S233</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13313,6 +14483,11 @@
           <t>CDC Gabon confirmed as named LP in Amethis West Africa fund (€40-45m, 2014, CIMA zone). Added as Commitments DB row 110.</t>
         </is>
       </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>S234</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13345,6 +14520,11 @@
           <t>CNPS-CI reported to invest in "investment funds such as one launched by Amethis and the Africa50 fund". Specific fund name unconfirmed. Added as Commitments DB row 111 with confidence M.</t>
         </is>
       </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>S235</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13377,6 +14557,11 @@
           <t>Named African pension LPs in DPI ADP III (EPPF USD 20m, KenGen, Banki Kuu/CBK, Old Mutual Umbrella Kenya) and EKIF (KPLC PF USD 9m). Added as Commitments DB rows 112-116.</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>S236</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13409,6 +14594,11 @@
           <t>22 Nigerian PFAs invested in NIDF across Series 1-6; fund size N58bn (~USD 190m). Added as Commitments DB row 117.</t>
         </is>
       </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>S237</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13441,6 +14631,11 @@
           <t>KEPFIC USD 11m investment in Acorn Student Accommodation D-REIT; blended return 18.3%. Added as Commitments DB row 118.</t>
         </is>
       </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>S238</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13473,6 +14668,11 @@
           <t>PODCPF ~3% PE allocation managed by Mergence Lesotho (only PE manager in country). Added as Commitments DB row 119.</t>
         </is>
       </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>S239</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13503,6 +14703,11 @@
       <c r="F241" t="inlineStr">
         <is>
           <t>Corroborates Mergence Lesotho investing on behalf of largest Lesotho pension fund in local infrastructure &amp; development projects (medical agriculture, Maseru property).</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>S240</t>
         </is>
       </c>
     </row>
@@ -33109,7 +34314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R119"/>
+  <dimension ref="A1:S119"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -33219,6 +34424,11 @@
           <t>Investment approach</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Source IDs</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="23.25" customHeight="1" s="16">
       <c r="A2" s="2" t="inlineStr">
@@ -33309,6 +34519,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="2" t="inlineStr">
@@ -33401,6 +34616,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="16">
       <c r="A4" s="2" t="inlineStr">
@@ -33675,6 +34895,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>S002;S219;S220</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="16">
       <c r="A7" s="2" t="inlineStr">
@@ -33767,6 +34992,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>S032;S033</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="16">
       <c r="A8" s="2" t="inlineStr">
@@ -33857,6 +35087,11 @@
           <t>Platform / Anchor Sponsor</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="23.25" customHeight="1" s="16">
       <c r="A9" s="2" t="inlineStr">
@@ -33947,6 +35182,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>S004;S088</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="23.25" customHeight="1" s="16">
       <c r="A10" s="2" t="inlineStr">
@@ -34039,6 +35279,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" s="16">
       <c r="A11" s="2" t="inlineStr">
@@ -34131,6 +35376,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" s="16">
       <c r="A12" s="2" t="inlineStr">
@@ -34223,6 +35473,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" s="16">
       <c r="A13" s="2" t="inlineStr">
@@ -34315,6 +35570,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>S145;S147</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" s="16">
       <c r="A14" s="2" t="inlineStr">
@@ -34405,6 +35665,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>S030;S031</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="34.5" customHeight="1" s="16">
       <c r="A15" s="2" t="inlineStr">
@@ -34497,6 +35762,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" s="16">
       <c r="A16" s="2" t="inlineStr">
@@ -34589,6 +35859,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>S030;S031</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="23.25" customHeight="1" s="16">
       <c r="A17" s="2" t="inlineStr">
@@ -34679,6 +35954,11 @@
           <t>Co-investment</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>S023</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="23.25" customHeight="1" s="16">
       <c r="A18" s="2" t="inlineStr">
@@ -34771,6 +36051,11 @@
           <t>Platform / Anchor Sponsor</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>S023;S024</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.25" customHeight="1" s="16">
       <c r="A19" s="2" t="inlineStr">
@@ -34863,6 +36148,11 @@
           <t>Platform / Anchor Sponsor</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>S023;S024</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23.25" customHeight="1" s="16">
       <c r="A20" s="2" t="inlineStr">
@@ -34955,6 +36245,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>S027;S028</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.25" customHeight="1" s="16">
       <c r="A21" s="2" t="inlineStr">
@@ -35047,6 +36342,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>S224;S027</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="23.25" customHeight="1" s="16">
       <c r="A22" s="2" t="inlineStr">
@@ -35139,6 +36439,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>S027;S224</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="23.25" customHeight="1" s="16">
       <c r="A23" s="2" t="inlineStr">
@@ -35231,6 +36536,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>S029</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="23.25" customHeight="1" s="16">
       <c r="A24" s="2" t="inlineStr">
@@ -35321,6 +36631,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>S028;S027</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23.25" customHeight="1" s="16">
       <c r="A25" s="2" t="inlineStr">
@@ -35413,6 +36728,11 @@
           <t>Platform / Anchor Sponsor</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>S179</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23.25" customHeight="1" s="16">
       <c r="A26" s="2" t="inlineStr">
@@ -35505,6 +36825,11 @@
           <t>Platform / Anchor Sponsor</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="23.25" customHeight="1" s="16">
       <c r="A27" s="2" t="inlineStr">
@@ -35597,6 +36922,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>S007;S218</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="16">
       <c r="A28" s="2" t="inlineStr">
@@ -35689,6 +37019,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>S007;S218</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="23.25" customHeight="1" s="16">
       <c r="A29" s="2" t="inlineStr">
@@ -35781,6 +37116,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>S218</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="23.25" customHeight="1" s="16">
       <c r="A30" s="2" t="inlineStr">
@@ -35869,6 +37209,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>S218</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23.25" customHeight="1" s="16">
       <c r="A31" s="2" t="inlineStr">
@@ -35961,6 +37306,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>S218</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="23.25" customHeight="1" s="16">
       <c r="A32" s="2" t="inlineStr">
@@ -36051,6 +37401,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>S017;S018</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="23.25" customHeight="1" s="16">
       <c r="A33" s="2" t="inlineStr">
@@ -36141,6 +37496,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>S017;S018</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="23.25" customHeight="1" s="16">
       <c r="A34" s="2" t="inlineStr">
@@ -36233,6 +37593,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>S017;S128;S127</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="23.25" customHeight="1" s="16">
       <c r="A35" s="2" t="inlineStr">
@@ -36325,6 +37690,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="23.25" customHeight="1" s="16">
       <c r="A36" s="2" t="inlineStr">
@@ -36415,6 +37785,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>S014;S143;S144</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="23.25" customHeight="1" s="16">
       <c r="A37" s="2" t="inlineStr">
@@ -36507,6 +37882,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>S013;S074;S012</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="23.25" customHeight="1" s="16">
       <c r="A38" s="2" t="inlineStr">
@@ -36597,6 +37977,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>S102;S101</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="23.25" customHeight="1" s="16">
       <c r="A39" s="2" t="inlineStr">
@@ -36687,6 +38072,11 @@
           <t>Platform / Anchor Sponsor</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>S019;S206</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="23.25" customHeight="1" s="16">
       <c r="A40" s="2" t="inlineStr">
@@ -36777,6 +38167,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="23.25" customHeight="1" s="16">
       <c r="A41" s="2" t="inlineStr">
@@ -36869,6 +38264,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>S021;S020</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="23.25" customHeight="1" s="16">
       <c r="A42" s="2" t="inlineStr">
@@ -36959,6 +38359,11 @@
           <t>Platform / Anchor Sponsor</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>S025</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="23.25" customHeight="1" s="16">
       <c r="A43" s="2" t="inlineStr">
@@ -37051,6 +38456,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>S026</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="23.25" customHeight="1" s="16">
       <c r="A44" s="2" t="inlineStr">
@@ -37143,6 +38553,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="23.25" customHeight="1" s="16">
       <c r="A45" s="2" t="inlineStr">
@@ -37235,6 +38650,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="16">
       <c r="A46" s="2" t="inlineStr">
@@ -37325,6 +38745,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>S034</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="23.25" customHeight="1" s="16">
       <c r="A47" s="2" t="inlineStr">
@@ -37417,6 +38842,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>S034;S035</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="23.25" customHeight="1" s="16">
       <c r="A48" s="2" t="inlineStr">
@@ -37509,6 +38939,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="23.25" customHeight="1" s="16">
       <c r="A49" s="2" t="inlineStr">
@@ -37601,6 +39036,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="23.25" customHeight="1" s="16">
       <c r="A50" s="2" t="inlineStr">
@@ -37693,6 +39133,11 @@
           <t>Platform / Anchor Sponsor</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="16">
       <c r="A51" s="2" t="inlineStr">
@@ -37783,6 +39228,11 @@
           <t>Co-investment</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>S075;S077;S076</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="16">
       <c r="A52" s="2" t="inlineStr">
@@ -37873,6 +39323,11 @@
           <t>Fund of Funds LP</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>S080;S081</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="34.5" customHeight="1" s="16">
       <c r="A53" s="2" t="inlineStr">
@@ -37963,6 +39418,11 @@
           <t>Fund of Funds LP</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>S080;S081</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="23.25" customHeight="1" s="16">
       <c r="A54" s="2" t="inlineStr">
@@ -38053,6 +39513,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>S087;S220</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="23.25" customHeight="1" s="16">
       <c r="A55" s="2" t="inlineStr">
@@ -38145,6 +39610,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>S083;S087</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="23.25" customHeight="1" s="16">
       <c r="A56" s="2" t="inlineStr">
@@ -38237,6 +39707,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>S083;S087</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="34.5" customHeight="1" s="16">
       <c r="A57" s="2" t="inlineStr">
@@ -38329,6 +39804,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>S084;S087</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="34.5" customHeight="1" s="16">
       <c r="A58" s="2" t="inlineStr">
@@ -38421,6 +39901,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>S084;S087</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="23.25" customHeight="1" s="16">
       <c r="A59" s="2" t="inlineStr">
@@ -38513,6 +39998,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>S082</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="34.5" customHeight="1" s="16">
       <c r="A60" s="2" t="inlineStr">
@@ -38605,6 +40095,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>S087</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="23.25" customHeight="1" s="16">
       <c r="A61" s="2" t="inlineStr">
@@ -38697,6 +40192,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>S084;S087</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="23.25" customHeight="1" s="16">
       <c r="A62" s="2" t="inlineStr">
@@ -38785,6 +40285,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>S083;S087</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="23.25" customHeight="1" s="16">
       <c r="A63" s="2" t="inlineStr">
@@ -38875,6 +40380,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>S085;S001;S082</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="23.25" customHeight="1" s="16">
       <c r="A64" s="2" t="inlineStr">
@@ -38965,6 +40475,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>S088;S089;S090</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="23.25" customHeight="1" s="16">
       <c r="A65" s="2" t="inlineStr">
@@ -39055,6 +40570,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>S088;S089;S090</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="23.25" customHeight="1" s="16">
       <c r="A66" s="2" t="inlineStr">
@@ -39145,6 +40665,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>S088;S089;S090</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="23.25" customHeight="1" s="16">
       <c r="A67" s="2" t="inlineStr">
@@ -39235,6 +40760,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>S088;S089;S090</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="23.25" customHeight="1" s="16">
       <c r="A68" s="2" t="inlineStr">
@@ -39325,6 +40855,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>S092;S095;S093</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="23.25" customHeight="1" s="16">
       <c r="A69" s="2" t="inlineStr">
@@ -39415,6 +40950,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>S096;S097;S098</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="23.25" customHeight="1" s="16">
       <c r="A70" s="2" t="inlineStr">
@@ -39505,6 +41045,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>S103;S104</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="23.25" customHeight="1" s="16">
       <c r="A71" s="2" t="inlineStr">
@@ -39595,6 +41140,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>S103;S104</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="23.25" customHeight="1" s="16">
       <c r="A72" s="2" t="inlineStr">
@@ -39685,6 +41235,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>S103;S104</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="23.25" customHeight="1" s="16">
       <c r="A73" s="2" t="inlineStr">
@@ -39777,6 +41332,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>S102;S101;S104</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="23.25" customHeight="1" s="16">
       <c r="A74" s="2" t="inlineStr">
@@ -39869,6 +41429,11 @@
           <t>Mandate / Pipeline Only</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>S106;S107;S105</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="23.25" customHeight="1" s="16">
       <c r="A75" s="2" t="inlineStr">
@@ -39959,6 +41524,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>S114;S113</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="23.25" customHeight="1" s="16">
       <c r="A76" s="2" t="inlineStr">
@@ -40049,6 +41619,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>S113</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="23.25" customHeight="1" s="16">
       <c r="A77" s="2" t="inlineStr">
@@ -40141,6 +41716,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>S115;S116;S117</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="34.5" customHeight="1" s="16">
       <c r="A78" s="2" t="inlineStr">
@@ -40233,6 +41813,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>S115;S116</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="45.75" customHeight="1" s="16">
       <c r="A79" s="2" t="inlineStr">
@@ -40323,6 +41908,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>S139;S140;S141</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="23.25" customHeight="1" s="16">
       <c r="A80" s="2" t="inlineStr">
@@ -40415,6 +42005,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>S145;S146;S147</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="34.5" customHeight="1" s="16">
       <c r="A81" s="2" t="inlineStr">
@@ -40505,6 +42100,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>S153;S154;S155</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="23.25" customHeight="1" s="16">
       <c r="A82" s="2" t="inlineStr">
@@ -40597,6 +42197,11 @@
           <t>Mandate / Pipeline Only</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>S158;S156;S175</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="23.25" customHeight="1" s="16">
       <c r="A83" s="2" t="inlineStr">
@@ -40687,6 +42292,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>S165;S166;S168</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="45.75" customHeight="1" s="16">
       <c r="A84" s="2" t="inlineStr">
@@ -40777,6 +42387,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>S165;S168</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="90.75" customHeight="1" s="16">
       <c r="A85" s="2" t="inlineStr">
@@ -40867,6 +42482,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>S165;S167;S168</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="34.5" customHeight="1" s="16">
       <c r="A86" s="2" t="inlineStr">
@@ -40957,6 +42577,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>S172;S170;S169</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="34.5" customHeight="1" s="16">
       <c r="A87" t="inlineStr">
@@ -41047,6 +42672,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>S178</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="45.75" customHeight="1" s="16">
       <c r="A88" t="inlineStr">
@@ -41139,6 +42769,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>S180</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="34.5" customHeight="1" s="16">
       <c r="A89" t="inlineStr">
@@ -41231,6 +42866,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>S180</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="34.5" customHeight="1" s="16">
       <c r="A90" t="inlineStr">
@@ -41321,6 +42961,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>S181;S180</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="23.25" customHeight="1" s="16">
       <c r="A91" t="inlineStr">
@@ -41413,6 +43058,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>S181;S180</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="23.25" customHeight="1" s="16">
       <c r="A92" t="inlineStr">
@@ -41503,6 +43153,11 @@
           <t>Direct Investment</t>
         </is>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>S182</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="124.5" customHeight="1" s="16">
       <c r="A93" t="inlineStr">
@@ -41595,6 +43250,11 @@
           <t>Guarantee-backed Instrument</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>S187;S191;S190</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="124.5" customHeight="1" s="16">
       <c r="A94" t="inlineStr">
@@ -41685,6 +43345,11 @@
           <t>Guarantee-backed Instrument</t>
         </is>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>S188;S186</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="79.5" customHeight="1" s="16">
       <c r="A95" t="inlineStr">
@@ -41777,6 +43442,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>S194;S193;S197</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="34.5" customHeight="1" s="16">
       <c r="A96" t="inlineStr">
@@ -41867,6 +43537,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>S168;S167;S165</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="45.75" customHeight="1" s="16">
       <c r="A97" t="inlineStr">
@@ -41957,6 +43632,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>S192;S172;S170</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="57" customHeight="1" s="16">
       <c r="A98" t="inlineStr">
@@ -42047,6 +43727,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>S199</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -42137,6 +43822,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>S204;S203</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -42227,6 +43917,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>S203</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -42317,6 +44012,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>S203</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -42407,6 +44107,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>S205;S203</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -42497,6 +44202,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>S207;S208</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -42589,6 +44299,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>S218;S007</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -42681,6 +44396,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>S218;S007</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -42773,6 +44493,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>S218;S007</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -42865,6 +44590,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>S218;S007</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -42957,6 +44687,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>S218;S007</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -43049,6 +44784,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>S233</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -43139,6 +44879,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>S234</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -43231,6 +44976,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>S235;S234</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -43321,6 +45071,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>S236;S162</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -43411,6 +45166,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>S236;S162</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -43501,6 +45261,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>S236;S162</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -43591,6 +45356,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>S236;S162</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -43681,6 +45451,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>S236;S162</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -43773,6 +45548,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>S237</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -43863,6 +45643,11 @@
           <t>Fund LP</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>S238;S105</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -43953,6 +45738,11 @@
       <c r="R119" t="inlineStr">
         <is>
           <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>S239;S240</t>
         </is>
       </c>
     </row>

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -47920,11 +47920,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Norfund, OeEB (Austria)</t>
+          <t>BII; FMO; Norfund; OeEB (Austria)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -47934,7 +47934,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Historical pioneer fund for East African pension PE participation.</t>
+          <t>Historical pioneer fund for East African pension PE participation. DFI project-database cross-check adds BII and FMO to the existing Norfund/OeEB ARVF I record.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -48137,11 +48137,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>BII (USD 30m), EIB, IFC, Proparco, Swedfund</t>
+          <t>BII (USD 30m); EIB; IFC; Proparco; SIFEM; Swedfund</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -48151,7 +48151,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Single largest East African PE fund with disclosed local-pension cohort.</t>
+          <t>Single largest East African PE fund with disclosed local-pension cohort. DFI project-database cross-check adds SIFEM to the named Catalyst Fund II DFI LP set.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -48285,11 +48285,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>IFC, EIB, BII, Norfund, DEG, Finnfund</t>
+          <t>IFC; EIB; BII; Norfund; DEG; Finnfund; Swedfund</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -48299,7 +48299,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Vantage's 'historical pattern' of substantial SA pension LP base; specific names not publicly itemised.</t>
+          <t>Vantage's 'historical pattern' of substantial SA pension LP base; specific names not publicly itemised. DFI project-database cross-check adds Swedfund to the named Vantage Mezzanine IV DFI LP set.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -48945,14 +48945,12 @@
           <t>PIC South Africa (historical)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Various DFIs</t>
+          <t>BII; IFC</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -48962,7 +48960,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Digital infrastructure; PIC participant.</t>
+          <t>Digital infrastructure; PIC participant. DFI project-database cross-check replaces generic DFI label with named BII and IFC commitments.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -49874,11 +49872,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>FMO</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>NSIA impact report identifies a USD 5m FGF commitment to Verod Growth Fund II.</t>
+          <t>NSIA impact report identifies a USD 5m FGF commitment to Verod Growth Fund II. DFI project-database cross-check identifies FMO as a Verod Capital Growth II investor.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -49937,11 +49940,16 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>BII; BIO; FMO; IFC; Norfund; Proparco/FISEA</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>NSIA impact report identifies a USD 7.5m FGF commitment to Verod Growth Fund III.</t>
+          <t>NSIA impact report identifies a USD 7.5m FGF commitment to Verod Growth Fund III. DFI project-database cross-check identifies BII, BIO, FMO, IFC, Norfund and Proparco/FISEA as Verod Growth Fund III investors.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -50205,11 +50213,11 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Dutch Good Growth Fund (DGGF); IFC; EIB</t>
+          <t>Dutch Good Growth Fund (DGGF); IFC; EIB; Norfund; Proparco/FISEA</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -50219,7 +50227,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>VCTF government co-investment helped Oasis domicile the fund locally in Ghana. DGGF TA/legal work helped make the Ghana structure bankable for international DFIs; first close included DGGF, IFC and local investors, with EIB later disclosing an USD 8m commitment.</t>
+          <t>VCTF government co-investment helped Oasis domicile the fund locally in Ghana. DGGF TA/legal work helped make the Ghana structure bankable for international DFIs; first close included DGGF, IFC and local investors, with EIB later disclosing an USD 8m commitment. DFI project-database cross-check adds Norfund and Proparco/FISEA as Oasis Africa Fund LPs.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -50478,21 +50486,21 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>BII; FMO; IFC; IFU</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cayman Islands LP. Provides growth capital to Sub-Saharan Africa portfolio companies. Originally managed by Abraaj Group; fund transitioned to Neoma Capital Partners after Abraaj bankruptcy 2018. Source: GIPF 2023 AR p.97.</t>
+          <t>Cayman Islands LP. Provides growth capital to Sub-Saharan Africa portfolio companies. Originally managed by Abraaj Group; fund transitioned to Neoma Capital Partners after Abraaj bankruptcy 2018. Source: GIPF 2023 AR p.97. DFI project-database cross-check identifies BII, FMO, IFC and IFU as Neoma/Abraaj Africa Fund III investors.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -50892,11 +50900,11 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BII; FMO; Finnfund; IFC; IFU; Norfund; Proparco/FISEA; SIFEM; Swedfund</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -50906,7 +50914,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Rare case of multiple named African pension LPs in a USD 900m pan-African PE fund, disclosed via MiDA Advisors / USAID INVEST campaign rather than GP press release.</t>
+          <t>Rare case of multiple named African pension LPs in a USD 900m pan-African PE fund, disclosed via MiDA Advisors / USAID INVEST campaign rather than GP press release. DFI project-database cross-check identifies BII, FMO, Finnfund, IFC, IFU, Norfund, Proparco/FISEA, SIFEM and Swedfund as ADP III LPs/parallel fund investors.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -51130,11 +51138,11 @@
         </is>
       </c>
       <c r="B4" s="23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
-          <t>Ascent Rift Valley Fund II (ARVF II); Capital Alliance Private Equity I-IV (CAPE); Catalyst Fund II; Growth Investment Partners (GIP) Ghana; Growth Investment Partners (GIP) Zambia; Helios Investors II/III/IV (historical); Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Vantage Mezzanine IV (Pan-African sub-fund); Africa Food Security Fund (AFSF)</t>
+          <t>Growth Investment Partners (GIP) Ghana; Growth Investment Partners (GIP) Zambia; Ascent Rift Valley Fund I (ARVF I); Ascent Rift Valley Fund II (ARVF II); Catalyst Fund II; Helios Investors II/III/IV (historical); Vantage Mezzanine IV (Pan-African sub-fund); Convergence Partners Communications Infrastructure Fund; Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Capital Alliance Private Equity I-IV (CAPE); Africa Food Security Fund (AFSF); Verod Growth Fund III; Neoma Africa Fund III (B) L.P. (previously Abraaj Africa Fund III); African Development Partners III (ADP III)</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -51151,20 +51159,20 @@
     <row r="5" ht="23.25" customHeight="1" s="16">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>AfDB</t>
+          <t>IFC</t>
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Africa50 (general); Africa50 Infrastructure Acceleration Fund (IAF); Mediterrania Capital II / III / IV; Nigeria Infrastructure Fund (NIF, NSIA sub-fund); Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Africa Food Security Fund (AFSF); InfraCredit</t>
+          <t>Ascent Rift Valley Fund II (ARVF II); Adenia Capital V; Catalyst Fund II; Vantage Mezzanine IV (Pan-African sub-fund); Africa50 Infrastructure Acceleration Fund (IAF); Convergence Partners Communications Infrastructure Fund; Verod Growth Fund III; MedServe oncology and diagnostics expansion; Oasis Africa VC Fund (OAF); Neoma Africa Fund III (B) L.P. (previously Abraaj Africa Fund III); African Development Partners III (ADP III)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
+          <t>World Bank Group investor and disclosure source; active in flagship PE/infrastructure vehicles.</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -51176,20 +51184,20 @@
     <row r="6" ht="34.5" customHeight="1" s="16">
       <c r="A6" s="23" t="inlineStr">
         <is>
-          <t>Norfund</t>
+          <t>AfDB</t>
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Adenia Capital V; AfricInvest FIVE (Financial Inclusion Vehicle); Ascent Rift Valley Fund I (ARVF I); Ascent Rift Valley Fund II (ARVF II); Growth Investment Partners (GIP) Ghana; Vantage Mezzanine IV (Pan-African sub-fund)</t>
+          <t>Mediterrania Capital II / III / IV; AfricInvest FIVE (Financial Inclusion Vehicle); Africa50 (general); Africa50 Infrastructure Acceleration Fund (IAF); Nigeria Infrastructure Fund (NIF, NSIA sub-fund); Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Africa Food Security Fund (AFSF); InfraCredit; Nigeria Infrastructure Debt Fund (NIDF)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>Frequent DFI co-investor in SME, infrastructure, and financial inclusion vehicles.</t>
+          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -51201,40 +51209,40 @@
     <row r="7" ht="34.5" customHeight="1" s="16">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>IFC</t>
+          <t>Norfund</t>
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>Adenia Capital V; Africa50 Infrastructure Acceleration Fund (IAF); Ascent Rift Valley Fund II (ARVF II); Catalyst Fund II; Vantage Mezzanine IV (Pan-African sub-fund); Oasis Africa VC Fund (OAF)</t>
+          <t>Growth Investment Partners (GIP) Ghana; Ascent Rift Valley Fund I (ARVF I); Ascent Rift Valley Fund II (ARVF II); Adenia Capital V; Vantage Mezzanine IV (Pan-African sub-fund); AfricInvest FIVE (Financial Inclusion Vehicle); Verod Growth Fund III; Oasis Africa VC Fund (OAF); African Development Partners III (ADP III)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>World Bank Group investor and disclosure source; active in flagship PE/infrastructure vehicles.</t>
+          <t>Frequent DFI co-investor in SME, infrastructure, and financial inclusion vehicles.</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>2 (Active)</t>
+          <t>1 (Top tier)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="23.25" customHeight="1" s="16">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>EIB</t>
+          <t>FMO</t>
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Adenia Capital V; Catalyst Fund II; Mediterrania Capital II / III / IV; Vantage Mezzanine IV (Pan-African sub-fund); Oasis Africa VC Fund (OAF)</t>
+          <t>Ci-Gaba Fund of Funds; Ascent Rift Valley Fund I (ARVF I); Ascent Rift Valley Fund II (ARVF II); Adenia Capital V; Verod Growth Fund II; Verod Growth Fund III; Neoma Africa Fund III (B) L.P. (previously Abraaj Africa Fund III); African Development Partners III (ADP III)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -51244,47 +51252,47 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>2 (Active)</t>
+          <t>1 (Top tier)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="23.25" customHeight="1" s="16">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>FMO</t>
+          <t>Proparco</t>
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>Adenia Capital V; Ascent Rift Valley Fund II (ARVF II); Ci-Gaba Fund of Funds</t>
+          <t>Ascent Rift Valley Fund II (ARVF II); Adenia Capital V; Catalyst Fund II; Verod Growth Fund III; Oasis Africa VC Fund (OAF); African Development Partners III (ADP III)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Frequent co-investor across funds and fund-of-funds with African pension/SWF participation.</t>
+          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>2 (Active)</t>
+          <t>1 (Top tier)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="23.25" customHeight="1" s="16">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>Proparco</t>
+          <t>EIB</t>
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Adenia Capital V; Ascent Rift Valley Fund II (ARVF II); Catalyst Fund II</t>
+          <t>Adenia Capital V; Catalyst Fund II; Vantage Mezzanine IV (Pan-African sub-fund); Mediterrania Capital II / III / IV; Oasis Africa VC Fund (OAF)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -51301,15 +51309,15 @@
     <row r="11" ht="23.25" customHeight="1" s="16">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>DEG</t>
+          <t>IFU</t>
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>Adenia Capital V; Vantage Mezzanine IV (Pan-African sub-fund)</t>
+          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Africa Food Security Fund (AFSF); Neoma Africa Fund III (B) L.P. (previously Abraaj Africa Fund III); African Development Partners III (ADP III)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -51319,39 +51327,39 @@
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>3 (Selective / TA)</t>
+          <t>2 (Active)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" s="16">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>FSD Africa Investments</t>
+          <t>Swedfund</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>Ci-Gaba Fund of Funds; Rwanda SME Growth Fund</t>
+          <t>Growth Investment Partners (GIP) Zambia; Catalyst Fund II; Vantage Mezzanine IV (Pan-African sub-fund); African Development Partners III (ADP III)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Catalytic capital provider focused on local institutional-capital mobilization and product design.</t>
+          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>3 (Selective / TA)</t>
+          <t>2 (Active)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34.5" customHeight="1" s="16">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>KfW</t>
+          <t>DGGF</t>
         </is>
       </c>
       <c r="B13" s="23" t="n">
@@ -51359,7 +51367,7 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Oyass Capital; InfraCredit</t>
+          <t>Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Africa Food Security Fund (AFSF); Oasis Africa VC Fund (OAF)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -51369,47 +51377,47 @@
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>3 (Selective / TA)</t>
+          <t>2 (Active)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="16">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>MiDA Advisors</t>
+          <t>KfW</t>
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>AOFSA pooled infrastructure mandates (South Africa); KEPFIC pooled mandates (Kenya)</t>
+          <t>Oyass Capital (SME fund); AfricInvest FIVE (Financial Inclusion Vehicle); InfraCredit</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>Technical-assistance and transaction-advisory provider for pension-consortium infrastructure pipelines.</t>
+          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>3 (Selective / TA)</t>
+          <t>2 (Active)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="16">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>Swedfund</t>
+          <t>SIFEM</t>
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>Catalyst Fund II; Growth Investment Partners (GIP) Zambia</t>
+          <t>Adenia Capital V; Catalyst Fund II; African Development Partners III (ADP III)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -51419,14 +51427,14 @@
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>3 (Selective / TA)</t>
+          <t>2 (Active)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" s="16">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>USAID</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B16" s="23" t="n">
@@ -51434,12 +51442,12 @@
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>AOFSA pooled infrastructure mandates (South Africa); KEPFIC pooled mandates (Kenya)</t>
+          <t>Ascent Rift Valley Fund II (ARVF II); Verod Growth Fund III</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Technical-assistance provider supporting pension-consortium formation and capacity building.</t>
+          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -51451,7 +51459,7 @@
     <row r="17" ht="15" customHeight="1" s="16">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>World Bank / IFC J-CAP</t>
+          <t>DEG</t>
         </is>
       </c>
       <c r="B17" s="23" t="n">
@@ -51459,12 +51467,12 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>AOFSA pooled infrastructure mandates (South Africa); KEPFIC pooled mandates (Kenya)</t>
+          <t>Adenia Capital V; Vantage Mezzanine IV (Pan-African sub-fund)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Technical-assistance and market-development provider for pension-consortium structures.</t>
+          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -51476,15 +51484,15 @@
     <row r="18" ht="15" customHeight="1" s="16">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>BCEAO</t>
+          <t>European Union / IFAD</t>
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>Africa50 (general)</t>
+          <t>Yield Uganda Investment Fund; Teranga Capital</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -51501,20 +51509,20 @@
     <row r="19" ht="15" customHeight="1" s="16">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FSD Africa Investments</t>
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>Ascent Rift Valley Fund II (ARVF II)</t>
+          <t>Ci-Gaba Fund of Funds; Rwanda SME Growth Fund</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
+          <t>Catalytic capital provider focused on local institutional-capital mobilization and product design.</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -51526,15 +51534,15 @@
     <row r="20" ht="15" customHeight="1" s="16">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib</t>
+          <t>Finnfund</t>
         </is>
       </c>
       <c r="B20" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>Africa50 (general)</t>
+          <t>Vantage Mezzanine IV (Pan-African sub-fund); African Development Partners III (ADP III)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -51551,7 +51559,7 @@
     <row r="21" ht="15" customHeight="1" s="16">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>Batseta Council</t>
+          <t>BOAD</t>
         </is>
       </c>
       <c r="B21" s="23" t="n">
@@ -51559,12 +51567,12 @@
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>AOFSA pooled infrastructure mandates (South Africa)</t>
+          <t>Amethis West Africa</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>South African retirement-fund industry body supporting AOFSA secretariat/governance.</t>
+          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -51576,7 +51584,7 @@
     <row r="22" ht="15" customHeight="1" s="16">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>CDP Group</t>
+          <t>DFC</t>
         </is>
       </c>
       <c r="B22" s="23" t="n">
@@ -51584,7 +51592,7 @@
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>Mediterrania Capital II / III / IV</t>
+          <t>Adenia Capital V</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -51601,7 +51609,7 @@
     <row r="23" ht="23.25" customHeight="1" s="16">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>CrossBoundary</t>
+          <t>EBID</t>
         </is>
       </c>
       <c r="B23" s="23" t="n">
@@ -51609,12 +51617,12 @@
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>AOFSA pooled infrastructure mandates (South Africa)</t>
+          <t>Africa Food Security Fund (AFSF)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>Technical-assistance provider supporting AOFSA pipeline development.</t>
+          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -51626,15 +51634,15 @@
     <row r="24" ht="15" customHeight="1" s="16">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>Dutch Good Growth Fund</t>
+          <t>FinDev Canada</t>
         </is>
       </c>
       <c r="B24" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Africa Food Security Fund (AFSF); Oasis Africa VC Fund (OAF)</t>
+          <t>Adenia Capital V</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -51651,7 +51659,7 @@
     <row r="25" ht="15" customHeight="1" s="16">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>FCA Investments</t>
+          <t>GuarantCo / PIDG</t>
         </is>
       </c>
       <c r="B25" s="23" t="n">
@@ -51659,7 +51667,7 @@
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>Yield Uganda Investment Fund</t>
+          <t>InfraCredit</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -51676,7 +51684,7 @@
     <row r="26" ht="15" customHeight="1" s="16">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>FinDev Canada</t>
+          <t>InfraCo Africa</t>
         </is>
       </c>
       <c r="B26" s="23" t="n">
@@ -51684,7 +51692,7 @@
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>Adenia Capital V</t>
+          <t>InfraCredit</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -51699,129 +51707,39 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="16">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>IFU</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>AfricInvest FIVE (Financial Inclusion Vehicle); Africa Food Security Fund (AFSF)</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
-        <is>
-          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>3 (Selective / TA)</t>
-        </is>
-      </c>
+      <c r="A27" s="23" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>OeEB</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>Ascent Rift Valley Fund I (ARVF I)</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>3 (Selective / TA)</t>
-        </is>
-      </c>
+      <c r="A28" s="23" t="n"/>
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>SIFEM</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>Adenia Capital V</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>3 (Selective / TA)</t>
-        </is>
-      </c>
+      <c r="A29" s="23" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="16">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>Soros Economic Development Fund</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>Yield Uganda Investment Fund</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>3 (Selective / TA)</t>
-        </is>
-      </c>
+      <c r="A30" s="23" t="n"/>
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
     </row>
     <row r="31" ht="109.5" customHeight="1" s="16">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t>US DFC</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>Adenia Capital V</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
-        <is>
-          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>3 (Selective / TA)</t>
-        </is>
-      </c>
+      <c r="A31" s="23" t="n"/>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
     </row>
     <row r="32" ht="109.5" customHeight="1" s="16"/>
     <row r="33" ht="109.5" customHeight="1" s="16"/>
@@ -51840,106 +51758,10 @@
     <row r="46" ht="23.85" customHeight="1" s="16"/>
     <row r="47" ht="23.85" customHeight="1" s="16"/>
     <row r="48" ht="129.75" customHeight="1" s="16"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>EBID</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Africa Food Security Fund (AFSF)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Co-investor or catalytic-capital provider appearing in retained vehicles with African PF/SWF participation.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>3 (Selective / TA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Kuramo Capital Management</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Africa Food Security Fund (AFSF)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Other named LP / fund-of-funds investor appearing in retained vehicles with African PF/SWF participation.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>3 (Selective / TA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>GuarantCo / PIDG</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>InfraCredit</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Guarantee/catalytic capital provider that established InfraCredit with NSIA via PIDG/GuarantCo.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>3 (Selective / TA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>InfraCo Africa</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>InfraCredit</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>PIDG project-development arm/shareholder capital provider to InfraCredit.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3 (Selective / TA)</t>
-        </is>
-      </c>
-    </row>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
   </sheetData>
   <autoFilter ref="A3:E27"/>
   <mergeCells count="3">

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -2286,7 +2286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="16" min="1" max="1"/>
@@ -4697,6 +4697,300 @@
       <c r="H65" t="inlineStr">
         <is>
           <t>https://vctf.com.gh/wp-content/uploads/2022/09/Venture-Capital-Annual-report-2015.pdf; https://english.dggf.nl/site/binaries/site-content/collections/documents/2025/11/17/getting-sme-risk-capital-funds-to-first-close/dggf-knowledge-product-getting-sme-risk-capital-funds-to-first-close.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>added 2026-06-22</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Enko Impact Credit Fund</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PIC (mgr for GEPF) (USD 30m)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Named African public pension asset manager commitment to a specific private credit fund, with amount disclosed.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.bii.co.uk/en/news-insight/news/bii-and-pic-announce-first-investment-under-new-partnership-to-drive-growth-for-african-businesses/; https://www.ecofinagency.com/news-finances/2411-50773-enko-capital-raises-130mln-for-its-private-credit-fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>added 2026-06-22</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Hlayisani Venture Fund II</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PIC (mgr for GEPF)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Fund manager names PIC as anchor investor in ZAR 500m first close.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://hlayisani.com/news/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>added 2026-06-22</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>African Women Impact Fund (AWIF)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Motor Industry Retirement Fund (MIRF); Copartes Pension Fund</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>UNECA names African pension funds and amount brought under AWIF initiative; fund-of-funds/gender-lens alternatives vehicle.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.uneca.org/stories/african-women-impact-fund-launches-with-usd%2460-million-commitment-to-drive-an-inclusive; https://www.midaadvisors.com/advisory-firm-the-african-women-impact-fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Funds &amp; LP Co-Investors</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>added 2026-06-22</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Kholo Capital Mezzanine Debt Fund I</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Mineworkers Provident Fund; National Fund for Municipal Workers (NFMW)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>First-close coverage names two South African pension funds as institutional investors in a specific mezzanine/private debt fund.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.africaprivateequitynews.com/p/kholo-capital-mezzanine-debt-fund-i-achieves-first-close; https://ffnews.com/newsarticle/debt-fund-kholo-capital-mezzanine-debt-fund-i-achieve-first-close-at-r870m/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Commitments Database</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>added 2026-06-23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Africa50 Infrastructure Acceleration Fund (IAF)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Public Service Superannuation Scheme/Fund Kenya</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Africa50 official release names Public Service Superannuation Fund (Kenya) as a recent IAF commitment; reconciled to existing PSSS institution name.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.africa50.com/media/news/article/africa50-infrastructure-acceleration-fund-marks-inaugural-investment-in-port-operator-mass-cereales-al-maghreb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Commitments Database</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>added 2026-06-23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Africa50 Infrastructure Acceleration Fund (IAF)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CNPS Cameroon</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Africa50 official release names CNPS Cameroon as a recent IAF commitment; distinct from existing AFC equity holding.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.africa50.com/media/news/article/africa50-infrastructure-acceleration-fund-marks-inaugural-investment-in-port-operator-mass-cereales-al-maghreb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Commitments Database</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>added 2026-06-23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Africa Credit Opportunities Fund III (ACO Fund 3)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>GEPF (via PIC)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>GEPF official annual report names approved allocation to Ninety One Credit Fund / Africa Credit Opportunities Fund III; GP/DFI sources confirm fund first close and co-investor base.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://gepf.co.za/wp-content/uploads/2025/11/GEPF_AR_2025_digital.pdf; https://ninetyone.com/en/newsroom/ninety-one-announces-usd260-million-first-close-of-aco-fund-3; https://www.findevcanada.ca/en/news/findev-canada-commits-usd-20-million-ninety-ones-africa-credit-opportunities-fund-iii-support</t>
         </is>
       </c>
     </row>
@@ -4982,7 +5276,7 @@
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>Candidate - new 2026 item</t>
+          <t>Added to Commitments Database - 2026-06-22</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -5032,7 +5326,7 @@
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
-          <t>Add to Commitments and Fund Vehicles as confirmed first-close/commitments-to-date, with note that final close is pending.</t>
+          <t>Added to Commitments Database, Fund Vehicles, Source Library, Inclusion Audit, and DFI/Other LP patterns where applicable.</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
@@ -5614,7 +5908,7 @@
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>Candidate - likely add after amount/source detail check</t>
+          <t>Actioned - added to database 2026-06-23</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
@@ -5634,7 +5928,7 @@
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>Not yet checked in this sweep.</t>
+          <t>IFC; BII; SIFEM; Standard Bank debt facility; FinDev Canada</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -5654,7 +5948,7 @@
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
-          <t>GEPF annual report confirms approved allocation; commitment amount not yet isolated.</t>
+          <t>GEPF annual report confirms approved allocation; Ninety One first close USD 260m; GEPF amount not disclosed.</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -5664,12 +5958,12 @@
       </c>
       <c r="K12" s="21" t="inlineStr">
         <is>
-          <t>Research Ninety One/DFI fund-close disclosures and GEPF note 3.1 for commitment amount; likely add to Commitments Database if allocator-to-fund allocation is sufficiently specific.</t>
+          <t>Added to Commitments Database, Source Library, Inclusion Audit, and fund-level co-investor view.</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t>Official GEPF report names a specific African private credit fund allocation approved in FY2024/25.</t>
+          <t>Official GEPF report names a specific African private credit fund allocation approved in FY2024/25; GP/DFI sources confirm ACO Fund 3 first close and co-investor base.</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -5679,7 +5973,7 @@
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t>https://www.pic.gov.za/DocAnnualReports1/PIC%20Integrated%20Annual%20Report%202024.pdf</t>
+          <t>https://ninetyone.com/en/newsroom/ninety-one-announces-usd260-million-first-close-of-aco-fund-3; https://www.findevcanada.ca/en/news/findev-canada-commits-usd-20-million-ninety-ones-africa-credit-opportunities-fund-iii-support</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -5784,7 +6078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G251"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="2"/>
@@ -14708,6 +15002,376 @@
       <c r="G241" t="inlineStr">
         <is>
           <t>S240</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>PIC / GEPF</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>DFI / investor press release</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>BII and PIC announce first investment under new partnership to drive growth for African businesses</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://www.bii.co.uk/en/news-insight/news/bii-and-pic-announce-first-investment-under-new-partnership-to-drive-growth-for-african-businesses/</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>PIC/GEPF via PIC USD 30m commitment to Enko Impact Credit Fund; BII partnership co-investment evidence.</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>S241</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>PIC / GEPF</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Trade press</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Ecofin Agency ? Enko Capital raises $130mln for its private credit fund</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://www.ecofinagency.com/news-finances/2411-50773-enko-capital-raises-130mln-for-its-private-credit-fund</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Enko Impact Credit Fund first close and PIC USD 30m commitment corroboration.</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>S242</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>PIC / GEPF</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Fund manager press release</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Hlayisani Capital ? Hlayisani Venture Fund II first close / anchored by PIC and SA SME Fund</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://hlayisani.com/news/</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Hlayisani Venture Fund II ZAR 500m first close anchored by PIC and SA SME Fund.</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>S243</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>MIRF / Copartes Pension Fund</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>UN agency press release</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>UNECA ? African Women Impact Fund launches with USD 60 million commitment</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://www.uneca.org/stories/african-women-impact-fund-launches-with-usd%2460-million-commitment-to-drive-an-inclusive</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>MIRF and Copartes Pension Fund brought USD 45m under AWIF as part of USD 60m first commitment with BADEA.</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>S244</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>MIRF / Copartes Pension Fund</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Advisor case study</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>MiDA Advisors ? The African Women Impact Fund</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.midaadvisors.com/advisory-firm-the-african-women-impact-fund</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>AWIF structure, investor mobilization context, and African pension capital participation.</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>S245</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Mineworkers Provident Fund / NFMW</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Trade press</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Africa Private Equity News ? Kholo Capital Mezzanine Debt Fund I achieves first close</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://www.africaprivateequitynews.com/p/kholo-capital-mezzanine-debt-fund-i-achieves-first-close</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Kholo Capital Mezzanine Debt Fund I R870m first close and named South African pension LPs.</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>S246</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Mineworkers Provident Fund / NFMW</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Trade press</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Fintech Finance ? Debt fund Kholo Capital Mezzanine Debt Fund I achieve first close at R870m</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://ffnews.com/newsarticle/debt-fund-kholo-capital-mezzanine-debt-fund-i-achieve-first-close-at-r870m/</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Corroborates Kholo Capital Mezzanine Debt Fund I first close and institutional investor participation.</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>S247</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Africa50 IAF / Kenya PSSS / CNPS Cameroon</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Africa50 Infrastructure Acceleration Fund marks inaugural investment in port operator Mass Cereales al Maghreb</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://www.africa50.com/media/news/article/africa50-infrastructure-acceleration-fund-marks-inaugural-investment-in-port-operator-mass-cereales-al-maghreb/</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Africa50 IAF recent commitments from DBSA, Axian Group, Public Service Superannuation Fund (Kenya), and CNPS Cameroon.</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>S248</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Ninety One</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Fund manager press release</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Ninety One announces USD 260 million first close of ACO Fund 3</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://ninetyone.com/en/newsroom/ninety-one-announces-usd260-million-first-close-of-aco-fund-3</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>ACO Fund 3 first close, fund strategy, anchor LPs IFC, BII, SIFEM, and Standard Bank debt facility.</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>S249</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>FinDev Canada / Ninety One</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>DFI press release</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>FinDev Canada commits USD 20 million to Ninety One Africa Credit Opportunities Fund III</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://www.findevcanada.ca/en/news/findev-canada-commits-usd-20-million-ninety-ones-africa-credit-opportunities-fund-iii-support</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Additional DFI co-investor evidence for Ninety One Africa Credit Opportunities Fund III.</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>S250</t>
         </is>
       </c>
     </row>
@@ -34314,7 +34978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S119"/>
+  <dimension ref="A1:S128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
@@ -45743,6 +46407,873 @@
       <c r="S119" t="inlineStr">
         <is>
           <t>S239;S240</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>PIC (mgr for GEPF)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Public PF asset manager</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Fund LP / co-investor</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Enko Capital</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Enko Impact Credit Fund</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Private credit</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Press release / trade press</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>BII / PIC partnership announcement; Ecofin Enko first-close coverage</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>PIC committed USD 30m to Enko Impact Credit Fund as the first investment under the BII-PIC partnership. BII committed USD 25m; Ecofin reports a USD 130m first close and names PIC among key investors. Fund provides private credit to mid-sized businesses in Sub-Saharan Africa.</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>SME / Mid-market finance</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>S241;S242</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>PIC (mgr for GEPF)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Public PF asset manager</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Fund LP / anchor investor</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Hlayisani Capital</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Hlayisani Venture Fund II</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>VC / growth equity</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Share of ZAR 500m first close</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>ZAR</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Fund manager press release</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Hlayisani Venture Fund II first-close announcement</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Hlayisani states that Hlayisani Venture Fund II achieved a ZAR 500m first close anchored by PIC and SA SME Fund. Fund backs high-growth South African businesses, including technology-enabled SMEs and platforms.</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Technology-enabled SMEs</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>S243</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Motor Industry Retirement Fund (MIRF)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Multi-employer PF</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Fund-of-funds allocation / initiative anchor</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>African Women Impact Fund / RisCura</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>African Women Impact Fund (AWIF)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Fund of Funds / gender-lens private markets</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Share of USD 45m MIRF/Copartes allocation</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>UN agency press release / advisor case study</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>UNECA AWIF launch; MiDA AWIF case study</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>UNECA reports MIRF and Copartes Pension Fund brought USD 45m of assets under the African Women Impact Fund initiative, alongside a USD 15m BADEA commitment for a USD 60m first commitment. AWIF is a fund-of-funds/gender-lens platform investing in women fund managers and gender-diverse teams.</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Fund of Funds</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Gender-lens / women fund managers</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Fund of Funds LP</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>S244;S245</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Copartes Pension Fund</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Pension fund</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Fund-of-funds allocation / initiative anchor</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>African Women Impact Fund / RisCura</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>African Women Impact Fund (AWIF)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Fund of Funds / gender-lens private markets</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Share of USD 45m MIRF/Copartes allocation</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>UN agency press release / advisor case study</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>UNECA AWIF launch; MiDA AWIF case study</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>UNECA reports MIRF and Copartes Pension Fund brought USD 45m of assets under the African Women Impact Fund initiative, alongside a USD 15m BADEA commitment for a USD 60m first commitment. Individual split between MIRF and Copartes was not disclosed publicly.</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Fund of Funds</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Gender-lens / women fund managers</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Fund of Funds LP</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>S244;S245</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Mineworkers Provident Fund</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Multi-employer PF</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Kholo Capital</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Kholo Capital Mezzanine Debt Fund I</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Private credit / mezzanine debt</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Share of ZAR 870m first close</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>ZAR</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Trade press</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Kholo Capital Mezzanine Debt Fund I first-close coverage</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Kholo Capital Mezzanine Debt Fund I reached a ZAR 870m first close with institutional investors including Mineworkers Provident Fund and National Fund for Municipal Workers. The fund provides mezzanine/private debt to mid-market businesses in Southern Africa.</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Mid-market finance</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>S246;S247</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>National Fund for Municipal Workers (NFMW)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Multi-employer PF</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Kholo Capital</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Kholo Capital Mezzanine Debt Fund I</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Private credit / mezzanine debt</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Share of ZAR 870m first close</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>ZAR</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Trade press</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Kholo Capital Mezzanine Debt Fund I first-close coverage</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Kholo Capital Mezzanine Debt Fund I reached a ZAR 870m first close with institutional investors including Mineworkers Provident Fund and National Fund for Municipal Workers. Later coverage reported final close at about ZAR 1.4bn, but allocator-level final-close amounts were not publicly split.</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Mid-market finance</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>S246;S247</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Public Service Superannuation Scheme (PSSS)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Africa50</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Africa50 Infrastructure Acceleration Fund (IAF)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Africa50 MCM inaugural investment announcement May 2025</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Africa50 stated that IAF's inaugural MCM transaction followed recent commitments from DBSA, Axian Group, Public Service Superannuation Fund (Kenya), and CNPS Cameroon, adding to first-close capital. Name reconciled to existing dashboard institution Public Service Superannuation Scheme (PSSS).</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>S248</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CNPS Cameroon</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Public PF</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Africa50</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Africa50 Infrastructure Acceleration Fund (IAF)</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Pan-Africa</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Africa50 MCM inaugural investment announcement May 2025</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Africa50 stated that IAF's inaugural MCM transaction followed recent commitments from DBSA, Axian Group, Public Service Superannuation Fund (Kenya), and CNPS Cameroon, adding to first-close capital. Distinct from CNPS Cameroon's existing AFC equity-shareholder row.</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Real Assets / Infrastructure Equity</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>S248</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>GEPF (via PIC)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Public PF (via mgr)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Ninety One</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Africa Credit Opportunities Fund III (ACO Fund 3)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Private credit</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Africa + emerging markets</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Annual report / GP press release</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>GEPF annual report; Ninety One ACO Fund 3 first close</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>GEPF 2025 annual report names an approved allocation to the Ninety One Credit Fund / Africa Credit Opportunities Fund III inside the Pan-African private markets portfolio. Ninety One reported ACO Fund 3 first close at USD 260m with IFC, BII and SIFEM as anchor LPs plus a Standard Bank debt facility; FinDev Canada later committed USD 20m.</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>SME / Mid-market finance; Infrastructure</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>S219;S249;S250</t>
         </is>
       </c>
     </row>
@@ -47341,7 +48872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="16" min="1" max="1"/>
@@ -48699,7 +50230,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>222.5 first close (&gt;275 mobilised)</t>
+          <t>222.5 first close (&gt;275 mobilised; later commitments added in 2025)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -48714,30 +50245,30 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5+ named</t>
+          <t>7+ named</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>NSIA Nigeria, CDC Sénégal, CDC Benin, CNSS Togo, CDG Invest Morocco</t>
+          <t>NSIA Nigeria, CDC Senegal, CDC Benin, CNSS Togo, CDG Invest Morocco, Public Service Superannuation Scheme/Fund Kenya, CNPS Cameroon</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>AfDB, IFC</t>
+          <t>AfDB, IFC, DBSA</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Attijariwafa Bank (Morocco), Arab Bank for Economic Development in Africa, West African Development Bank (BOAD)</t>
+          <t>Attijariwafa Bank (Morocco), Arab Bank for Economic Development in Africa, West African Development Bank (BOAD), Axian Group</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>First major pan-African infra fund MAJORITY-funded by African institutions. Africa50's flagship LP-style vehicle.</t>
+          <t>First major pan-African infra fund majority-funded by African institutions. May 2025 Africa50 release adds Kenya PSSS/PSSF and CNPS Cameroon as recent African PF LPs.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -51066,6 +52597,352 @@
         </is>
       </c>
       <c r="O54" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Enko Impact Credit Fund</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Enko Capital</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>130</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Private credit</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PIC (mgr for GEPF) (USD 30m)</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>BII (USD 25m)</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>SICOM Global Fund; other unnamed African pension funds and institutional investors</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>BII-PIC partnership first investment; Ecofin reports USD 130m first close, with PIC USD 30m and BII USD 25m commitments.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>SME / Mid-market finance</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Hlayisani Venture Fund II</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hlayisani Capital</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>~27 (ZAR 500m first close)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>VC / growth equity</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PIC (mgr for GEPF)</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>SA SME Fund</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>ZAR 500m first close anchored by PIC and SA SME Fund; South African venture/growth fund for technology-enabled SMEs and platforms.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Technology-enabled SMEs</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>African Women Impact Fund (AWIF)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>African Women Impact Fund / RisCura</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>60</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Fund of Funds / gender-lens private markets</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Motor Industry Retirement Fund (MIRF); Copartes Pension Fund (combined USD 45m under AWIF initiative)</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>BADEA (USD 15m)</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD 60m first commitment combines USD 45m from MIRF/Copartes with USD 15m BADEA; AWIF backs women fund managers and gender-diverse investment teams.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Fund of Funds</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Gender-lens / women fund managers</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Fund of Funds LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Kholo Capital Mezzanine Debt Fund I</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kholo Capital</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>~47 at first close (ZAR 870m); later ZAR 1.4bn final close</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Private credit / mezzanine debt</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Mineworkers Provident Fund; National Fund for Municipal Workers (NFMW)</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Other institutional investors not individually split in public first-close coverage</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>First close named two South African pension funds; fund provides mezzanine/private debt to mid-market businesses in Southern Africa.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Mid-market finance</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Fund LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Africa Credit Opportunities Fund III (ACO Fund 3)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ninety One</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>260 first close</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Private credit</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Africa + emerging markets</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>GEPF (via PIC) (amount not disclosed)</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>IFC, BII, SIFEM, FinDev Canada</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Standard Bank USD 45m debt facility</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>GEPF-approved allocation to specific Ninety One African credit fund; GP first-close source names DFI anchors and Standard Bank facility.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Private Credit</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>SME / Mid-market finance; Infrastructure</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t>Fund LP</t>
         </is>
@@ -51087,7 +52964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="16" min="1" max="1"/>
@@ -51138,11 +53015,11 @@
         </is>
       </c>
       <c r="B4" s="23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
-          <t>Growth Investment Partners (GIP) Ghana; Growth Investment Partners (GIP) Zambia; Ascent Rift Valley Fund I (ARVF I); Ascent Rift Valley Fund II (ARVF II); Catalyst Fund II; Helios Investors II/III/IV (historical); Vantage Mezzanine IV (Pan-African sub-fund); Convergence Partners Communications Infrastructure Fund; Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Capital Alliance Private Equity I-IV (CAPE); Africa Food Security Fund (AFSF); Verod Growth Fund III; Neoma Africa Fund III (B) L.P. (previously Abraaj Africa Fund III); African Development Partners III (ADP III)</t>
+          <t>Growth Investment Partners (GIP) Ghana; Growth Investment Partners (GIP) Zambia; Ascent Rift Valley Fund I (ARVF I); Ascent Rift Valley Fund II (ARVF II); Catalyst Fund II; Helios Investors II/III/IV (historical); Vantage Mezzanine IV (Pan-African sub-fund); Convergence Partners Communications Infrastructure Fund; Sahel Capital Fund for Agricultural Finance in Nigeria (FAFIN); Capital Alliance Private Equity I-IV (CAPE); Africa Food Security Fund (AFSF); Verod Growth Fund III; Neoma Africa Fund III (B) L.P. (previously Abraaj Africa Fund III); African Development Partners III (ADP III); Enko Impact Credit Fund</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -51758,10 +53635,31 @@
     <row r="46" ht="23.85" customHeight="1" s="16"/>
     <row r="47" ht="23.85" customHeight="1" s="16"/>
     <row r="48" ht="129.75" customHeight="1" s="16"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BADEA</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>African Women Impact Fund (AWIF)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Catalytic commitment alongside African pension capital in gender-lens fund-of-funds platform.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3 (Selective / TA)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:E27"/>
   <mergeCells count="3">

--- a/african_pf and swf_dataset_5.13.26.xlsx
+++ b/african_pf and swf_dataset_5.13.26.xlsx
@@ -2220,6 +2220,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="16">
       <c r="A19" s="18" t="inlineStr">
         <is>
@@ -2235,6 +2236,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
@@ -2521,7 +2523,7 @@
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>https://archive.fsdafrica.org/arm-harith-and-fsd-africa-investments-announce-gbp-10m-commitment-to-unlock-nigerian-pension-funds-and-catalyse-local-capital-for-infrastructure/</t>
+          <t>https://fsdafrica.org/nairobi-15-april-2025-10am-eat-fsd-africa-investments-fsdai-the-uk-backed-specialist-development-finance-investor-is-investing-gbp-10-million-into-arm-hariths-climate-and-transition-in/</t>
         </is>
       </c>
     </row>
@@ -7877,7 +7879,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>PSSSF investment guidelines / Annual report</t>
+          <t>PSSSF official website</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -7887,7 +7889,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.psssf.go.tz/uploads/publication/37Publication2023-05-022267.pdf</t>
+          <t>https://www.psssf.go.tz/</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9098,7 +9100,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Savannah Impact Advisory (Manager of Ci Gaba FoF)</t>
+          <t>Savannah Impact Advisory - Ci-Gaba Fund page</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -9108,7 +9110,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://siaghana.com/our-about/</t>
+          <t>https://www.siaghana.com/ci-gaba-fund</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -9505,7 +9507,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>AVCA — AfricInvest FIVE second close brings Norfund, IFU, CBK Pension Fund as investors (Oct 2018)</t>
+          <t>AfricInvest - FIVE second close brings Norfund, IFU, CBK Pension Fund as investors (Oct 2018)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -9515,7 +9517,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.avca-africa.org/newsroom/member-news/2018/africinvest-s-five-achieves-its-second-close-bringing-norfund-ifu-and-cbk-pension-fund-as-investors/</t>
+          <t>https://www.africinvest.com/news-and-media/news/africinvest-s-five-achieves-its-second-close-bringing-norfund-ifu-and-cbk-pension-fund-as-investors/</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -9579,7 +9581,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>AVCA — AfricInvest FIVE fourth close (2019)</t>
+          <t>AfricInvest - FIVE fourth close brings AfDB as investor (2019)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -9589,7 +9591,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.avca-africa.org/newsroom/member-news/2019/africinvest-s-five-achieves-fourth-close/</t>
+          <t>https://www.africinvest.com/news-and-media/news/africinvest-s-permanent-vehicle-five-achieves-its-fourth-close-bringing-afdb-as-investor/</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -12095,7 +12097,7 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Prosper Africa — U.S., Kenyan and South African Pension Funds Commit Over $94m to African PE &amp; Infrastructure</t>
+          <t>Africa PSA mirror - U.S., Kenyan and South African Pension Funds Commit Over $94m to African PE &amp; Infrastructure</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -12105,7 +12107,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.prosperafrica.gov/news/impact-story/u-s-kenyan-and-south-african-pension-funds-commit-over-94-million-to-african-private-equity-infrastructure/</t>
+          <t>https://www.africapsa.org/news/u-s-kenyan-and-south-african-pension-funds-commit-over-94-million-to-african-private-equity-infrastructure/</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -15407,6 +15409,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -15830,6 +15833,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -16704,6 +16708,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="16">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -16711,6 +16716,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="23.25" customHeight="1" s="16">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -16819,6 +16825,8 @@
         <v>0.19</v>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="16">
       <c r="A11" s="8" t="inlineStr">
         <is>
@@ -17092,6 +17100,8 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="16">
       <c r="A32" s="8" t="inlineStr">
         <is>
@@ -28714,6 +28724,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -47495,7 +47506,7 @@
       </c>
       <c r="P2" s="26" t="inlineStr">
         <is>
-          <t>https://archive.fsdafrica.org/arm-harith-and-fsd-africa-investments-announce-gbp-10m-commitment-to-unlock-nigerian-pension-funds-and-catalyse-local-capital-for-infrastructure/</t>
+          <t>https://fsdafrica.org/nairobi-15-april-2025-10am-eat-fsd-africa-investments-fsdai-the-uk-backed-specialist-development-finance-investor-is-investing-gbp-10-million-into-arm-hariths-climate-and-transition-in/</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -48896,6 +48907,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="45.75" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -52981,6 +52993,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="45.75" customHeight="1" s="16">
       <c r="A3" s="24" t="inlineStr">
         <is>
@@ -53707,6 +53720,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="23.25" customHeight="1" s="16">
       <c r="A3" s="1" t="inlineStr">
         <is>
